--- a/_SourceFiles/DeedInfo-3-Hobbies.xlsx
+++ b/_SourceFiles/DeedInfo-3-Hobbies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\SourceFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\_SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAB468D-9FF4-47EB-B101-0255172A678F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519937AB-B8AB-4BB4-951A-568441845630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17925" yWindow="0" windowWidth="13620" windowHeight="15600" activeTab="6" xr2:uid="{CDC9C16A-58F0-4807-B5CD-F77FF9D2EA43}"/>
+    <workbookView xWindow="7005" yWindow="2115" windowWidth="21420" windowHeight="13425" activeTab="6" xr2:uid="{CDC9C16A-58F0-4807-B5CD-F77FF9D2EA43}"/>
   </bookViews>
   <sheets>
     <sheet name="Type" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="270">
   <si>
     <t>TITLE</t>
   </si>
@@ -734,6 +734,123 @@
   </si>
   <si>
     <t>The Rarest of Birds in Eriador</t>
+  </si>
+  <si>
+    <t>All the Birds of Lothlórien</t>
+  </si>
+  <si>
+    <t>Birds of Lothlórien: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Lothlórien: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Lothlórien</t>
+  </si>
+  <si>
+    <t>All the Birds of Mirkwood</t>
+  </si>
+  <si>
+    <t>Birds of Mirkwood: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Mirkwood: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Mirkwood</t>
+  </si>
+  <si>
+    <t>All the Birds of the Great River</t>
+  </si>
+  <si>
+    <t>Birds of the Great River: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of the Great River: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird of the Great River</t>
+  </si>
+  <si>
+    <t>All the Birds of the Wold</t>
+  </si>
+  <si>
+    <t>Birds of the Wold: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of the Wold: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird of the Wold</t>
+  </si>
+  <si>
+    <t>All the Birds of Fangorn</t>
+  </si>
+  <si>
+    <t>Birds of Fangorn: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of Fangorn: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in Fangorn</t>
+  </si>
+  <si>
+    <t>All the Birds of the Croftlands</t>
+  </si>
+  <si>
+    <t>Birds of the Croftlands: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>The Rarest Bird of the Croftlands</t>
+  </si>
+  <si>
+    <t>Birds of the Croftlands: Rare</t>
+  </si>
+  <si>
+    <t>All the Birds of the Entwash</t>
+  </si>
+  <si>
+    <t>Birds of the Entwash: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of the Entwash: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird of the Entwash</t>
+  </si>
+  <si>
+    <t>All the Birds of the Westfold</t>
+  </si>
+  <si>
+    <t>Birds of the Westfold: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of the Westfold: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird in the Westfold</t>
+  </si>
+  <si>
+    <t>All the Birds of the Eastfold</t>
+  </si>
+  <si>
+    <t>Birds of the Eastfold: Common and Uncommon</t>
+  </si>
+  <si>
+    <t>Birds of the Eastfold: Rare</t>
+  </si>
+  <si>
+    <t>The Rarest Bird of the Eastfold</t>
+  </si>
+  <si>
+    <t>The Rarest of Birds in Rohan and the Great River</t>
+  </si>
+  <si>
+    <t>Eriador</t>
+  </si>
+  <si>
+    <t>Rohan and the Great River</t>
   </si>
 </sst>
 </file>
@@ -3046,7 +3163,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0167BB01-205D-43FC-93D0-141B65BF993A}">
-  <dimension ref="A1:AL66"/>
+  <dimension ref="A1:AL101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -3057,7 +3174,7 @@
     <col min="11" max="11" width="0" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.140625" customWidth="1"/>
-    <col min="16" max="16" width="43.5703125" customWidth="1"/>
+    <col min="16" max="16" width="43.5703125" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3178,21 +3295,18 @@
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1879490678</v>
-      </c>
-      <c r="C2" t="s">
-        <v>170</v>
-      </c>
-      <c r="I2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="C2" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D2" t="s">
+        <v>138</v>
+      </c>
+      <c r="M2">
+        <v>320</v>
       </c>
       <c r="O2" t="str">
         <f>CONCATENATE(R2,T2,U2,AL2," -- ",C2)</f>
-        <v xml:space="preserve">  [1] = {["ID"] = 1879490678; }; -- All the Birds of Bree-land</v>
+        <v xml:space="preserve">  [1] = {["CAT_ID"] = 320; }; -- Eriador</v>
       </c>
       <c r="P2" s="1" t="e">
         <f t="shared" ref="P2" si="0">CONCATENATE(R2,S2,V2,X2,Z2,AB2,AD2,AF2,AG2,AH2,AI2,AJ2,AK2,AL2)</f>
@@ -3208,27 +3322,27 @@
       </c>
       <c r="S2" t="str">
         <f t="shared" ref="S2" si="1">IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"                     ")</f>
-        <v xml:space="preserve">["ID"] = 1879490678; </v>
+        <v xml:space="preserve">                     </v>
       </c>
       <c r="T2" t="str">
         <f t="shared" ref="T2" si="2">IF(LEN(A2)&gt;0,CONCATENATE("[""ID""] = ",A2,"; "),"")</f>
-        <v xml:space="preserve">["ID"] = 1879490678; </v>
+        <v/>
       </c>
       <c r="U2" t="str">
         <f t="shared" ref="U2" si="3">IF(LEN(M2)&gt;0,CONCATENATE("[""CAT_ID""] = ",M2,"; "),"")</f>
-        <v/>
+        <v xml:space="preserve">["CAT_ID"] = 320; </v>
       </c>
       <c r="V2" s="1" t="str">
         <f t="shared" ref="V2" si="4">IF(LEN(B2)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B2)),B2,"; "),"")</f>
         <v/>
       </c>
-      <c r="W2" t="e">
+      <c r="W2">
         <f>VLOOKUP(D2,Type!A$2:B$17,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X2" t="e">
+        <v>14</v>
+      </c>
+      <c r="X2" t="str">
         <f>CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(W2)),W2,"; ")</f>
-        <v>#N/A</v>
+        <v xml:space="preserve">["TYPE"] = 14; </v>
       </c>
       <c r="Y2" t="str">
         <f t="shared" ref="Y2" si="5">TEXT(E2,0)</f>
@@ -3254,13 +3368,13 @@
         <f>CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AC2)),TEXT(AC2,"0"),"; ")</f>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
-      <c r="AE2">
+      <c r="AE2" t="e">
         <f>VLOOKUP(I2,Faction!A$2:B$77,2,FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="AF2" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="AF2" t="e">
         <f t="shared" ref="AF2" si="8">CONCATENATE("[""FACTION""] = ",TEXT(AE2,"0"),"; ")</f>
-        <v xml:space="preserve">["FACTION"] = 1; </v>
+        <v>#N/A</v>
       </c>
       <c r="AG2" t="str">
         <f>CONCATENATE("[""TIER""] = ",TEXT(L2,"0"),"; ")</f>
@@ -3268,7 +3382,7 @@
       </c>
       <c r="AH2" t="str">
         <f>CONCATENATE("[""NAME""] = { [""EN""] = """,C2,"""; }; ")</f>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Bree-land"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Eriador"; }; </v>
       </c>
       <c r="AI2" t="str">
         <f>CONCATENATE("[""LORE""] = { [""EN""] = """,K2,"""; }; ")</f>
@@ -3289,20 +3403,20 @@
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1879490611</v>
+        <v>1879490678</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I3" t="s">
         <v>79</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ref="O3:O66" si="9">CONCATENATE(R3,T3,U3,AL3," -- ",C3)</f>
-        <v xml:space="preserve">  [2] = {["ID"] = 1879490611; }; -- Birds of Bree-land: Common and Uncommon</v>
+        <v xml:space="preserve">  [2] = {["ID"] = 1879490678; }; -- All the Birds of Bree-land</v>
       </c>
       <c r="P3" s="1" t="e">
         <f t="shared" ref="P3:P66" si="10">CONCATENATE(R3,S3,V3,X3,Z3,AB3,AD3,AF3,AG3,AH3,AI3,AJ3,AK3,AL3)</f>
@@ -3318,11 +3432,11 @@
       </c>
       <c r="S3" t="str">
         <f t="shared" ref="S3:S66" si="13">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"                     ")</f>
-        <v xml:space="preserve">["ID"] = 1879490611; </v>
+        <v xml:space="preserve">["ID"] = 1879490678; </v>
       </c>
       <c r="T3" t="str">
         <f t="shared" ref="T3:T66" si="14">IF(LEN(A3)&gt;0,CONCATENATE("[""ID""] = ",A3,"; "),"")</f>
-        <v xml:space="preserve">["ID"] = 1879490611; </v>
+        <v xml:space="preserve">["ID"] = 1879490678; </v>
       </c>
       <c r="U3" t="str">
         <f t="shared" ref="U3:U66" si="15">IF(LEN(M3)&gt;0,CONCATENATE("[""CAT_ID""] = ",M3,"; "),"")</f>
@@ -3374,11 +3488,11 @@
       </c>
       <c r="AG3" t="str">
         <f t="shared" ref="AG3:AG66" si="25">CONCATENATE("[""TIER""] = ",TEXT(L3,"0"),"; ")</f>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH3" t="str">
         <f t="shared" ref="AH3:AH66" si="26">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Bree-land: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Bree-land"; }; </v>
       </c>
       <c r="AI3" t="str">
         <f t="shared" ref="AI3:AI66" si="27">CONCATENATE("[""LORE""] = { [""EN""] = """,K3,"""; }; ")</f>
@@ -3399,10 +3513,10 @@
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1879490469</v>
+        <v>1879490611</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I4" t="s">
         <v>79</v>
@@ -3412,7 +3526,7 @@
       </c>
       <c r="O4" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">  [3] = {["ID"] = 1879490469; }; -- Birds of Bree-land: Rare</v>
+        <v xml:space="preserve">  [3] = {["ID"] = 1879490611; }; -- Birds of Bree-land: Common and Uncommon</v>
       </c>
       <c r="P4" s="1" t="e">
         <f t="shared" si="10"/>
@@ -3428,11 +3542,11 @@
       </c>
       <c r="S4" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490469; </v>
+        <v xml:space="preserve">["ID"] = 1879490611; </v>
       </c>
       <c r="T4" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490469; </v>
+        <v xml:space="preserve">["ID"] = 1879490611; </v>
       </c>
       <c r="U4" t="str">
         <f t="shared" si="15"/>
@@ -3488,7 +3602,7 @@
       </c>
       <c r="AH4" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Bree-land: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Bree-land: Common and Uncommon"; }; </v>
       </c>
       <c r="AI4" t="str">
         <f t="shared" si="27"/>
@@ -3509,10 +3623,10 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1879490610</v>
+        <v>1879490469</v>
       </c>
       <c r="C5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I5" t="s">
         <v>79</v>
@@ -3522,7 +3636,7 @@
       </c>
       <c r="O5" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">  [4] = {["ID"] = 1879490610; }; -- The Rarest Bird in Bree-land</v>
+        <v xml:space="preserve">  [4] = {["ID"] = 1879490469; }; -- Birds of Bree-land: Rare</v>
       </c>
       <c r="P5" s="1" t="e">
         <f t="shared" si="10"/>
@@ -3538,11 +3652,11 @@
       </c>
       <c r="S5" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490610; </v>
+        <v xml:space="preserve">["ID"] = 1879490469; </v>
       </c>
       <c r="T5" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490610; </v>
+        <v xml:space="preserve">["ID"] = 1879490469; </v>
       </c>
       <c r="U5" t="str">
         <f t="shared" si="15"/>
@@ -3598,7 +3712,7 @@
       </c>
       <c r="AH5" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Bree-land"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Bree-land: Rare"; }; </v>
       </c>
       <c r="AI5" t="str">
         <f t="shared" si="27"/>
@@ -3619,20 +3733,20 @@
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1879490682</v>
+        <v>1879490610</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I6" t="s">
         <v>79</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">  [5] = {["ID"] = 1879490682; }; -- All the Birds of the Shire</v>
+        <v xml:space="preserve">  [5] = {["ID"] = 1879490610; }; -- The Rarest Bird in Bree-land</v>
       </c>
       <c r="P6" s="1" t="e">
         <f t="shared" si="10"/>
@@ -3648,11 +3762,11 @@
       </c>
       <c r="S6" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490682; </v>
+        <v xml:space="preserve">["ID"] = 1879490610; </v>
       </c>
       <c r="T6" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490682; </v>
+        <v xml:space="preserve">["ID"] = 1879490610; </v>
       </c>
       <c r="U6" t="str">
         <f t="shared" si="15"/>
@@ -3704,11 +3818,11 @@
       </c>
       <c r="AG6" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH6" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Shire"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Bree-land"; }; </v>
       </c>
       <c r="AI6" t="str">
         <f t="shared" si="27"/>
@@ -3729,20 +3843,20 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1879490617</v>
+        <v>1879490682</v>
       </c>
       <c r="C7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I7" t="s">
         <v>79</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">  [6] = {["ID"] = 1879490617; }; -- Birds of The Shire: Common and Uncommon</v>
+        <v xml:space="preserve">  [6] = {["ID"] = 1879490682; }; -- All the Birds of the Shire</v>
       </c>
       <c r="P7" s="1" t="e">
         <f t="shared" si="10"/>
@@ -3758,11 +3872,11 @@
       </c>
       <c r="S7" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490617; </v>
+        <v xml:space="preserve">["ID"] = 1879490682; </v>
       </c>
       <c r="T7" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490617; </v>
+        <v xml:space="preserve">["ID"] = 1879490682; </v>
       </c>
       <c r="U7" t="str">
         <f t="shared" si="15"/>
@@ -3814,11 +3928,11 @@
       </c>
       <c r="AG7" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH7" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of The Shire: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Shire"; }; </v>
       </c>
       <c r="AI7" t="str">
         <f t="shared" si="27"/>
@@ -3839,17 +3953,20 @@
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1879490640</v>
+        <v>1879490617</v>
       </c>
       <c r="C8" t="s">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="I8" t="s">
+        <v>79</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">  [7] = {["ID"] = 1879490640; }; -- Birds of The Shire: Rare</v>
+        <v xml:space="preserve">  [7] = {["ID"] = 1879490617; }; -- Birds of The Shire: Common and Uncommon</v>
       </c>
       <c r="P8" s="1" t="e">
         <f t="shared" si="10"/>
@@ -3865,11 +3982,11 @@
       </c>
       <c r="S8" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490640; </v>
+        <v xml:space="preserve">["ID"] = 1879490617; </v>
       </c>
       <c r="T8" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490640; </v>
+        <v xml:space="preserve">["ID"] = 1879490617; </v>
       </c>
       <c r="U8" t="str">
         <f t="shared" si="15"/>
@@ -3911,13 +4028,13 @@
         <f t="shared" si="23"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
-      <c r="AE8" t="e">
+      <c r="AE8">
         <f>VLOOKUP(I8,Faction!A$2:B$77,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="str">
         <f t="shared" si="24"/>
-        <v>#N/A</v>
+        <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AG8" t="str">
         <f t="shared" si="25"/>
@@ -3925,7 +4042,7 @@
       </c>
       <c r="AH8" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of The Shire: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of The Shire: Common and Uncommon"; }; </v>
       </c>
       <c r="AI8" t="str">
         <f t="shared" si="27"/>
@@ -3946,17 +4063,17 @@
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>1879490622</v>
+        <v>1879490640</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">  [8] = {["ID"] = 1879490622; }; -- The Rarest Bird in The Shire</v>
+        <v xml:space="preserve">  [8] = {["ID"] = 1879490640; }; -- Birds of The Shire: Rare</v>
       </c>
       <c r="P9" s="1" t="e">
         <f t="shared" si="10"/>
@@ -3972,11 +4089,11 @@
       </c>
       <c r="S9" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490622; </v>
+        <v xml:space="preserve">["ID"] = 1879490640; </v>
       </c>
       <c r="T9" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490622; </v>
+        <v xml:space="preserve">["ID"] = 1879490640; </v>
       </c>
       <c r="U9" t="str">
         <f t="shared" si="15"/>
@@ -4032,7 +4149,7 @@
       </c>
       <c r="AH9" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in The Shire"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of The Shire: Rare"; }; </v>
       </c>
       <c r="AI9" t="str">
         <f t="shared" si="27"/>
@@ -4053,17 +4170,17 @@
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1879490671</v>
+        <v>1879490622</v>
       </c>
       <c r="C10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">  [9] = {["ID"] = 1879490671; }; -- All the Birds of Ered Luin</v>
+        <v xml:space="preserve">  [9] = {["ID"] = 1879490622; }; -- The Rarest Bird in The Shire</v>
       </c>
       <c r="P10" s="1" t="e">
         <f t="shared" si="10"/>
@@ -4079,11 +4196,11 @@
       </c>
       <c r="S10" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490671; </v>
+        <v xml:space="preserve">["ID"] = 1879490622; </v>
       </c>
       <c r="T10" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490671; </v>
+        <v xml:space="preserve">["ID"] = 1879490622; </v>
       </c>
       <c r="U10" t="str">
         <f t="shared" si="15"/>
@@ -4135,11 +4252,11 @@
       </c>
       <c r="AG10" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH10" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Ered Luin"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in The Shire"; }; </v>
       </c>
       <c r="AI10" t="str">
         <f t="shared" si="27"/>
@@ -4160,17 +4277,17 @@
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>1879490651</v>
+        <v>1879490671</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [10] = {["ID"] = 1879490651; }; -- Birds of Ered Luin: Common and Uncommon</v>
+        <v xml:space="preserve"> [10] = {["ID"] = 1879490671; }; -- All the Birds of Ered Luin</v>
       </c>
       <c r="P11" s="1" t="e">
         <f t="shared" si="10"/>
@@ -4186,11 +4303,11 @@
       </c>
       <c r="S11" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490651; </v>
+        <v xml:space="preserve">["ID"] = 1879490671; </v>
       </c>
       <c r="T11" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490651; </v>
+        <v xml:space="preserve">["ID"] = 1879490671; </v>
       </c>
       <c r="U11" t="str">
         <f t="shared" si="15"/>
@@ -4242,11 +4359,11 @@
       </c>
       <c r="AG11" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH11" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Ered Luin: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Ered Luin"; }; </v>
       </c>
       <c r="AI11" t="str">
         <f t="shared" si="27"/>
@@ -4267,17 +4384,17 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>1879490635</v>
+        <v>1879490651</v>
       </c>
       <c r="C12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L12">
         <v>1</v>
       </c>
       <c r="O12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [11] = {["ID"] = 1879490635; }; -- Birds of Ered Luin: Rare</v>
+        <v xml:space="preserve"> [11] = {["ID"] = 1879490651; }; -- Birds of Ered Luin: Common and Uncommon</v>
       </c>
       <c r="P12" s="1" t="e">
         <f t="shared" si="10"/>
@@ -4293,11 +4410,11 @@
       </c>
       <c r="S12" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490635; </v>
+        <v xml:space="preserve">["ID"] = 1879490651; </v>
       </c>
       <c r="T12" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490635; </v>
+        <v xml:space="preserve">["ID"] = 1879490651; </v>
       </c>
       <c r="U12" t="str">
         <f t="shared" si="15"/>
@@ -4353,7 +4470,7 @@
       </c>
       <c r="AH12" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Ered Luin: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Ered Luin: Common and Uncommon"; }; </v>
       </c>
       <c r="AI12" t="str">
         <f t="shared" si="27"/>
@@ -4374,17 +4491,17 @@
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>1879490633</v>
+        <v>1879490635</v>
       </c>
       <c r="C13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
       <c r="O13" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [12] = {["ID"] = 1879490633; }; -- The Rarest Bird in Ered Luin</v>
+        <v xml:space="preserve"> [12] = {["ID"] = 1879490635; }; -- Birds of Ered Luin: Rare</v>
       </c>
       <c r="P13" s="1" t="e">
         <f t="shared" si="10"/>
@@ -4400,11 +4517,11 @@
       </c>
       <c r="S13" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490633; </v>
+        <v xml:space="preserve">["ID"] = 1879490635; </v>
       </c>
       <c r="T13" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490633; </v>
+        <v xml:space="preserve">["ID"] = 1879490635; </v>
       </c>
       <c r="U13" t="str">
         <f t="shared" si="15"/>
@@ -4460,7 +4577,7 @@
       </c>
       <c r="AH13" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Ered Luin"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Ered Luin: Rare"; }; </v>
       </c>
       <c r="AI13" t="str">
         <f t="shared" si="27"/>
@@ -4481,17 +4598,17 @@
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1879490668</v>
+        <v>1879490633</v>
       </c>
       <c r="C14" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [13] = {["ID"] = 1879490668; }; -- All the Birds of Swanfleet</v>
+        <v xml:space="preserve"> [13] = {["ID"] = 1879490633; }; -- The Rarest Bird in Ered Luin</v>
       </c>
       <c r="P14" s="1" t="e">
         <f t="shared" si="10"/>
@@ -4507,11 +4624,11 @@
       </c>
       <c r="S14" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490668; </v>
+        <v xml:space="preserve">["ID"] = 1879490633; </v>
       </c>
       <c r="T14" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490668; </v>
+        <v xml:space="preserve">["ID"] = 1879490633; </v>
       </c>
       <c r="U14" t="str">
         <f t="shared" si="15"/>
@@ -4563,11 +4680,11 @@
       </c>
       <c r="AG14" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH14" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Swanfleet"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Ered Luin"; }; </v>
       </c>
       <c r="AI14" t="str">
         <f t="shared" si="27"/>
@@ -4588,17 +4705,17 @@
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>1879490642</v>
+        <v>1879490668</v>
       </c>
       <c r="C15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [14] = {["ID"] = 1879490642; }; -- Birds of Swanfleet: Common and Uncommon</v>
+        <v xml:space="preserve"> [14] = {["ID"] = 1879490668; }; -- All the Birds of Swanfleet</v>
       </c>
       <c r="P15" s="1" t="e">
         <f t="shared" si="10"/>
@@ -4614,11 +4731,11 @@
       </c>
       <c r="S15" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490642; </v>
+        <v xml:space="preserve">["ID"] = 1879490668; </v>
       </c>
       <c r="T15" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490642; </v>
+        <v xml:space="preserve">["ID"] = 1879490668; </v>
       </c>
       <c r="U15" t="str">
         <f t="shared" si="15"/>
@@ -4670,11 +4787,11 @@
       </c>
       <c r="AG15" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH15" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Swanfleet: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Swanfleet"; }; </v>
       </c>
       <c r="AI15" t="str">
         <f t="shared" si="27"/>
@@ -4695,17 +4812,17 @@
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>1879490641</v>
+        <v>1879490642</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L16">
         <v>1</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [15] = {["ID"] = 1879490641; }; -- Birds of Swanfleet: Rare</v>
+        <v xml:space="preserve"> [15] = {["ID"] = 1879490642; }; -- Birds of Swanfleet: Common and Uncommon</v>
       </c>
       <c r="P16" s="1" t="e">
         <f t="shared" si="10"/>
@@ -4721,11 +4838,11 @@
       </c>
       <c r="S16" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490641; </v>
+        <v xml:space="preserve">["ID"] = 1879490642; </v>
       </c>
       <c r="T16" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490641; </v>
+        <v xml:space="preserve">["ID"] = 1879490642; </v>
       </c>
       <c r="U16" t="str">
         <f t="shared" si="15"/>
@@ -4781,7 +4898,7 @@
       </c>
       <c r="AH16" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Swanfleet: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Swanfleet: Common and Uncommon"; }; </v>
       </c>
       <c r="AI16" t="str">
         <f t="shared" si="27"/>
@@ -4802,17 +4919,17 @@
     </row>
     <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>1879490645</v>
+        <v>1879490641</v>
       </c>
       <c r="C17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L17">
         <v>1</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [16] = {["ID"] = 1879490645; }; -- The Rarest Bird in Swanfleet</v>
+        <v xml:space="preserve"> [16] = {["ID"] = 1879490641; }; -- Birds of Swanfleet: Rare</v>
       </c>
       <c r="P17" s="1" t="e">
         <f t="shared" si="10"/>
@@ -4828,11 +4945,11 @@
       </c>
       <c r="S17" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490645; </v>
+        <v xml:space="preserve">["ID"] = 1879490641; </v>
       </c>
       <c r="T17" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490645; </v>
+        <v xml:space="preserve">["ID"] = 1879490641; </v>
       </c>
       <c r="U17" t="str">
         <f t="shared" si="15"/>
@@ -4888,7 +5005,7 @@
       </c>
       <c r="AH17" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Swanfleet"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Swanfleet: Rare"; }; </v>
       </c>
       <c r="AI17" t="str">
         <f t="shared" si="27"/>
@@ -4909,17 +5026,17 @@
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>1879490670</v>
+        <v>1879490645</v>
       </c>
       <c r="C18" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [17] = {["ID"] = 1879490670; }; -- All the Birds of Cardolan</v>
+        <v xml:space="preserve"> [17] = {["ID"] = 1879490645; }; -- The Rarest Bird in Swanfleet</v>
       </c>
       <c r="P18" s="1" t="e">
         <f t="shared" si="10"/>
@@ -4935,11 +5052,11 @@
       </c>
       <c r="S18" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490670; </v>
+        <v xml:space="preserve">["ID"] = 1879490645; </v>
       </c>
       <c r="T18" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490670; </v>
+        <v xml:space="preserve">["ID"] = 1879490645; </v>
       </c>
       <c r="U18" t="str">
         <f t="shared" si="15"/>
@@ -4991,11 +5108,11 @@
       </c>
       <c r="AG18" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH18" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Cardolan"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Swanfleet"; }; </v>
       </c>
       <c r="AI18" t="str">
         <f t="shared" si="27"/>
@@ -5016,17 +5133,17 @@
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>1879490621</v>
+        <v>1879490670</v>
       </c>
       <c r="C19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [18] = {["ID"] = 1879490621; }; -- Birds of Cardolan: Common and Uncommon</v>
+        <v xml:space="preserve"> [18] = {["ID"] = 1879490670; }; -- All the Birds of Cardolan</v>
       </c>
       <c r="P19" s="1" t="e">
         <f t="shared" si="10"/>
@@ -5042,11 +5159,11 @@
       </c>
       <c r="S19" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490621; </v>
+        <v xml:space="preserve">["ID"] = 1879490670; </v>
       </c>
       <c r="T19" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490621; </v>
+        <v xml:space="preserve">["ID"] = 1879490670; </v>
       </c>
       <c r="U19" t="str">
         <f t="shared" si="15"/>
@@ -5098,11 +5215,11 @@
       </c>
       <c r="AG19" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH19" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Cardolan: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Cardolan"; }; </v>
       </c>
       <c r="AI19" t="str">
         <f t="shared" si="27"/>
@@ -5123,17 +5240,17 @@
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>1879490627</v>
+        <v>1879490621</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L20">
         <v>1</v>
       </c>
       <c r="O20" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [19] = {["ID"] = 1879490627; }; -- Birds of Cardolan: Rare</v>
+        <v xml:space="preserve"> [19] = {["ID"] = 1879490621; }; -- Birds of Cardolan: Common and Uncommon</v>
       </c>
       <c r="P20" s="1" t="e">
         <f t="shared" si="10"/>
@@ -5149,11 +5266,11 @@
       </c>
       <c r="S20" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490627; </v>
+        <v xml:space="preserve">["ID"] = 1879490621; </v>
       </c>
       <c r="T20" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490627; </v>
+        <v xml:space="preserve">["ID"] = 1879490621; </v>
       </c>
       <c r="U20" t="str">
         <f t="shared" si="15"/>
@@ -5209,7 +5326,7 @@
       </c>
       <c r="AH20" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Cardolan: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Cardolan: Common and Uncommon"; }; </v>
       </c>
       <c r="AI20" t="str">
         <f t="shared" si="27"/>
@@ -5230,17 +5347,17 @@
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>1879490647</v>
+        <v>1879490627</v>
       </c>
       <c r="C21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L21">
         <v>1</v>
       </c>
       <c r="O21" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [20] = {["ID"] = 1879490647; }; -- The Rarest Bird in Cardolan</v>
+        <v xml:space="preserve"> [20] = {["ID"] = 1879490627; }; -- Birds of Cardolan: Rare</v>
       </c>
       <c r="P21" s="1" t="e">
         <f t="shared" si="10"/>
@@ -5256,11 +5373,11 @@
       </c>
       <c r="S21" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490647; </v>
+        <v xml:space="preserve">["ID"] = 1879490627; </v>
       </c>
       <c r="T21" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490647; </v>
+        <v xml:space="preserve">["ID"] = 1879490627; </v>
       </c>
       <c r="U21" t="str">
         <f t="shared" si="15"/>
@@ -5316,7 +5433,7 @@
       </c>
       <c r="AH21" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Cardolan"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Cardolan: Rare"; }; </v>
       </c>
       <c r="AI21" t="str">
         <f t="shared" si="27"/>
@@ -5337,17 +5454,17 @@
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>1879490676</v>
+        <v>1879490647</v>
       </c>
       <c r="C22" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [21] = {["ID"] = 1879490676; }; -- All the Birds of the Lone-lands</v>
+        <v xml:space="preserve"> [21] = {["ID"] = 1879490647; }; -- The Rarest Bird in Cardolan</v>
       </c>
       <c r="P22" s="1" t="e">
         <f t="shared" si="10"/>
@@ -5363,11 +5480,11 @@
       </c>
       <c r="S22" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490676; </v>
+        <v xml:space="preserve">["ID"] = 1879490647; </v>
       </c>
       <c r="T22" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490676; </v>
+        <v xml:space="preserve">["ID"] = 1879490647; </v>
       </c>
       <c r="U22" t="str">
         <f t="shared" si="15"/>
@@ -5419,11 +5536,11 @@
       </c>
       <c r="AG22" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH22" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Lone-lands"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Cardolan"; }; </v>
       </c>
       <c r="AI22" t="str">
         <f t="shared" si="27"/>
@@ -5444,17 +5561,17 @@
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>1879490649</v>
+        <v>1879490676</v>
       </c>
       <c r="C23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [22] = {["ID"] = 1879490649; }; -- Birds of the Lone-lands: Common and Uncommon</v>
+        <v xml:space="preserve"> [22] = {["ID"] = 1879490676; }; -- All the Birds of the Lone-lands</v>
       </c>
       <c r="P23" s="1" t="e">
         <f t="shared" si="10"/>
@@ -5470,11 +5587,11 @@
       </c>
       <c r="S23" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490649; </v>
+        <v xml:space="preserve">["ID"] = 1879490676; </v>
       </c>
       <c r="T23" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490649; </v>
+        <v xml:space="preserve">["ID"] = 1879490676; </v>
       </c>
       <c r="U23" t="str">
         <f t="shared" si="15"/>
@@ -5526,11 +5643,11 @@
       </c>
       <c r="AG23" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH23" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Lone-lands: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Lone-lands"; }; </v>
       </c>
       <c r="AI23" t="str">
         <f t="shared" si="27"/>
@@ -5551,17 +5668,17 @@
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>1879490632</v>
+        <v>1879490649</v>
       </c>
       <c r="C24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L24">
         <v>1</v>
       </c>
       <c r="O24" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [23] = {["ID"] = 1879490632; }; -- Birds of the Lone-lands: Rare</v>
+        <v xml:space="preserve"> [23] = {["ID"] = 1879490649; }; -- Birds of the Lone-lands: Common and Uncommon</v>
       </c>
       <c r="P24" s="1" t="e">
         <f t="shared" si="10"/>
@@ -5577,11 +5694,11 @@
       </c>
       <c r="S24" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490632; </v>
+        <v xml:space="preserve">["ID"] = 1879490649; </v>
       </c>
       <c r="T24" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490632; </v>
+        <v xml:space="preserve">["ID"] = 1879490649; </v>
       </c>
       <c r="U24" t="str">
         <f t="shared" si="15"/>
@@ -5637,7 +5754,7 @@
       </c>
       <c r="AH24" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Lone-lands: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Lone-lands: Common and Uncommon"; }; </v>
       </c>
       <c r="AI24" t="str">
         <f t="shared" si="27"/>
@@ -5658,17 +5775,17 @@
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>1879490637</v>
+        <v>1879490632</v>
       </c>
       <c r="C25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L25">
         <v>1</v>
       </c>
       <c r="O25" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [24] = {["ID"] = 1879490637; }; -- The Rarest Bird in the Lone-lands</v>
+        <v xml:space="preserve"> [24] = {["ID"] = 1879490632; }; -- Birds of the Lone-lands: Rare</v>
       </c>
       <c r="P25" s="1" t="e">
         <f t="shared" si="10"/>
@@ -5684,11 +5801,11 @@
       </c>
       <c r="S25" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490637; </v>
+        <v xml:space="preserve">["ID"] = 1879490632; </v>
       </c>
       <c r="T25" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490637; </v>
+        <v xml:space="preserve">["ID"] = 1879490632; </v>
       </c>
       <c r="U25" t="str">
         <f t="shared" si="15"/>
@@ -5744,7 +5861,7 @@
       </c>
       <c r="AH25" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Lone-lands"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Lone-lands: Rare"; }; </v>
       </c>
       <c r="AI25" t="str">
         <f t="shared" si="27"/>
@@ -5765,17 +5882,17 @@
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>1879490675</v>
+        <v>1879490637</v>
       </c>
       <c r="C26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [25] = {["ID"] = 1879490675; }; -- All the Birds of the North Downs</v>
+        <v xml:space="preserve"> [25] = {["ID"] = 1879490637; }; -- The Rarest Bird in the Lone-lands</v>
       </c>
       <c r="P26" s="1" t="e">
         <f t="shared" si="10"/>
@@ -5791,11 +5908,11 @@
       </c>
       <c r="S26" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490675; </v>
+        <v xml:space="preserve">["ID"] = 1879490637; </v>
       </c>
       <c r="T26" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490675; </v>
+        <v xml:space="preserve">["ID"] = 1879490637; </v>
       </c>
       <c r="U26" t="str">
         <f t="shared" si="15"/>
@@ -5847,11 +5964,11 @@
       </c>
       <c r="AG26" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH26" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the North Downs"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Lone-lands"; }; </v>
       </c>
       <c r="AI26" t="str">
         <f t="shared" si="27"/>
@@ -5872,17 +5989,17 @@
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>1879490630</v>
+        <v>1879490675</v>
       </c>
       <c r="C27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [26] = {["ID"] = 1879490630; }; -- Birds of The North Downs: Common and Uncommon</v>
+        <v xml:space="preserve"> [26] = {["ID"] = 1879490675; }; -- All the Birds of the North Downs</v>
       </c>
       <c r="P27" s="1" t="e">
         <f t="shared" si="10"/>
@@ -5898,11 +6015,11 @@
       </c>
       <c r="S27" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490630; </v>
+        <v xml:space="preserve">["ID"] = 1879490675; </v>
       </c>
       <c r="T27" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490630; </v>
+        <v xml:space="preserve">["ID"] = 1879490675; </v>
       </c>
       <c r="U27" t="str">
         <f t="shared" si="15"/>
@@ -5954,11 +6071,11 @@
       </c>
       <c r="AG27" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH27" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of The North Downs: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the North Downs"; }; </v>
       </c>
       <c r="AI27" t="str">
         <f t="shared" si="27"/>
@@ -5979,17 +6096,17 @@
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>1879490626</v>
+        <v>1879490630</v>
       </c>
       <c r="C28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L28">
         <v>1</v>
       </c>
       <c r="O28" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [27] = {["ID"] = 1879490626; }; -- Birds of the North Downs: Rare</v>
+        <v xml:space="preserve"> [27] = {["ID"] = 1879490630; }; -- Birds of The North Downs: Common and Uncommon</v>
       </c>
       <c r="P28" s="1" t="e">
         <f t="shared" si="10"/>
@@ -6005,11 +6122,11 @@
       </c>
       <c r="S28" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490626; </v>
+        <v xml:space="preserve">["ID"] = 1879490630; </v>
       </c>
       <c r="T28" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490626; </v>
+        <v xml:space="preserve">["ID"] = 1879490630; </v>
       </c>
       <c r="U28" t="str">
         <f t="shared" si="15"/>
@@ -6065,7 +6182,7 @@
       </c>
       <c r="AH28" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the North Downs: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of The North Downs: Common and Uncommon"; }; </v>
       </c>
       <c r="AI28" t="str">
         <f t="shared" si="27"/>
@@ -6086,17 +6203,17 @@
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>1879490625</v>
+        <v>1879490626</v>
       </c>
       <c r="C29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L29">
         <v>1</v>
       </c>
       <c r="O29" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [28] = {["ID"] = 1879490625; }; -- The Rarest Bird in the North Downs</v>
+        <v xml:space="preserve"> [28] = {["ID"] = 1879490626; }; -- Birds of the North Downs: Rare</v>
       </c>
       <c r="P29" s="1" t="e">
         <f t="shared" si="10"/>
@@ -6112,11 +6229,11 @@
       </c>
       <c r="S29" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490625; </v>
+        <v xml:space="preserve">["ID"] = 1879490626; </v>
       </c>
       <c r="T29" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490625; </v>
+        <v xml:space="preserve">["ID"] = 1879490626; </v>
       </c>
       <c r="U29" t="str">
         <f t="shared" si="15"/>
@@ -6172,7 +6289,7 @@
       </c>
       <c r="AH29" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the North Downs"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the North Downs: Rare"; }; </v>
       </c>
       <c r="AI29" t="str">
         <f t="shared" si="27"/>
@@ -6193,17 +6310,17 @@
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>1879490677</v>
+        <v>1879490625</v>
       </c>
       <c r="C30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [29] = {["ID"] = 1879490677; }; -- All the Birds of the Trollshaws</v>
+        <v xml:space="preserve"> [29] = {["ID"] = 1879490625; }; -- The Rarest Bird in the North Downs</v>
       </c>
       <c r="P30" s="1" t="e">
         <f t="shared" si="10"/>
@@ -6219,11 +6336,11 @@
       </c>
       <c r="S30" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490677; </v>
+        <v xml:space="preserve">["ID"] = 1879490625; </v>
       </c>
       <c r="T30" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490677; </v>
+        <v xml:space="preserve">["ID"] = 1879490625; </v>
       </c>
       <c r="U30" t="str">
         <f t="shared" si="15"/>
@@ -6275,11 +6392,11 @@
       </c>
       <c r="AG30" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH30" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Trollshaws"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the North Downs"; }; </v>
       </c>
       <c r="AI30" t="str">
         <f t="shared" si="27"/>
@@ -6300,17 +6417,17 @@
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>1879490614</v>
+        <v>1879490677</v>
       </c>
       <c r="C31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [30] = {["ID"] = 1879490614; }; -- Birds of the Trollshaws: Common and Uncommon</v>
+        <v xml:space="preserve"> [30] = {["ID"] = 1879490677; }; -- All the Birds of the Trollshaws</v>
       </c>
       <c r="P31" s="1" t="e">
         <f t="shared" si="10"/>
@@ -6326,11 +6443,11 @@
       </c>
       <c r="S31" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490614; </v>
+        <v xml:space="preserve">["ID"] = 1879490677; </v>
       </c>
       <c r="T31" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490614; </v>
+        <v xml:space="preserve">["ID"] = 1879490677; </v>
       </c>
       <c r="U31" t="str">
         <f t="shared" si="15"/>
@@ -6382,11 +6499,11 @@
       </c>
       <c r="AG31" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH31" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Trollshaws: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Trollshaws"; }; </v>
       </c>
       <c r="AI31" t="str">
         <f t="shared" si="27"/>
@@ -6407,17 +6524,17 @@
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>1879490639</v>
+        <v>1879490614</v>
       </c>
       <c r="C32" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L32">
         <v>1</v>
       </c>
       <c r="O32" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [31] = {["ID"] = 1879490639; }; -- Birds of the Trollshaws: Rare</v>
+        <v xml:space="preserve"> [31] = {["ID"] = 1879490614; }; -- Birds of the Trollshaws: Common and Uncommon</v>
       </c>
       <c r="P32" s="1" t="e">
         <f t="shared" si="10"/>
@@ -6433,11 +6550,11 @@
       </c>
       <c r="S32" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490639; </v>
+        <v xml:space="preserve">["ID"] = 1879490614; </v>
       </c>
       <c r="T32" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490639; </v>
+        <v xml:space="preserve">["ID"] = 1879490614; </v>
       </c>
       <c r="U32" t="str">
         <f t="shared" si="15"/>
@@ -6493,7 +6610,7 @@
       </c>
       <c r="AH32" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Trollshaws: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Trollshaws: Common and Uncommon"; }; </v>
       </c>
       <c r="AI32" t="str">
         <f t="shared" si="27"/>
@@ -6514,17 +6631,17 @@
     </row>
     <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>1879490629</v>
+        <v>1879490639</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L33">
         <v>1</v>
       </c>
       <c r="O33" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [32] = {["ID"] = 1879490629; }; -- The Rarest Bird in the Trollshaws</v>
+        <v xml:space="preserve"> [32] = {["ID"] = 1879490639; }; -- Birds of the Trollshaws: Rare</v>
       </c>
       <c r="P33" s="1" t="e">
         <f t="shared" si="10"/>
@@ -6540,11 +6657,11 @@
       </c>
       <c r="S33" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490629; </v>
+        <v xml:space="preserve">["ID"] = 1879490639; </v>
       </c>
       <c r="T33" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490629; </v>
+        <v xml:space="preserve">["ID"] = 1879490639; </v>
       </c>
       <c r="U33" t="str">
         <f t="shared" si="15"/>
@@ -6600,7 +6717,7 @@
       </c>
       <c r="AH33" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Trollshaws"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Trollshaws: Rare"; }; </v>
       </c>
       <c r="AI33" t="str">
         <f t="shared" si="27"/>
@@ -6621,17 +6738,17 @@
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>1879490673</v>
+        <v>1879490629</v>
       </c>
       <c r="C34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [33] = {["ID"] = 1879490673; }; -- All the Birds of the Misty Mountains</v>
+        <v xml:space="preserve"> [33] = {["ID"] = 1879490629; }; -- The Rarest Bird in the Trollshaws</v>
       </c>
       <c r="P34" s="1" t="e">
         <f t="shared" si="10"/>
@@ -6647,11 +6764,11 @@
       </c>
       <c r="S34" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490673; </v>
+        <v xml:space="preserve">["ID"] = 1879490629; </v>
       </c>
       <c r="T34" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490673; </v>
+        <v xml:space="preserve">["ID"] = 1879490629; </v>
       </c>
       <c r="U34" t="str">
         <f t="shared" si="15"/>
@@ -6703,11 +6820,11 @@
       </c>
       <c r="AG34" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH34" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Misty Mountains"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Trollshaws"; }; </v>
       </c>
       <c r="AI34" t="str">
         <f t="shared" si="27"/>
@@ -6728,17 +6845,17 @@
     </row>
     <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>1879490650</v>
+        <v>1879490673</v>
       </c>
       <c r="C35" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [34] = {["ID"] = 1879490650; }; -- Birds of the Misty Mountains: Common and Uncommon</v>
+        <v xml:space="preserve"> [34] = {["ID"] = 1879490673; }; -- All the Birds of the Misty Mountains</v>
       </c>
       <c r="P35" s="1" t="e">
         <f t="shared" si="10"/>
@@ -6754,11 +6871,11 @@
       </c>
       <c r="S35" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490650; </v>
+        <v xml:space="preserve">["ID"] = 1879490673; </v>
       </c>
       <c r="T35" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490650; </v>
+        <v xml:space="preserve">["ID"] = 1879490673; </v>
       </c>
       <c r="U35" t="str">
         <f t="shared" si="15"/>
@@ -6810,11 +6927,11 @@
       </c>
       <c r="AG35" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH35" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Misty Mountains: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Misty Mountains"; }; </v>
       </c>
       <c r="AI35" t="str">
         <f t="shared" si="27"/>
@@ -6835,17 +6952,17 @@
     </row>
     <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>1879490620</v>
+        <v>1879490650</v>
       </c>
       <c r="C36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L36">
         <v>1</v>
       </c>
       <c r="O36" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [35] = {["ID"] = 1879490620; }; -- Birds of the Misty Mountains: Rare</v>
+        <v xml:space="preserve"> [35] = {["ID"] = 1879490650; }; -- Birds of the Misty Mountains: Common and Uncommon</v>
       </c>
       <c r="P36" s="1" t="e">
         <f t="shared" si="10"/>
@@ -6861,11 +6978,11 @@
       </c>
       <c r="S36" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490620; </v>
+        <v xml:space="preserve">["ID"] = 1879490650; </v>
       </c>
       <c r="T36" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490620; </v>
+        <v xml:space="preserve">["ID"] = 1879490650; </v>
       </c>
       <c r="U36" t="str">
         <f t="shared" si="15"/>
@@ -6921,7 +7038,7 @@
       </c>
       <c r="AH36" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Misty Mountains: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Misty Mountains: Common and Uncommon"; }; </v>
       </c>
       <c r="AI36" t="str">
         <f t="shared" si="27"/>
@@ -6942,17 +7059,17 @@
     </row>
     <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>1879490612</v>
+        <v>1879490620</v>
       </c>
       <c r="C37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L37">
         <v>1</v>
       </c>
       <c r="O37" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [36] = {["ID"] = 1879490612; }; -- The Rarest Bird in the Misty Mountains</v>
+        <v xml:space="preserve"> [36] = {["ID"] = 1879490620; }; -- Birds of the Misty Mountains: Rare</v>
       </c>
       <c r="P37" s="1" t="e">
         <f t="shared" si="10"/>
@@ -6968,11 +7085,11 @@
       </c>
       <c r="S37" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490612; </v>
+        <v xml:space="preserve">["ID"] = 1879490620; </v>
       </c>
       <c r="T37" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490612; </v>
+        <v xml:space="preserve">["ID"] = 1879490620; </v>
       </c>
       <c r="U37" t="str">
         <f t="shared" si="15"/>
@@ -7028,7 +7145,7 @@
       </c>
       <c r="AH37" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Misty Mountains"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Misty Mountains: Rare"; }; </v>
       </c>
       <c r="AI37" t="str">
         <f t="shared" si="27"/>
@@ -7049,17 +7166,17 @@
     </row>
     <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>1879490674</v>
+        <v>1879490612</v>
       </c>
       <c r="C38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [37] = {["ID"] = 1879490674; }; -- All the Birds of Evendim</v>
+        <v xml:space="preserve"> [37] = {["ID"] = 1879490612; }; -- The Rarest Bird in the Misty Mountains</v>
       </c>
       <c r="P38" s="1" t="e">
         <f t="shared" si="10"/>
@@ -7075,11 +7192,11 @@
       </c>
       <c r="S38" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490674; </v>
+        <v xml:space="preserve">["ID"] = 1879490612; </v>
       </c>
       <c r="T38" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490674; </v>
+        <v xml:space="preserve">["ID"] = 1879490612; </v>
       </c>
       <c r="U38" t="str">
         <f t="shared" si="15"/>
@@ -7131,11 +7248,11 @@
       </c>
       <c r="AG38" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH38" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Evendim"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Misty Mountains"; }; </v>
       </c>
       <c r="AI38" t="str">
         <f t="shared" si="27"/>
@@ -7156,17 +7273,17 @@
     </row>
     <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>1879490643</v>
+        <v>1879490674</v>
       </c>
       <c r="C39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [38] = {["ID"] = 1879490643; }; -- Birds of Evendim: Common and Uncommon</v>
+        <v xml:space="preserve"> [38] = {["ID"] = 1879490674; }; -- All the Birds of Evendim</v>
       </c>
       <c r="P39" s="1" t="e">
         <f t="shared" si="10"/>
@@ -7182,11 +7299,11 @@
       </c>
       <c r="S39" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490643; </v>
+        <v xml:space="preserve">["ID"] = 1879490674; </v>
       </c>
       <c r="T39" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490643; </v>
+        <v xml:space="preserve">["ID"] = 1879490674; </v>
       </c>
       <c r="U39" t="str">
         <f t="shared" si="15"/>
@@ -7238,11 +7355,11 @@
       </c>
       <c r="AG39" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH39" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Evendim: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Evendim"; }; </v>
       </c>
       <c r="AI39" t="str">
         <f t="shared" si="27"/>
@@ -7263,17 +7380,17 @@
     </row>
     <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>1879490638</v>
+        <v>1879490643</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L40">
         <v>1</v>
       </c>
       <c r="O40" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [39] = {["ID"] = 1879490638; }; -- Birds of Evendim: Rare</v>
+        <v xml:space="preserve"> [39] = {["ID"] = 1879490643; }; -- Birds of Evendim: Common and Uncommon</v>
       </c>
       <c r="P40" s="1" t="e">
         <f t="shared" si="10"/>
@@ -7289,11 +7406,11 @@
       </c>
       <c r="S40" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490638; </v>
+        <v xml:space="preserve">["ID"] = 1879490643; </v>
       </c>
       <c r="T40" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490638; </v>
+        <v xml:space="preserve">["ID"] = 1879490643; </v>
       </c>
       <c r="U40" t="str">
         <f t="shared" si="15"/>
@@ -7349,7 +7466,7 @@
       </c>
       <c r="AH40" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Evendim: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Evendim: Common and Uncommon"; }; </v>
       </c>
       <c r="AI40" t="str">
         <f t="shared" si="27"/>
@@ -7370,17 +7487,17 @@
     </row>
     <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>1879490615</v>
+        <v>1879490638</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L41">
         <v>1</v>
       </c>
       <c r="O41" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [40] = {["ID"] = 1879490615; }; -- The Rarest Bird in Evendim</v>
+        <v xml:space="preserve"> [40] = {["ID"] = 1879490638; }; -- Birds of Evendim: Rare</v>
       </c>
       <c r="P41" s="1" t="e">
         <f t="shared" si="10"/>
@@ -7396,11 +7513,11 @@
       </c>
       <c r="S41" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490615; </v>
+        <v xml:space="preserve">["ID"] = 1879490638; </v>
       </c>
       <c r="T41" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490615; </v>
+        <v xml:space="preserve">["ID"] = 1879490638; </v>
       </c>
       <c r="U41" t="str">
         <f t="shared" si="15"/>
@@ -7456,7 +7573,7 @@
       </c>
       <c r="AH41" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Evendim"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Evendim: Rare"; }; </v>
       </c>
       <c r="AI41" t="str">
         <f t="shared" si="27"/>
@@ -7477,17 +7594,17 @@
     </row>
     <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>1879490664</v>
+        <v>1879490615</v>
       </c>
       <c r="C42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [41] = {["ID"] = 1879490664; }; -- All the Birds of Angmar</v>
+        <v xml:space="preserve"> [41] = {["ID"] = 1879490615; }; -- The Rarest Bird in Evendim</v>
       </c>
       <c r="P42" s="1" t="e">
         <f t="shared" si="10"/>
@@ -7503,11 +7620,11 @@
       </c>
       <c r="S42" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490664; </v>
+        <v xml:space="preserve">["ID"] = 1879490615; </v>
       </c>
       <c r="T42" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490664; </v>
+        <v xml:space="preserve">["ID"] = 1879490615; </v>
       </c>
       <c r="U42" t="str">
         <f t="shared" si="15"/>
@@ -7559,11 +7676,11 @@
       </c>
       <c r="AG42" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH42" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Angmar"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Evendim"; }; </v>
       </c>
       <c r="AI42" t="str">
         <f t="shared" si="27"/>
@@ -7584,17 +7701,17 @@
     </row>
     <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>1879490646</v>
+        <v>1879490664</v>
       </c>
       <c r="C43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [42] = {["ID"] = 1879490646; }; -- Birds of Angmar: Common and Uncommon</v>
+        <v xml:space="preserve"> [42] = {["ID"] = 1879490664; }; -- All the Birds of Angmar</v>
       </c>
       <c r="P43" s="1" t="e">
         <f t="shared" si="10"/>
@@ -7610,11 +7727,11 @@
       </c>
       <c r="S43" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490646; </v>
+        <v xml:space="preserve">["ID"] = 1879490664; </v>
       </c>
       <c r="T43" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490646; </v>
+        <v xml:space="preserve">["ID"] = 1879490664; </v>
       </c>
       <c r="U43" t="str">
         <f t="shared" si="15"/>
@@ -7666,11 +7783,11 @@
       </c>
       <c r="AG43" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH43" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Angmar: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Angmar"; }; </v>
       </c>
       <c r="AI43" t="str">
         <f t="shared" si="27"/>
@@ -7691,17 +7808,17 @@
     </row>
     <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>1879490636</v>
+        <v>1879490646</v>
       </c>
       <c r="C44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L44">
         <v>1</v>
       </c>
       <c r="O44" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [43] = {["ID"] = 1879490636; }; -- Birds of Angmar: Rare</v>
+        <v xml:space="preserve"> [43] = {["ID"] = 1879490646; }; -- Birds of Angmar: Common and Uncommon</v>
       </c>
       <c r="P44" s="1" t="e">
         <f t="shared" si="10"/>
@@ -7717,11 +7834,11 @@
       </c>
       <c r="S44" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490636; </v>
+        <v xml:space="preserve">["ID"] = 1879490646; </v>
       </c>
       <c r="T44" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490636; </v>
+        <v xml:space="preserve">["ID"] = 1879490646; </v>
       </c>
       <c r="U44" t="str">
         <f t="shared" si="15"/>
@@ -7777,7 +7894,7 @@
       </c>
       <c r="AH44" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Angmar: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Angmar: Common and Uncommon"; }; </v>
       </c>
       <c r="AI44" t="str">
         <f t="shared" si="27"/>
@@ -7798,17 +7915,17 @@
     </row>
     <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>1879490648</v>
+        <v>1879490636</v>
       </c>
       <c r="C45" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L45">
         <v>1</v>
       </c>
       <c r="O45" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [44] = {["ID"] = 1879490648; }; -- The Rarest Bird in Angmar</v>
+        <v xml:space="preserve"> [44] = {["ID"] = 1879490636; }; -- Birds of Angmar: Rare</v>
       </c>
       <c r="P45" s="1" t="e">
         <f t="shared" si="10"/>
@@ -7824,11 +7941,11 @@
       </c>
       <c r="S45" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490648; </v>
+        <v xml:space="preserve">["ID"] = 1879490636; </v>
       </c>
       <c r="T45" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490648; </v>
+        <v xml:space="preserve">["ID"] = 1879490636; </v>
       </c>
       <c r="U45" t="str">
         <f t="shared" si="15"/>
@@ -7884,7 +8001,7 @@
       </c>
       <c r="AH45" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Angmar"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Angmar: Rare"; }; </v>
       </c>
       <c r="AI45" t="str">
         <f t="shared" si="27"/>
@@ -7905,17 +8022,17 @@
     </row>
     <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>1879490680</v>
+        <v>1879490648</v>
       </c>
       <c r="C46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [45] = {["ID"] = 1879490680; }; -- All the Birds of Forochel</v>
+        <v xml:space="preserve"> [45] = {["ID"] = 1879490648; }; -- The Rarest Bird in Angmar</v>
       </c>
       <c r="P46" s="1" t="e">
         <f t="shared" si="10"/>
@@ -7931,11 +8048,11 @@
       </c>
       <c r="S46" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490680; </v>
+        <v xml:space="preserve">["ID"] = 1879490648; </v>
       </c>
       <c r="T46" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490680; </v>
+        <v xml:space="preserve">["ID"] = 1879490648; </v>
       </c>
       <c r="U46" t="str">
         <f t="shared" si="15"/>
@@ -7987,11 +8104,11 @@
       </c>
       <c r="AG46" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH46" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Forochel"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Angmar"; }; </v>
       </c>
       <c r="AI46" t="str">
         <f t="shared" si="27"/>
@@ -8012,17 +8129,17 @@
     </row>
     <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>1879490613</v>
+        <v>1879490680</v>
       </c>
       <c r="C47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [46] = {["ID"] = 1879490613; }; -- Birds of Forochel: Common and Uncommon</v>
+        <v xml:space="preserve"> [46] = {["ID"] = 1879490680; }; -- All the Birds of Forochel</v>
       </c>
       <c r="P47" s="1" t="e">
         <f t="shared" si="10"/>
@@ -8038,11 +8155,11 @@
       </c>
       <c r="S47" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490613; </v>
+        <v xml:space="preserve">["ID"] = 1879490680; </v>
       </c>
       <c r="T47" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490613; </v>
+        <v xml:space="preserve">["ID"] = 1879490680; </v>
       </c>
       <c r="U47" t="str">
         <f t="shared" si="15"/>
@@ -8094,11 +8211,11 @@
       </c>
       <c r="AG47" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH47" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Forochel: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Forochel"; }; </v>
       </c>
       <c r="AI47" t="str">
         <f t="shared" si="27"/>
@@ -8119,17 +8236,17 @@
     </row>
     <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>1879490624</v>
+        <v>1879490613</v>
       </c>
       <c r="C48" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L48">
         <v>1</v>
       </c>
       <c r="O48" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [47] = {["ID"] = 1879490624; }; -- Birds of Forochel: Rare</v>
+        <v xml:space="preserve"> [47] = {["ID"] = 1879490613; }; -- Birds of Forochel: Common and Uncommon</v>
       </c>
       <c r="P48" s="1" t="e">
         <f t="shared" si="10"/>
@@ -8145,11 +8262,11 @@
       </c>
       <c r="S48" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490624; </v>
+        <v xml:space="preserve">["ID"] = 1879490613; </v>
       </c>
       <c r="T48" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490624; </v>
+        <v xml:space="preserve">["ID"] = 1879490613; </v>
       </c>
       <c r="U48" t="str">
         <f t="shared" si="15"/>
@@ -8205,7 +8322,7 @@
       </c>
       <c r="AH48" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Forochel: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Forochel: Common and Uncommon"; }; </v>
       </c>
       <c r="AI48" t="str">
         <f t="shared" si="27"/>
@@ -8226,17 +8343,17 @@
     </row>
     <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>1879490618</v>
+        <v>1879490624</v>
       </c>
       <c r="C49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L49">
         <v>1</v>
       </c>
       <c r="O49" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [48] = {["ID"] = 1879490618; }; -- The Rarest Bird in Forochel</v>
+        <v xml:space="preserve"> [48] = {["ID"] = 1879490624; }; -- Birds of Forochel: Rare</v>
       </c>
       <c r="P49" s="1" t="e">
         <f t="shared" si="10"/>
@@ -8252,11 +8369,11 @@
       </c>
       <c r="S49" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490618; </v>
+        <v xml:space="preserve">["ID"] = 1879490624; </v>
       </c>
       <c r="T49" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490618; </v>
+        <v xml:space="preserve">["ID"] = 1879490624; </v>
       </c>
       <c r="U49" t="str">
         <f t="shared" si="15"/>
@@ -8312,7 +8429,7 @@
       </c>
       <c r="AH49" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Forochel"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Forochel: Rare"; }; </v>
       </c>
       <c r="AI49" t="str">
         <f t="shared" si="27"/>
@@ -8333,17 +8450,17 @@
     </row>
     <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>1879490681</v>
+        <v>1879490618</v>
       </c>
       <c r="C50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [49] = {["ID"] = 1879490681; }; -- All the Birds of Eregion</v>
+        <v xml:space="preserve"> [49] = {["ID"] = 1879490618; }; -- The Rarest Bird in Forochel</v>
       </c>
       <c r="P50" s="1" t="e">
         <f t="shared" si="10"/>
@@ -8359,11 +8476,11 @@
       </c>
       <c r="S50" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490681; </v>
+        <v xml:space="preserve">["ID"] = 1879490618; </v>
       </c>
       <c r="T50" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490681; </v>
+        <v xml:space="preserve">["ID"] = 1879490618; </v>
       </c>
       <c r="U50" t="str">
         <f t="shared" si="15"/>
@@ -8415,11 +8532,11 @@
       </c>
       <c r="AG50" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH50" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Eregion"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Forochel"; }; </v>
       </c>
       <c r="AI50" t="str">
         <f t="shared" si="27"/>
@@ -8440,17 +8557,17 @@
     </row>
     <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>1879490631</v>
+        <v>1879490681</v>
       </c>
       <c r="C51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [50] = {["ID"] = 1879490631; }; -- Birds of Eregion: Common and Uncommon</v>
+        <v xml:space="preserve"> [50] = {["ID"] = 1879490681; }; -- All the Birds of Eregion</v>
       </c>
       <c r="P51" s="1" t="e">
         <f t="shared" si="10"/>
@@ -8466,11 +8583,11 @@
       </c>
       <c r="S51" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490631; </v>
+        <v xml:space="preserve">["ID"] = 1879490681; </v>
       </c>
       <c r="T51" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490631; </v>
+        <v xml:space="preserve">["ID"] = 1879490681; </v>
       </c>
       <c r="U51" t="str">
         <f t="shared" si="15"/>
@@ -8522,11 +8639,11 @@
       </c>
       <c r="AG51" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH51" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Eregion: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Eregion"; }; </v>
       </c>
       <c r="AI51" t="str">
         <f t="shared" si="27"/>
@@ -8547,17 +8664,17 @@
     </row>
     <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>1879490644</v>
+        <v>1879490631</v>
       </c>
       <c r="C52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L52">
         <v>1</v>
       </c>
       <c r="O52" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [51] = {["ID"] = 1879490644; }; -- Birds of Eregion: Rare</v>
+        <v xml:space="preserve"> [51] = {["ID"] = 1879490631; }; -- Birds of Eregion: Common and Uncommon</v>
       </c>
       <c r="P52" s="1" t="e">
         <f t="shared" si="10"/>
@@ -8573,11 +8690,11 @@
       </c>
       <c r="S52" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490644; </v>
+        <v xml:space="preserve">["ID"] = 1879490631; </v>
       </c>
       <c r="T52" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490644; </v>
+        <v xml:space="preserve">["ID"] = 1879490631; </v>
       </c>
       <c r="U52" t="str">
         <f t="shared" si="15"/>
@@ -8633,7 +8750,7 @@
       </c>
       <c r="AH52" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Eregion: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Eregion: Common and Uncommon"; }; </v>
       </c>
       <c r="AI52" t="str">
         <f t="shared" si="27"/>
@@ -8654,17 +8771,17 @@
     </row>
     <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>1879490628</v>
+        <v>1879490644</v>
       </c>
       <c r="C53" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L53">
         <v>1</v>
       </c>
       <c r="O53" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [52] = {["ID"] = 1879490628; }; -- The Rarest Bird in Eregion</v>
+        <v xml:space="preserve"> [52] = {["ID"] = 1879490644; }; -- Birds of Eregion: Rare</v>
       </c>
       <c r="P53" s="1" t="e">
         <f t="shared" si="10"/>
@@ -8680,11 +8797,11 @@
       </c>
       <c r="S53" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490628; </v>
+        <v xml:space="preserve">["ID"] = 1879490644; </v>
       </c>
       <c r="T53" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490628; </v>
+        <v xml:space="preserve">["ID"] = 1879490644; </v>
       </c>
       <c r="U53" t="str">
         <f t="shared" si="15"/>
@@ -8740,7 +8857,7 @@
       </c>
       <c r="AH53" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Eregion"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Eregion: Rare"; }; </v>
       </c>
       <c r="AI53" t="str">
         <f t="shared" si="27"/>
@@ -8761,17 +8878,17 @@
     </row>
     <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>1879490669</v>
+        <v>1879490628</v>
       </c>
       <c r="C54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [53] = {["ID"] = 1879490669; }; -- All the Birds of Enedwaith</v>
+        <v xml:space="preserve"> [53] = {["ID"] = 1879490628; }; -- The Rarest Bird in Eregion</v>
       </c>
       <c r="P54" s="1" t="e">
         <f t="shared" si="10"/>
@@ -8787,11 +8904,11 @@
       </c>
       <c r="S54" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490669; </v>
+        <v xml:space="preserve">["ID"] = 1879490628; </v>
       </c>
       <c r="T54" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490669; </v>
+        <v xml:space="preserve">["ID"] = 1879490628; </v>
       </c>
       <c r="U54" t="str">
         <f t="shared" si="15"/>
@@ -8843,11 +8960,11 @@
       </c>
       <c r="AG54" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH54" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Enedwaith"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Eregion"; }; </v>
       </c>
       <c r="AI54" t="str">
         <f t="shared" si="27"/>
@@ -8868,17 +8985,17 @@
     </row>
     <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>1879490616</v>
+        <v>1879490669</v>
       </c>
       <c r="C55" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [54] = {["ID"] = 1879490616; }; -- Birds of Enedwaith: Common and Uncommon</v>
+        <v xml:space="preserve"> [54] = {["ID"] = 1879490669; }; -- All the Birds of Enedwaith</v>
       </c>
       <c r="P55" s="1" t="e">
         <f t="shared" si="10"/>
@@ -8894,11 +9011,11 @@
       </c>
       <c r="S55" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490616; </v>
+        <v xml:space="preserve">["ID"] = 1879490669; </v>
       </c>
       <c r="T55" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490616; </v>
+        <v xml:space="preserve">["ID"] = 1879490669; </v>
       </c>
       <c r="U55" t="str">
         <f t="shared" si="15"/>
@@ -8950,11 +9067,11 @@
       </c>
       <c r="AG55" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH55" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Enedwaith: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Enedwaith"; }; </v>
       </c>
       <c r="AI55" t="str">
         <f t="shared" si="27"/>
@@ -8975,17 +9092,17 @@
     </row>
     <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>1879490652</v>
+        <v>1879490616</v>
       </c>
       <c r="C56" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L56">
         <v>1</v>
       </c>
       <c r="O56" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [55] = {["ID"] = 1879490652; }; -- Birds of Enedwaith: Rare</v>
+        <v xml:space="preserve"> [55] = {["ID"] = 1879490616; }; -- Birds of Enedwaith: Common and Uncommon</v>
       </c>
       <c r="P56" s="1" t="e">
         <f t="shared" si="10"/>
@@ -9001,11 +9118,11 @@
       </c>
       <c r="S56" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490652; </v>
+        <v xml:space="preserve">["ID"] = 1879490616; </v>
       </c>
       <c r="T56" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490652; </v>
+        <v xml:space="preserve">["ID"] = 1879490616; </v>
       </c>
       <c r="U56" t="str">
         <f t="shared" si="15"/>
@@ -9061,7 +9178,7 @@
       </c>
       <c r="AH56" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Enedwaith: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Enedwaith: Common and Uncommon"; }; </v>
       </c>
       <c r="AI56" t="str">
         <f t="shared" si="27"/>
@@ -9082,17 +9199,17 @@
     </row>
     <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>1879490653</v>
+        <v>1879490652</v>
       </c>
       <c r="C57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L57">
         <v>1</v>
       </c>
       <c r="O57" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [56] = {["ID"] = 1879490653; }; -- The Rarest Bird in Enedwaith</v>
+        <v xml:space="preserve"> [56] = {["ID"] = 1879490652; }; -- Birds of Enedwaith: Rare</v>
       </c>
       <c r="P57" s="1" t="e">
         <f t="shared" si="10"/>
@@ -9108,11 +9225,11 @@
       </c>
       <c r="S57" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490653; </v>
+        <v xml:space="preserve">["ID"] = 1879490652; </v>
       </c>
       <c r="T57" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490653; </v>
+        <v xml:space="preserve">["ID"] = 1879490652; </v>
       </c>
       <c r="U57" t="str">
         <f t="shared" si="15"/>
@@ -9168,7 +9285,7 @@
       </c>
       <c r="AH57" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Enedwaith"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Enedwaith: Rare"; }; </v>
       </c>
       <c r="AI57" t="str">
         <f t="shared" si="27"/>
@@ -9189,17 +9306,17 @@
     </row>
     <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>1879490672</v>
+        <v>1879490653</v>
       </c>
       <c r="C58" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [57] = {["ID"] = 1879490672; }; -- All the Birds of Dunland</v>
+        <v xml:space="preserve"> [57] = {["ID"] = 1879490653; }; -- The Rarest Bird in Enedwaith</v>
       </c>
       <c r="P58" s="1" t="e">
         <f t="shared" si="10"/>
@@ -9215,11 +9332,11 @@
       </c>
       <c r="S58" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490672; </v>
+        <v xml:space="preserve">["ID"] = 1879490653; </v>
       </c>
       <c r="T58" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490672; </v>
+        <v xml:space="preserve">["ID"] = 1879490653; </v>
       </c>
       <c r="U58" t="str">
         <f t="shared" si="15"/>
@@ -9271,11 +9388,11 @@
       </c>
       <c r="AG58" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH58" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Dunland"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Enedwaith"; }; </v>
       </c>
       <c r="AI58" t="str">
         <f t="shared" si="27"/>
@@ -9296,17 +9413,17 @@
     </row>
     <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>1879490623</v>
+        <v>1879490672</v>
       </c>
       <c r="C59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [58] = {["ID"] = 1879490623; }; -- Birds of Dunland: Common and Uncommon</v>
+        <v xml:space="preserve"> [58] = {["ID"] = 1879490672; }; -- All the Birds of Dunland</v>
       </c>
       <c r="P59" s="1" t="e">
         <f t="shared" si="10"/>
@@ -9322,11 +9439,11 @@
       </c>
       <c r="S59" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490623; </v>
+        <v xml:space="preserve">["ID"] = 1879490672; </v>
       </c>
       <c r="T59" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490623; </v>
+        <v xml:space="preserve">["ID"] = 1879490672; </v>
       </c>
       <c r="U59" t="str">
         <f t="shared" si="15"/>
@@ -9378,11 +9495,11 @@
       </c>
       <c r="AG59" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
+        <v xml:space="preserve">["TIER"] = 0; </v>
       </c>
       <c r="AH59" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Dunland: Common and Uncommon"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Dunland"; }; </v>
       </c>
       <c r="AI59" t="str">
         <f t="shared" si="27"/>
@@ -9403,17 +9520,17 @@
     </row>
     <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>1879490634</v>
+        <v>1879490623</v>
       </c>
       <c r="C60" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L60">
         <v>1</v>
       </c>
       <c r="O60" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [59] = {["ID"] = 1879490634; }; -- Birds of Dunland: Rare</v>
+        <v xml:space="preserve"> [59] = {["ID"] = 1879490623; }; -- Birds of Dunland: Common and Uncommon</v>
       </c>
       <c r="P60" s="1" t="e">
         <f t="shared" si="10"/>
@@ -9429,11 +9546,11 @@
       </c>
       <c r="S60" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490634; </v>
+        <v xml:space="preserve">["ID"] = 1879490623; </v>
       </c>
       <c r="T60" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490634; </v>
+        <v xml:space="preserve">["ID"] = 1879490623; </v>
       </c>
       <c r="U60" t="str">
         <f t="shared" si="15"/>
@@ -9489,7 +9606,7 @@
       </c>
       <c r="AH60" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Dunland: Rare"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Dunland: Common and Uncommon"; }; </v>
       </c>
       <c r="AI60" t="str">
         <f t="shared" si="27"/>
@@ -9510,17 +9627,17 @@
     </row>
     <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>1879490619</v>
+        <v>1879490634</v>
       </c>
       <c r="C61" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L61">
         <v>1</v>
       </c>
       <c r="O61" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [60] = {["ID"] = 1879490619; }; -- The Rarest Bird in Dunland</v>
+        <v xml:space="preserve"> [60] = {["ID"] = 1879490634; }; -- Birds of Dunland: Rare</v>
       </c>
       <c r="P61" s="1" t="e">
         <f t="shared" si="10"/>
@@ -9536,11 +9653,11 @@
       </c>
       <c r="S61" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490619; </v>
+        <v xml:space="preserve">["ID"] = 1879490634; </v>
       </c>
       <c r="T61" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490619; </v>
+        <v xml:space="preserve">["ID"] = 1879490634; </v>
       </c>
       <c r="U61" t="str">
         <f t="shared" si="15"/>
@@ -9596,7 +9713,7 @@
       </c>
       <c r="AH61" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Dunland"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Dunland: Rare"; }; </v>
       </c>
       <c r="AI61" t="str">
         <f t="shared" si="27"/>
@@ -9617,17 +9734,17 @@
     </row>
     <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>1879490679</v>
+        <v>1879490619</v>
       </c>
       <c r="C62" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [61] = {["ID"] = 1879490679; }; -- The Rarest of Birds in Eriador</v>
+        <v xml:space="preserve"> [61] = {["ID"] = 1879490619; }; -- The Rarest Bird in Dunland</v>
       </c>
       <c r="P62" s="1" t="e">
         <f t="shared" si="10"/>
@@ -9643,11 +9760,11 @@
       </c>
       <c r="S62" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">["ID"] = 1879490679; </v>
+        <v xml:space="preserve">["ID"] = 1879490619; </v>
       </c>
       <c r="T62" t="str">
         <f t="shared" si="14"/>
-        <v xml:space="preserve">["ID"] = 1879490679; </v>
+        <v xml:space="preserve">["ID"] = 1879490619; </v>
       </c>
       <c r="U62" t="str">
         <f t="shared" si="15"/>
@@ -9699,11 +9816,11 @@
       </c>
       <c r="AG62" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH62" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest of Birds in Eriador"; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Dunland"; }; </v>
       </c>
       <c r="AI62" t="str">
         <f t="shared" si="27"/>
@@ -9723,9 +9840,18 @@
       </c>
     </row>
     <row r="63" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1879490679</v>
+      </c>
+      <c r="C63" t="s">
+        <v>230</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
       <c r="O63" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [62] = {}; -- </v>
+        <v xml:space="preserve"> [62] = {["ID"] = 1879490679; }; -- The Rarest of Birds in Eriador</v>
       </c>
       <c r="P63" s="1" t="e">
         <f t="shared" si="10"/>
@@ -9741,11 +9867,11 @@
       </c>
       <c r="S63" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">                     </v>
+        <v xml:space="preserve">["ID"] = 1879490679; </v>
       </c>
       <c r="T63" t="str">
         <f t="shared" si="14"/>
-        <v/>
+        <v xml:space="preserve">["ID"] = 1879490679; </v>
       </c>
       <c r="U63" t="str">
         <f t="shared" si="15"/>
@@ -9801,7 +9927,7 @@
       </c>
       <c r="AH63" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest of Birds in Eriador"; }; </v>
       </c>
       <c r="AI63" t="str">
         <f t="shared" si="27"/>
@@ -9821,9 +9947,18 @@
       </c>
     </row>
     <row r="64" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="C64" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D64" t="s">
+        <v>138</v>
+      </c>
+      <c r="M64">
+        <v>321</v>
+      </c>
       <c r="O64" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [63] = {}; -- </v>
+        <v xml:space="preserve"> [63] = {["CAT_ID"] = 321; }; -- Rohan and the Great River</v>
       </c>
       <c r="P64" s="1" t="e">
         <f t="shared" si="10"/>
@@ -9847,19 +9982,19 @@
       </c>
       <c r="U64" t="str">
         <f t="shared" si="15"/>
-        <v/>
+        <v xml:space="preserve">["CAT_ID"] = 321; </v>
       </c>
       <c r="V64" s="1" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="W64" t="e">
+      <c r="W64">
         <f>VLOOKUP(D64,Type!A$2:B$17,2,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="X64" t="e">
+        <v>14</v>
+      </c>
+      <c r="X64" t="str">
         <f t="shared" si="17"/>
-        <v>#N/A</v>
+        <v xml:space="preserve">["TYPE"] = 14; </v>
       </c>
       <c r="Y64" t="str">
         <f t="shared" si="18"/>
@@ -9899,7 +10034,7 @@
       </c>
       <c r="AH64" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Rohan and the Great River"; }; </v>
       </c>
       <c r="AI64" t="str">
         <f t="shared" si="27"/>
@@ -9918,10 +10053,19 @@
         <v>};</v>
       </c>
     </row>
-    <row r="65" spans="15:38" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>1879501132</v>
+      </c>
+      <c r="C65" t="s">
+        <v>231</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
       <c r="O65" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [64] = {}; -- </v>
+        <v xml:space="preserve"> [64] = {["ID"] = 1879501132; }; -- All the Birds of Lothlórien</v>
       </c>
       <c r="P65" s="1" t="e">
         <f t="shared" si="10"/>
@@ -9937,11 +10081,11 @@
       </c>
       <c r="S65" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">                     </v>
+        <v xml:space="preserve">["ID"] = 1879501132; </v>
       </c>
       <c r="T65" t="str">
         <f t="shared" si="14"/>
-        <v/>
+        <v xml:space="preserve">["ID"] = 1879501132; </v>
       </c>
       <c r="U65" t="str">
         <f t="shared" si="15"/>
@@ -9997,7 +10141,7 @@
       </c>
       <c r="AH65" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Lothlórien"; }; </v>
       </c>
       <c r="AI65" t="str">
         <f t="shared" si="27"/>
@@ -10016,10 +10160,19 @@
         <v>};</v>
       </c>
     </row>
-    <row r="66" spans="15:38" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1879501133</v>
+      </c>
+      <c r="C66" t="s">
+        <v>232</v>
+      </c>
+      <c r="L66">
+        <v>1</v>
+      </c>
       <c r="O66" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve"> [65] = {}; -- </v>
+        <v xml:space="preserve"> [65] = {["ID"] = 1879501133; }; -- Birds of Lothlórien: Common and Uncommon</v>
       </c>
       <c r="P66" s="1" t="e">
         <f t="shared" si="10"/>
@@ -10035,11 +10188,11 @@
       </c>
       <c r="S66" t="str">
         <f t="shared" si="13"/>
-        <v xml:space="preserve">                     </v>
+        <v xml:space="preserve">["ID"] = 1879501133; </v>
       </c>
       <c r="T66" t="str">
         <f t="shared" si="14"/>
-        <v/>
+        <v xml:space="preserve">["ID"] = 1879501133; </v>
       </c>
       <c r="U66" t="str">
         <f t="shared" si="15"/>
@@ -10091,11 +10244,11 @@
       </c>
       <c r="AG66" t="str">
         <f t="shared" si="25"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AH66" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lothlórien: Common and Uncommon"; }; </v>
       </c>
       <c r="AI66" t="str">
         <f t="shared" si="27"/>
@@ -10114,8 +10267,3753 @@
         <v>};</v>
       </c>
     </row>
+    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1879501131</v>
+      </c>
+      <c r="C67" t="s">
+        <v>233</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="O67" t="str">
+        <f t="shared" ref="O67:O101" si="31">CONCATENATE(R67,T67,U67,AL67," -- ",C67)</f>
+        <v xml:space="preserve"> [66] = {["ID"] = 1879501131; }; -- Birds of Lothlórien: Rare</v>
+      </c>
+      <c r="P67" s="1" t="e">
+        <f t="shared" ref="P67:P101" si="32">CONCATENATE(R67,S67,V67,X67,Z67,AB67,AD67,AF67,AG67,AH67,AI67,AJ67,AK67,AL67)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q67">
+        <f t="shared" ref="Q67:Q101" si="33">ROW()-1</f>
+        <v>66</v>
+      </c>
+      <c r="R67" t="str">
+        <f t="shared" ref="R67:R101" si="34">CONCATENATE(REPT(" ",3-LEN(Q67)),"[",Q67,"] = {")</f>
+        <v xml:space="preserve"> [66] = {</v>
+      </c>
+      <c r="S67" t="str">
+        <f t="shared" ref="S67:S101" si="35">IF(LEN(A67)&gt;0,CONCATENATE("[""ID""] = ",A67,"; "),"                     ")</f>
+        <v xml:space="preserve">["ID"] = 1879501131; </v>
+      </c>
+      <c r="T67" t="str">
+        <f t="shared" ref="T67:T101" si="36">IF(LEN(A67)&gt;0,CONCATENATE("[""ID""] = ",A67,"; "),"")</f>
+        <v xml:space="preserve">["ID"] = 1879501131; </v>
+      </c>
+      <c r="U67" t="str">
+        <f t="shared" ref="U67:U101" si="37">IF(LEN(M67)&gt;0,CONCATENATE("[""CAT_ID""] = ",M67,"; "),"")</f>
+        <v/>
+      </c>
+      <c r="V67" s="1" t="str">
+        <f t="shared" ref="V67:V101" si="38">IF(LEN(B67)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B67)),B67,"; "),"")</f>
+        <v/>
+      </c>
+      <c r="W67" t="e">
+        <f>VLOOKUP(D67,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X67" t="e">
+        <f t="shared" ref="X67:X101" si="39">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(W67)),W67,"; ")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y67" t="str">
+        <f t="shared" ref="Y67:Y101" si="40">TEXT(E67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z67" t="str">
+        <f t="shared" ref="Z67:Z101" si="41">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(Y67)),TEXT(Y67,"0"),"; ")</f>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA67" t="str">
+        <f t="shared" ref="AA67:AA101" si="42">TEXT(G67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB67" t="str">
+        <f t="shared" ref="AB67:AB101" si="43">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AA67)),TEXT(AA67,"0"),"; ")</f>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC67" t="str">
+        <f t="shared" ref="AC67:AC101" si="44">TEXT(H67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD67" t="str">
+        <f t="shared" ref="AD67:AD101" si="45">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AC67)),TEXT(AC67,"0"),"; ")</f>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE67" t="e">
+        <f>VLOOKUP(I67,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF67" t="e">
+        <f t="shared" ref="AF67:AF101" si="46">CONCATENATE("[""FACTION""] = ",TEXT(AE67,"0"),"; ")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG67" t="str">
+        <f t="shared" ref="AG67:AG101" si="47">CONCATENATE("[""TIER""] = ",TEXT(L67,"0"),"; ")</f>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH67" t="str">
+        <f t="shared" ref="AH67:AH101" si="48">CONCATENATE("[""NAME""] = { [""EN""] = """,C67,"""; }; ")</f>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lothlórien: Rare"; }; </v>
+      </c>
+      <c r="AI67" t="str">
+        <f t="shared" ref="AI67:AI101" si="49">CONCATENATE("[""LORE""] = { [""EN""] = """,K67,"""; }; ")</f>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ67" t="str">
+        <f t="shared" ref="AJ67:AJ101" si="50">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,J67,"""; }; ")</f>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK67" t="str">
+        <f t="shared" ref="AK67:AK101" si="51">IF(LEN(F67)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,F67,"""; }; "),"")</f>
+        <v/>
+      </c>
+      <c r="AL67" t="str">
+        <f t="shared" ref="AL67:AL101" si="52">CONCATENATE("};")</f>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1879501134</v>
+      </c>
+      <c r="C68" t="s">
+        <v>234</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="O68" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [67] = {["ID"] = 1879501134; }; -- The Rarest Bird in Lothlórien</v>
+      </c>
+      <c r="P68" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q68">
+        <f t="shared" si="33"/>
+        <v>67</v>
+      </c>
+      <c r="R68" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [67] = {</v>
+      </c>
+      <c r="S68" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501134; </v>
+      </c>
+      <c r="T68" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501134; </v>
+      </c>
+      <c r="U68" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V68" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W68" t="e">
+        <f>VLOOKUP(D68,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X68" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y68" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z68" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA68" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB68" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC68" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD68" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE68" t="e">
+        <f>VLOOKUP(I68,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF68" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG68" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH68" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Lothlórien"; }; </v>
+      </c>
+      <c r="AI68" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ68" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK68" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL68" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1879501164</v>
+      </c>
+      <c r="C69" t="s">
+        <v>235</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="O69" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [68] = {["ID"] = 1879501164; }; -- All the Birds of Mirkwood</v>
+      </c>
+      <c r="P69" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q69">
+        <f t="shared" si="33"/>
+        <v>68</v>
+      </c>
+      <c r="R69" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [68] = {</v>
+      </c>
+      <c r="S69" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501164; </v>
+      </c>
+      <c r="T69" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501164; </v>
+      </c>
+      <c r="U69" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V69" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W69" t="e">
+        <f>VLOOKUP(D69,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X69" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y69" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z69" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA69" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB69" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC69" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD69" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE69" t="e">
+        <f>VLOOKUP(I69,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF69" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG69" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH69" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Mirkwood"; }; </v>
+      </c>
+      <c r="AI69" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ69" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK69" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL69" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1879501162</v>
+      </c>
+      <c r="C70" t="s">
+        <v>236</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="O70" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [69] = {["ID"] = 1879501162; }; -- Birds of Mirkwood: Common and Uncommon</v>
+      </c>
+      <c r="P70" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q70">
+        <f t="shared" si="33"/>
+        <v>69</v>
+      </c>
+      <c r="R70" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [69] = {</v>
+      </c>
+      <c r="S70" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501162; </v>
+      </c>
+      <c r="T70" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501162; </v>
+      </c>
+      <c r="U70" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V70" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W70" t="e">
+        <f>VLOOKUP(D70,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X70" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y70" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z70" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA70" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB70" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC70" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD70" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE70" t="e">
+        <f>VLOOKUP(I70,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF70" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG70" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH70" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Mirkwood: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI70" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ70" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK70" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL70" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>1879501161</v>
+      </c>
+      <c r="C71" t="s">
+        <v>237</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="O71" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [70] = {["ID"] = 1879501161; }; -- Birds of Mirkwood: Rare</v>
+      </c>
+      <c r="P71" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q71">
+        <f t="shared" si="33"/>
+        <v>70</v>
+      </c>
+      <c r="R71" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [70] = {</v>
+      </c>
+      <c r="S71" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501161; </v>
+      </c>
+      <c r="T71" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501161; </v>
+      </c>
+      <c r="U71" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V71" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W71" t="e">
+        <f>VLOOKUP(D71,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X71" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y71" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z71" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA71" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB71" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC71" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD71" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE71" t="e">
+        <f>VLOOKUP(I71,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF71" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG71" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH71" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Mirkwood: Rare"; }; </v>
+      </c>
+      <c r="AI71" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ71" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK71" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL71" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>1879501163</v>
+      </c>
+      <c r="C72" t="s">
+        <v>238</v>
+      </c>
+      <c r="L72">
+        <v>1</v>
+      </c>
+      <c r="O72" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [71] = {["ID"] = 1879501163; }; -- The Rarest Bird in Mirkwood</v>
+      </c>
+      <c r="P72" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q72">
+        <f t="shared" si="33"/>
+        <v>71</v>
+      </c>
+      <c r="R72" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [71] = {</v>
+      </c>
+      <c r="S72" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501163; </v>
+      </c>
+      <c r="T72" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501163; </v>
+      </c>
+      <c r="U72" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V72" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W72" t="e">
+        <f>VLOOKUP(D72,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X72" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y72" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z72" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA72" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB72" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC72" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD72" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE72" t="e">
+        <f>VLOOKUP(I72,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF72" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG72" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH72" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Mirkwood"; }; </v>
+      </c>
+      <c r="AI72" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ72" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK72" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL72" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1879501166</v>
+      </c>
+      <c r="C73" t="s">
+        <v>239</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="O73" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [72] = {["ID"] = 1879501166; }; -- All the Birds of the Great River</v>
+      </c>
+      <c r="P73" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q73">
+        <f t="shared" si="33"/>
+        <v>72</v>
+      </c>
+      <c r="R73" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [72] = {</v>
+      </c>
+      <c r="S73" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501166; </v>
+      </c>
+      <c r="T73" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501166; </v>
+      </c>
+      <c r="U73" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V73" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W73" t="e">
+        <f>VLOOKUP(D73,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X73" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y73" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z73" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA73" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB73" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC73" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD73" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE73" t="e">
+        <f>VLOOKUP(I73,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF73" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG73" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH73" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Great River"; }; </v>
+      </c>
+      <c r="AI73" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ73" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK73" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL73" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1879501167</v>
+      </c>
+      <c r="C74" t="s">
+        <v>240</v>
+      </c>
+      <c r="L74">
+        <v>1</v>
+      </c>
+      <c r="O74" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [73] = {["ID"] = 1879501167; }; -- Birds of the Great River: Common and Uncommon</v>
+      </c>
+      <c r="P74" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q74">
+        <f t="shared" si="33"/>
+        <v>73</v>
+      </c>
+      <c r="R74" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [73] = {</v>
+      </c>
+      <c r="S74" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501167; </v>
+      </c>
+      <c r="T74" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501167; </v>
+      </c>
+      <c r="U74" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V74" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W74" t="e">
+        <f>VLOOKUP(D74,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X74" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y74" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z74" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA74" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB74" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC74" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD74" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE74" t="e">
+        <f>VLOOKUP(I74,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF74" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG74" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH74" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Great River: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI74" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ74" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK74" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL74" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1879501168</v>
+      </c>
+      <c r="C75" t="s">
+        <v>241</v>
+      </c>
+      <c r="L75">
+        <v>1</v>
+      </c>
+      <c r="O75" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [74] = {["ID"] = 1879501168; }; -- Birds of the Great River: Rare</v>
+      </c>
+      <c r="P75" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q75">
+        <f t="shared" si="33"/>
+        <v>74</v>
+      </c>
+      <c r="R75" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [74] = {</v>
+      </c>
+      <c r="S75" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501168; </v>
+      </c>
+      <c r="T75" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501168; </v>
+      </c>
+      <c r="U75" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V75" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W75" t="e">
+        <f>VLOOKUP(D75,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X75" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y75" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z75" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA75" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB75" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC75" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD75" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE75" t="e">
+        <f>VLOOKUP(I75,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF75" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG75" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH75" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Great River: Rare"; }; </v>
+      </c>
+      <c r="AI75" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ75" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK75" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL75" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1879501165</v>
+      </c>
+      <c r="C76" t="s">
+        <v>242</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="O76" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [75] = {["ID"] = 1879501165; }; -- The Rarest Bird of the Great River</v>
+      </c>
+      <c r="P76" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q76">
+        <f t="shared" si="33"/>
+        <v>75</v>
+      </c>
+      <c r="R76" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [75] = {</v>
+      </c>
+      <c r="S76" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501165; </v>
+      </c>
+      <c r="T76" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501165; </v>
+      </c>
+      <c r="U76" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V76" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W76" t="e">
+        <f>VLOOKUP(D76,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X76" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y76" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z76" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA76" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB76" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC76" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD76" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE76" t="e">
+        <f>VLOOKUP(I76,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF76" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG76" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH76" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird of the Great River"; }; </v>
+      </c>
+      <c r="AI76" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ76" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK76" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL76" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>1879501170</v>
+      </c>
+      <c r="C77" t="s">
+        <v>243</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="O77" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [76] = {["ID"] = 1879501170; }; -- All the Birds of the Wold</v>
+      </c>
+      <c r="P77" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q77">
+        <f t="shared" si="33"/>
+        <v>76</v>
+      </c>
+      <c r="R77" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [76] = {</v>
+      </c>
+      <c r="S77" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501170; </v>
+      </c>
+      <c r="T77" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501170; </v>
+      </c>
+      <c r="U77" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V77" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W77" t="e">
+        <f>VLOOKUP(D77,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X77" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y77" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z77" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA77" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB77" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC77" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD77" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE77" t="e">
+        <f>VLOOKUP(I77,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF77" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG77" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH77" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Wold"; }; </v>
+      </c>
+      <c r="AI77" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ77" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK77" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL77" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1879501171</v>
+      </c>
+      <c r="C78" t="s">
+        <v>244</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="O78" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [77] = {["ID"] = 1879501171; }; -- Birds of the Wold: Common and Uncommon</v>
+      </c>
+      <c r="P78" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q78">
+        <f t="shared" si="33"/>
+        <v>77</v>
+      </c>
+      <c r="R78" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [77] = {</v>
+      </c>
+      <c r="S78" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501171; </v>
+      </c>
+      <c r="T78" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501171; </v>
+      </c>
+      <c r="U78" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V78" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W78" t="e">
+        <f>VLOOKUP(D78,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X78" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y78" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z78" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA78" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB78" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC78" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD78" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE78" t="e">
+        <f>VLOOKUP(I78,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF78" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG78" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH78" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Wold: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI78" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ78" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK78" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL78" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>1879501173</v>
+      </c>
+      <c r="C79" t="s">
+        <v>245</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="O79" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [78] = {["ID"] = 1879501173; }; -- Birds of the Wold: Rare</v>
+      </c>
+      <c r="P79" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q79">
+        <f t="shared" si="33"/>
+        <v>78</v>
+      </c>
+      <c r="R79" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [78] = {</v>
+      </c>
+      <c r="S79" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501173; </v>
+      </c>
+      <c r="T79" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501173; </v>
+      </c>
+      <c r="U79" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V79" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W79" t="e">
+        <f>VLOOKUP(D79,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X79" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y79" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z79" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA79" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB79" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC79" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD79" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE79" t="e">
+        <f>VLOOKUP(I79,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF79" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG79" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH79" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Wold: Rare"; }; </v>
+      </c>
+      <c r="AI79" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ79" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK79" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL79" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>1879501172</v>
+      </c>
+      <c r="C80" t="s">
+        <v>246</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="O80" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [79] = {["ID"] = 1879501172; }; -- The Rarest Bird of the Wold</v>
+      </c>
+      <c r="P80" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q80">
+        <f t="shared" si="33"/>
+        <v>79</v>
+      </c>
+      <c r="R80" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [79] = {</v>
+      </c>
+      <c r="S80" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501172; </v>
+      </c>
+      <c r="T80" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501172; </v>
+      </c>
+      <c r="U80" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V80" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W80" t="e">
+        <f>VLOOKUP(D80,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X80" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y80" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z80" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA80" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB80" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC80" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD80" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE80" t="e">
+        <f>VLOOKUP(I80,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF80" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG80" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH80" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird of the Wold"; }; </v>
+      </c>
+      <c r="AI80" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ80" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK80" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL80" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>1879501174</v>
+      </c>
+      <c r="C81" t="s">
+        <v>247</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="O81" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [80] = {["ID"] = 1879501174; }; -- All the Birds of Fangorn</v>
+      </c>
+      <c r="P81" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q81">
+        <f t="shared" si="33"/>
+        <v>80</v>
+      </c>
+      <c r="R81" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [80] = {</v>
+      </c>
+      <c r="S81" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501174; </v>
+      </c>
+      <c r="T81" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501174; </v>
+      </c>
+      <c r="U81" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V81" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W81" t="e">
+        <f>VLOOKUP(D81,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X81" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y81" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z81" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA81" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB81" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC81" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD81" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE81" t="e">
+        <f>VLOOKUP(I81,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF81" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG81" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH81" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Fangorn"; }; </v>
+      </c>
+      <c r="AI81" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ81" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK81" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL81" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>1879501176</v>
+      </c>
+      <c r="C82" t="s">
+        <v>248</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="O82" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [81] = {["ID"] = 1879501176; }; -- Birds of Fangorn: Common and Uncommon</v>
+      </c>
+      <c r="P82" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q82">
+        <f t="shared" si="33"/>
+        <v>81</v>
+      </c>
+      <c r="R82" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [81] = {</v>
+      </c>
+      <c r="S82" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501176; </v>
+      </c>
+      <c r="T82" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501176; </v>
+      </c>
+      <c r="U82" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V82" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W82" t="e">
+        <f>VLOOKUP(D82,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X82" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y82" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z82" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA82" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB82" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC82" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD82" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE82" t="e">
+        <f>VLOOKUP(I82,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF82" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG82" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH82" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Fangorn: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI82" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ82" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK82" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL82" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1879501175</v>
+      </c>
+      <c r="C83" t="s">
+        <v>249</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="O83" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [82] = {["ID"] = 1879501175; }; -- Birds of Fangorn: Rare</v>
+      </c>
+      <c r="P83" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q83">
+        <f t="shared" si="33"/>
+        <v>82</v>
+      </c>
+      <c r="R83" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [82] = {</v>
+      </c>
+      <c r="S83" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501175; </v>
+      </c>
+      <c r="T83" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501175; </v>
+      </c>
+      <c r="U83" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V83" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W83" t="e">
+        <f>VLOOKUP(D83,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X83" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y83" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z83" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA83" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB83" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC83" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD83" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE83" t="e">
+        <f>VLOOKUP(I83,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF83" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG83" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH83" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Fangorn: Rare"; }; </v>
+      </c>
+      <c r="AI83" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ83" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK83" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL83" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>1879501177</v>
+      </c>
+      <c r="C84" t="s">
+        <v>250</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="O84" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [83] = {["ID"] = 1879501177; }; -- The Rarest Bird in Fangorn</v>
+      </c>
+      <c r="P84" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q84">
+        <f t="shared" si="33"/>
+        <v>83</v>
+      </c>
+      <c r="R84" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [83] = {</v>
+      </c>
+      <c r="S84" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501177; </v>
+      </c>
+      <c r="T84" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501177; </v>
+      </c>
+      <c r="U84" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V84" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W84" t="e">
+        <f>VLOOKUP(D84,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X84" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y84" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z84" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA84" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB84" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC84" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD84" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE84" t="e">
+        <f>VLOOKUP(I84,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF84" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG84" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH84" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Fangorn"; }; </v>
+      </c>
+      <c r="AI84" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ84" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK84" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL84" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>1879501178</v>
+      </c>
+      <c r="C85" t="s">
+        <v>251</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="O85" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [84] = {["ID"] = 1879501178; }; -- All the Birds of the Croftlands</v>
+      </c>
+      <c r="P85" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q85">
+        <f t="shared" si="33"/>
+        <v>84</v>
+      </c>
+      <c r="R85" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [84] = {</v>
+      </c>
+      <c r="S85" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501178; </v>
+      </c>
+      <c r="T85" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501178; </v>
+      </c>
+      <c r="U85" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V85" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W85" t="e">
+        <f>VLOOKUP(D85,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X85" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y85" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z85" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA85" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB85" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC85" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD85" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE85" t="e">
+        <f>VLOOKUP(I85,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF85" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG85" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH85" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Croftlands"; }; </v>
+      </c>
+      <c r="AI85" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ85" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK85" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL85" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>1879501180</v>
+      </c>
+      <c r="C86" t="s">
+        <v>252</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="O86" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [85] = {["ID"] = 1879501180; }; -- Birds of the Croftlands: Common and Uncommon</v>
+      </c>
+      <c r="P86" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q86">
+        <f t="shared" si="33"/>
+        <v>85</v>
+      </c>
+      <c r="R86" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [85] = {</v>
+      </c>
+      <c r="S86" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501180; </v>
+      </c>
+      <c r="T86" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501180; </v>
+      </c>
+      <c r="U86" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V86" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W86" t="e">
+        <f>VLOOKUP(D86,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X86" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y86" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z86" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA86" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB86" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC86" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD86" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE86" t="e">
+        <f>VLOOKUP(I86,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF86" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG86" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH86" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Croftlands: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI86" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ86" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK86" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL86" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1879501181</v>
+      </c>
+      <c r="C87" t="s">
+        <v>254</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="O87" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [86] = {["ID"] = 1879501181; }; -- Birds of the Croftlands: Rare</v>
+      </c>
+      <c r="P87" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q87">
+        <f t="shared" si="33"/>
+        <v>86</v>
+      </c>
+      <c r="R87" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [86] = {</v>
+      </c>
+      <c r="S87" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501181; </v>
+      </c>
+      <c r="T87" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501181; </v>
+      </c>
+      <c r="U87" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V87" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W87" t="e">
+        <f>VLOOKUP(D87,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X87" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y87" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z87" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA87" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB87" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC87" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD87" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE87" t="e">
+        <f>VLOOKUP(I87,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF87" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG87" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH87" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Croftlands: Rare"; }; </v>
+      </c>
+      <c r="AI87" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ87" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK87" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL87" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>1879501179</v>
+      </c>
+      <c r="C88" t="s">
+        <v>253</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="O88" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [87] = {["ID"] = 1879501179; }; -- The Rarest Bird of the Croftlands</v>
+      </c>
+      <c r="P88" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q88">
+        <f t="shared" si="33"/>
+        <v>87</v>
+      </c>
+      <c r="R88" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [87] = {</v>
+      </c>
+      <c r="S88" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501179; </v>
+      </c>
+      <c r="T88" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501179; </v>
+      </c>
+      <c r="U88" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V88" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W88" t="e">
+        <f>VLOOKUP(D88,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X88" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y88" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z88" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA88" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB88" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC88" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD88" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE88" t="e">
+        <f>VLOOKUP(I88,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF88" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG88" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH88" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird of the Croftlands"; }; </v>
+      </c>
+      <c r="AI88" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ88" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK88" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL88" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1879501185</v>
+      </c>
+      <c r="C89" t="s">
+        <v>255</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="O89" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [88] = {["ID"] = 1879501185; }; -- All the Birds of the Entwash</v>
+      </c>
+      <c r="P89" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q89">
+        <f t="shared" si="33"/>
+        <v>88</v>
+      </c>
+      <c r="R89" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [88] = {</v>
+      </c>
+      <c r="S89" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501185; </v>
+      </c>
+      <c r="T89" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501185; </v>
+      </c>
+      <c r="U89" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V89" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W89" t="e">
+        <f>VLOOKUP(D89,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X89" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y89" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z89" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA89" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB89" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC89" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD89" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE89" t="e">
+        <f>VLOOKUP(I89,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF89" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG89" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH89" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Entwash"; }; </v>
+      </c>
+      <c r="AI89" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ89" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK89" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL89" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>1879501182</v>
+      </c>
+      <c r="C90" t="s">
+        <v>256</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="O90" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [89] = {["ID"] = 1879501182; }; -- Birds of the Entwash: Common and Uncommon</v>
+      </c>
+      <c r="P90" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q90">
+        <f t="shared" si="33"/>
+        <v>89</v>
+      </c>
+      <c r="R90" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [89] = {</v>
+      </c>
+      <c r="S90" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501182; </v>
+      </c>
+      <c r="T90" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501182; </v>
+      </c>
+      <c r="U90" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V90" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W90" t="e">
+        <f>VLOOKUP(D90,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X90" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y90" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z90" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA90" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB90" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC90" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD90" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE90" t="e">
+        <f>VLOOKUP(I90,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF90" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG90" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH90" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Entwash: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI90" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ90" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK90" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL90" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>1879501183</v>
+      </c>
+      <c r="C91" t="s">
+        <v>257</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="O91" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [90] = {["ID"] = 1879501183; }; -- Birds of the Entwash: Rare</v>
+      </c>
+      <c r="P91" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q91">
+        <f t="shared" si="33"/>
+        <v>90</v>
+      </c>
+      <c r="R91" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [90] = {</v>
+      </c>
+      <c r="S91" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501183; </v>
+      </c>
+      <c r="T91" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501183; </v>
+      </c>
+      <c r="U91" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V91" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W91" t="e">
+        <f>VLOOKUP(D91,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X91" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y91" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z91" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA91" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB91" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC91" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD91" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE91" t="e">
+        <f>VLOOKUP(I91,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF91" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG91" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH91" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Entwash: Rare"; }; </v>
+      </c>
+      <c r="AI91" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ91" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK91" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL91" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1879501184</v>
+      </c>
+      <c r="C92" t="s">
+        <v>258</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="O92" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [91] = {["ID"] = 1879501184; }; -- The Rarest Bird of the Entwash</v>
+      </c>
+      <c r="P92" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q92">
+        <f t="shared" si="33"/>
+        <v>91</v>
+      </c>
+      <c r="R92" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [91] = {</v>
+      </c>
+      <c r="S92" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501184; </v>
+      </c>
+      <c r="T92" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501184; </v>
+      </c>
+      <c r="U92" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V92" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W92" t="e">
+        <f>VLOOKUP(D92,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X92" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y92" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z92" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA92" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB92" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC92" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD92" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE92" t="e">
+        <f>VLOOKUP(I92,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF92" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG92" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH92" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird of the Entwash"; }; </v>
+      </c>
+      <c r="AI92" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ92" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK92" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL92" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1879501188</v>
+      </c>
+      <c r="C93" t="s">
+        <v>259</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="O93" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [92] = {["ID"] = 1879501188; }; -- All the Birds of the Westfold</v>
+      </c>
+      <c r="P93" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q93">
+        <f t="shared" si="33"/>
+        <v>92</v>
+      </c>
+      <c r="R93" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [92] = {</v>
+      </c>
+      <c r="S93" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501188; </v>
+      </c>
+      <c r="T93" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501188; </v>
+      </c>
+      <c r="U93" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V93" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W93" t="e">
+        <f>VLOOKUP(D93,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X93" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y93" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z93" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA93" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB93" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC93" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD93" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE93" t="e">
+        <f>VLOOKUP(I93,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF93" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG93" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH93" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Westfold"; }; </v>
+      </c>
+      <c r="AI93" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ93" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK93" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL93" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>1879501189</v>
+      </c>
+      <c r="C94" t="s">
+        <v>260</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="O94" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [93] = {["ID"] = 1879501189; }; -- Birds of the Westfold: Common and Uncommon</v>
+      </c>
+      <c r="P94" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q94">
+        <f t="shared" si="33"/>
+        <v>93</v>
+      </c>
+      <c r="R94" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [93] = {</v>
+      </c>
+      <c r="S94" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501189; </v>
+      </c>
+      <c r="T94" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501189; </v>
+      </c>
+      <c r="U94" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V94" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W94" t="e">
+        <f>VLOOKUP(D94,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X94" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y94" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z94" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA94" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB94" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC94" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD94" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE94" t="e">
+        <f>VLOOKUP(I94,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF94" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG94" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH94" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Westfold: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI94" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ94" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK94" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL94" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1879501186</v>
+      </c>
+      <c r="C95" t="s">
+        <v>261</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="O95" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [94] = {["ID"] = 1879501186; }; -- Birds of the Westfold: Rare</v>
+      </c>
+      <c r="P95" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q95">
+        <f t="shared" si="33"/>
+        <v>94</v>
+      </c>
+      <c r="R95" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [94] = {</v>
+      </c>
+      <c r="S95" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501186; </v>
+      </c>
+      <c r="T95" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501186; </v>
+      </c>
+      <c r="U95" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V95" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W95" t="e">
+        <f>VLOOKUP(D95,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X95" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y95" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z95" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA95" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB95" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC95" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD95" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE95" t="e">
+        <f>VLOOKUP(I95,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF95" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG95" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH95" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Westfold: Rare"; }; </v>
+      </c>
+      <c r="AI95" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ95" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK95" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL95" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>1879501187</v>
+      </c>
+      <c r="C96" t="s">
+        <v>262</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="O96" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [95] = {["ID"] = 1879501187; }; -- The Rarest Bird in the Westfold</v>
+      </c>
+      <c r="P96" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q96">
+        <f t="shared" si="33"/>
+        <v>95</v>
+      </c>
+      <c r="R96" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [95] = {</v>
+      </c>
+      <c r="S96" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501187; </v>
+      </c>
+      <c r="T96" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501187; </v>
+      </c>
+      <c r="U96" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V96" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W96" t="e">
+        <f>VLOOKUP(D96,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X96" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y96" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z96" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA96" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB96" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC96" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD96" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE96" t="e">
+        <f>VLOOKUP(I96,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF96" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG96" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH96" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Westfold"; }; </v>
+      </c>
+      <c r="AI96" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ96" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK96" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL96" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>1879501191</v>
+      </c>
+      <c r="C97" t="s">
+        <v>263</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="O97" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [96] = {["ID"] = 1879501191; }; -- All the Birds of the Eastfold</v>
+      </c>
+      <c r="P97" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q97">
+        <f t="shared" si="33"/>
+        <v>96</v>
+      </c>
+      <c r="R97" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [96] = {</v>
+      </c>
+      <c r="S97" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501191; </v>
+      </c>
+      <c r="T97" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501191; </v>
+      </c>
+      <c r="U97" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V97" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W97" t="e">
+        <f>VLOOKUP(D97,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X97" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y97" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z97" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA97" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB97" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC97" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD97" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE97" t="e">
+        <f>VLOOKUP(I97,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF97" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG97" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH97" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Eastfold"; }; </v>
+      </c>
+      <c r="AI97" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ97" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK97" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL97" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1879501190</v>
+      </c>
+      <c r="C98" t="s">
+        <v>264</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="O98" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [97] = {["ID"] = 1879501190; }; -- Birds of the Eastfold: Common and Uncommon</v>
+      </c>
+      <c r="P98" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q98">
+        <f t="shared" si="33"/>
+        <v>97</v>
+      </c>
+      <c r="R98" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [97] = {</v>
+      </c>
+      <c r="S98" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501190; </v>
+      </c>
+      <c r="T98" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501190; </v>
+      </c>
+      <c r="U98" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V98" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W98" t="e">
+        <f>VLOOKUP(D98,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X98" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y98" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z98" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA98" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB98" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC98" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD98" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE98" t="e">
+        <f>VLOOKUP(I98,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF98" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG98" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH98" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Eastfold: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AI98" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ98" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK98" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL98" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>1879501193</v>
+      </c>
+      <c r="C99" t="s">
+        <v>265</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="O99" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [98] = {["ID"] = 1879501193; }; -- Birds of the Eastfold: Rare</v>
+      </c>
+      <c r="P99" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q99">
+        <f t="shared" si="33"/>
+        <v>98</v>
+      </c>
+      <c r="R99" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [98] = {</v>
+      </c>
+      <c r="S99" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501193; </v>
+      </c>
+      <c r="T99" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501193; </v>
+      </c>
+      <c r="U99" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V99" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W99" t="e">
+        <f>VLOOKUP(D99,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X99" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y99" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z99" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA99" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB99" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC99" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD99" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE99" t="e">
+        <f>VLOOKUP(I99,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF99" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG99" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH99" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Eastfold: Rare"; }; </v>
+      </c>
+      <c r="AI99" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ99" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK99" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL99" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1879501192</v>
+      </c>
+      <c r="C100" t="s">
+        <v>266</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="O100" t="str">
+        <f t="shared" si="31"/>
+        <v xml:space="preserve"> [99] = {["ID"] = 1879501192; }; -- The Rarest Bird of the Eastfold</v>
+      </c>
+      <c r="P100" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q100">
+        <f t="shared" si="33"/>
+        <v>99</v>
+      </c>
+      <c r="R100" t="str">
+        <f t="shared" si="34"/>
+        <v xml:space="preserve"> [99] = {</v>
+      </c>
+      <c r="S100" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501192; </v>
+      </c>
+      <c r="T100" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501192; </v>
+      </c>
+      <c r="U100" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V100" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W100" t="e">
+        <f>VLOOKUP(D100,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X100" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y100" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z100" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA100" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB100" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC100" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD100" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE100" t="e">
+        <f>VLOOKUP(I100,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF100" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG100" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AH100" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird of the Eastfold"; }; </v>
+      </c>
+      <c r="AI100" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ100" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK100" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL100" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
+    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>1879501776</v>
+      </c>
+      <c r="C101" t="s">
+        <v>267</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="O101" t="str">
+        <f t="shared" si="31"/>
+        <v>[100] = {["ID"] = 1879501776; }; -- The Rarest of Birds in Rohan and the Great River</v>
+      </c>
+      <c r="P101" s="1" t="e">
+        <f t="shared" si="32"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q101">
+        <f t="shared" si="33"/>
+        <v>100</v>
+      </c>
+      <c r="R101" t="str">
+        <f t="shared" si="34"/>
+        <v>[100] = {</v>
+      </c>
+      <c r="S101" t="str">
+        <f t="shared" si="35"/>
+        <v xml:space="preserve">["ID"] = 1879501776; </v>
+      </c>
+      <c r="T101" t="str">
+        <f t="shared" si="36"/>
+        <v xml:space="preserve">["ID"] = 1879501776; </v>
+      </c>
+      <c r="U101" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="V101" s="1" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="W101" t="e">
+        <f>VLOOKUP(D101,Type!A$2:B$17,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X101" t="e">
+        <f t="shared" si="39"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y101" t="str">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="Z101" t="str">
+        <f t="shared" si="41"/>
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AA101" t="str">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="AB101" t="str">
+        <f t="shared" si="43"/>
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AC101" t="str">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AD101" t="str">
+        <f t="shared" si="45"/>
+        <v xml:space="preserve">["REP"] = 0; </v>
+      </c>
+      <c r="AE101" t="e">
+        <f>VLOOKUP(I101,Faction!A$2:B$77,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF101" t="e">
+        <f t="shared" si="46"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG101" t="str">
+        <f t="shared" si="47"/>
+        <v xml:space="preserve">["TIER"] = 0; </v>
+      </c>
+      <c r="AH101" t="str">
+        <f t="shared" si="48"/>
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest of Birds in Rohan and the Great River"; }; </v>
+      </c>
+      <c r="AI101" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ101" t="str">
+        <f t="shared" si="50"/>
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK101" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="AL101" t="str">
+        <f t="shared" si="52"/>
+        <v>};</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B1">
+  <conditionalFormatting sqref="B1:B2">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_SourceFiles/DeedInfo-3-Hobbies.xlsx
+++ b/_SourceFiles/DeedInfo-3-Hobbies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkckx\Documents\The Lord of the Rings Online\Plugins\CubePlugins\DeedTracker\_SourceFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE2AF40-C64A-4FFF-98C4-D899067287DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5F9D8D-9ECC-400C-BBFA-4F584FF4ACFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{CDC9C16A-58F0-4807-B5CD-F77FF9D2EA43}"/>
+    <workbookView xWindow="-18615" yWindow="1620" windowWidth="18600" windowHeight="14025" activeTab="6" xr2:uid="{CDC9C16A-58F0-4807-B5CD-F77FF9D2EA43}"/>
   </bookViews>
   <sheets>
     <sheet name="Type" sheetId="2" r:id="rId1"/>
@@ -3291,9 +3291,10 @@
     <col min="11" max="11" width="0" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="24.5703125" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" customWidth="1"/>
+    <col min="16" max="16" width="35.5703125" customWidth="1"/>
     <col min="17" max="17" width="43.5703125" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="14" customWidth="1"/>
+    <col min="34" max="34" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
@@ -3430,7 +3431,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <f>CONCATENATE(S2,U2,V2,AM2," -- ",C2)</f>
+        <f>CONCATENATE(S2,U2,V2,AH2,AM2," -- ",C2)</f>
         <v xml:space="preserve">  [1] = {["CAT_ID"] = 320; }; -- Eriador</v>
       </c>
       <c r="Q2" s="1" t="e">
@@ -3502,8 +3503,8 @@
         <v>#N/A</v>
       </c>
       <c r="AH2" t="str">
-        <f>CONCATENATE("[""TIER""] = ",TEXT(L2,"0"),"; ")</f>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <f>IF(L2&gt;0,CONCATENATE("[""TIER""] = ",TEXT(L2,"0"),"; "),"")</f>
+        <v/>
       </c>
       <c r="AI2" t="str">
         <f>CONCATENATE("[""NAME""] = { [""EN""] = """,C2,"""; }; ")</f>
@@ -3544,7 +3545,7 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <f t="shared" ref="P3:P66" si="10">CONCATENATE(S3,U3,V3,AM3," -- ",C3)</f>
+        <f t="shared" ref="P3:P66" si="10">CONCATENATE(S3,U3,V3,AH3,AM3," -- ",C3)</f>
         <v xml:space="preserve">  [2] = {["ID"] = 1879490678; }; -- All the Birds of Bree-land</v>
       </c>
       <c r="Q3" s="1" t="e">
@@ -3616,8 +3617,8 @@
         <v xml:space="preserve">["FACTION"] = 1; </v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH66" si="26">CONCATENATE("[""TIER""] = ",TEXT(L3,"0"),"; ")</f>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <f t="shared" ref="AH3:AH66" si="26">IF(L3&gt;0,CONCATENATE("[""TIER""] = ",TEXT(L3,"0"),"; "),"")</f>
+        <v/>
       </c>
       <c r="AI3" t="str">
         <f t="shared" ref="AI3:AI66" si="27">CONCATENATE("[""NAME""] = { [""EN""] = """,C3,"""; }; ")</f>
@@ -3659,7 +3660,7 @@
       </c>
       <c r="P4" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  [3] = {["ID"] = 1879490611; }; -- Birds of Bree-land: Common and Uncommon</v>
+        <v xml:space="preserve">  [3] = {["ID"] = 1879490611; ["TIER"] = 1; }; -- Birds of Bree-land: Common and Uncommon</v>
       </c>
       <c r="Q4" s="1" t="e">
         <f t="shared" si="11"/>
@@ -3773,7 +3774,7 @@
       </c>
       <c r="P5" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  [4] = {["ID"] = 1879490469; }; -- Birds of Bree-land: Rare</v>
+        <v xml:space="preserve">  [4] = {["ID"] = 1879490469; ["TIER"] = 1; }; -- Birds of Bree-land: Rare</v>
       </c>
       <c r="Q5" s="1" t="e">
         <f t="shared" si="11"/>
@@ -3887,7 +3888,7 @@
       </c>
       <c r="P6" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  [5] = {["ID"] = 1879490610; }; -- The Rarest Bird in Bree-land</v>
+        <v xml:space="preserve">  [5] = {["ID"] = 1879490610; ["TIER"] = 1; }; -- The Rarest Bird in Bree-land</v>
       </c>
       <c r="Q6" s="1" t="e">
         <f t="shared" si="11"/>
@@ -4073,7 +4074,7 @@
       </c>
       <c r="AH7" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI7" t="str">
         <f t="shared" si="27"/>
@@ -4115,7 +4116,7 @@
       </c>
       <c r="P8" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  [7] = {["ID"] = 1879490617; }; -- Birds of The Shire: Common and Uncommon</v>
+        <v xml:space="preserve">  [7] = {["ID"] = 1879490617; ["TIER"] = 1; }; -- Birds of The Shire: Common and Uncommon</v>
       </c>
       <c r="Q8" s="1" t="e">
         <f t="shared" si="11"/>
@@ -4226,7 +4227,7 @@
       </c>
       <c r="P9" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  [8] = {["ID"] = 1879490640; }; -- Birds of The Shire: Rare</v>
+        <v xml:space="preserve">  [8] = {["ID"] = 1879490640; ["TIER"] = 1; }; -- Birds of The Shire: Rare</v>
       </c>
       <c r="Q9" s="1" t="e">
         <f t="shared" si="11"/>
@@ -4337,7 +4338,7 @@
       </c>
       <c r="P10" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">  [9] = {["ID"] = 1879490622; }; -- The Rarest Bird in The Shire</v>
+        <v xml:space="preserve">  [9] = {["ID"] = 1879490622; ["TIER"] = 1; }; -- The Rarest Bird in The Shire</v>
       </c>
       <c r="Q10" s="1" t="e">
         <f t="shared" si="11"/>
@@ -4520,7 +4521,7 @@
       </c>
       <c r="AH11" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI11" t="str">
         <f t="shared" si="27"/>
@@ -4559,7 +4560,7 @@
       </c>
       <c r="P12" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [11] = {["ID"] = 1879490651; }; -- Birds of Ered Luin: Common and Uncommon</v>
+        <v xml:space="preserve"> [11] = {["ID"] = 1879490651; ["TIER"] = 1; }; -- Birds of Ered Luin: Common and Uncommon</v>
       </c>
       <c r="Q12" s="1" t="e">
         <f t="shared" si="11"/>
@@ -4670,7 +4671,7 @@
       </c>
       <c r="P13" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [12] = {["ID"] = 1879490635; }; -- Birds of Ered Luin: Rare</v>
+        <v xml:space="preserve"> [12] = {["ID"] = 1879490635; ["TIER"] = 1; }; -- Birds of Ered Luin: Rare</v>
       </c>
       <c r="Q13" s="1" t="e">
         <f t="shared" si="11"/>
@@ -4781,7 +4782,7 @@
       </c>
       <c r="P14" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [13] = {["ID"] = 1879490633; }; -- The Rarest Bird in Ered Luin</v>
+        <v xml:space="preserve"> [13] = {["ID"] = 1879490633; ["TIER"] = 1; }; -- The Rarest Bird in Ered Luin</v>
       </c>
       <c r="Q14" s="1" t="e">
         <f t="shared" si="11"/>
@@ -4964,7 +4965,7 @@
       </c>
       <c r="AH15" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI15" t="str">
         <f t="shared" si="27"/>
@@ -5003,7 +5004,7 @@
       </c>
       <c r="P16" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [15] = {["ID"] = 1879490642; }; -- Birds of Swanfleet: Common and Uncommon</v>
+        <v xml:space="preserve"> [15] = {["ID"] = 1879490642; ["TIER"] = 1; }; -- Birds of Swanfleet: Common and Uncommon</v>
       </c>
       <c r="Q16" s="1" t="e">
         <f t="shared" si="11"/>
@@ -5114,7 +5115,7 @@
       </c>
       <c r="P17" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [16] = {["ID"] = 1879490641; }; -- Birds of Swanfleet: Rare</v>
+        <v xml:space="preserve"> [16] = {["ID"] = 1879490641; ["TIER"] = 1; }; -- Birds of Swanfleet: Rare</v>
       </c>
       <c r="Q17" s="1" t="e">
         <f t="shared" si="11"/>
@@ -5225,7 +5226,7 @@
       </c>
       <c r="P18" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [17] = {["ID"] = 1879490645; }; -- The Rarest Bird in Swanfleet</v>
+        <v xml:space="preserve"> [17] = {["ID"] = 1879490645; ["TIER"] = 1; }; -- The Rarest Bird in Swanfleet</v>
       </c>
       <c r="Q18" s="1" t="e">
         <f t="shared" si="11"/>
@@ -5408,7 +5409,7 @@
       </c>
       <c r="AH19" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI19" t="str">
         <f t="shared" si="27"/>
@@ -5447,7 +5448,7 @@
       </c>
       <c r="P20" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [19] = {["ID"] = 1879490621; }; -- Birds of Cardolan: Common and Uncommon</v>
+        <v xml:space="preserve"> [19] = {["ID"] = 1879490621; ["TIER"] = 1; }; -- Birds of Cardolan: Common and Uncommon</v>
       </c>
       <c r="Q20" s="1" t="e">
         <f t="shared" si="11"/>
@@ -5558,7 +5559,7 @@
       </c>
       <c r="P21" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [20] = {["ID"] = 1879490627; }; -- Birds of Cardolan: Rare</v>
+        <v xml:space="preserve"> [20] = {["ID"] = 1879490627; ["TIER"] = 1; }; -- Birds of Cardolan: Rare</v>
       </c>
       <c r="Q21" s="1" t="e">
         <f t="shared" si="11"/>
@@ -5669,7 +5670,7 @@
       </c>
       <c r="P22" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [21] = {["ID"] = 1879490647; }; -- The Rarest Bird in Cardolan</v>
+        <v xml:space="preserve"> [21] = {["ID"] = 1879490647; ["TIER"] = 1; }; -- The Rarest Bird in Cardolan</v>
       </c>
       <c r="Q22" s="1" t="e">
         <f t="shared" si="11"/>
@@ -5852,7 +5853,7 @@
       </c>
       <c r="AH23" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI23" t="str">
         <f t="shared" si="27"/>
@@ -5891,7 +5892,7 @@
       </c>
       <c r="P24" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [23] = {["ID"] = 1879490649; }; -- Birds of the Lone-lands: Common and Uncommon</v>
+        <v xml:space="preserve"> [23] = {["ID"] = 1879490649; ["TIER"] = 1; }; -- Birds of the Lone-lands: Common and Uncommon</v>
       </c>
       <c r="Q24" s="1" t="e">
         <f t="shared" si="11"/>
@@ -6002,7 +6003,7 @@
       </c>
       <c r="P25" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [24] = {["ID"] = 1879490632; }; -- Birds of the Lone-lands: Rare</v>
+        <v xml:space="preserve"> [24] = {["ID"] = 1879490632; ["TIER"] = 1; }; -- Birds of the Lone-lands: Rare</v>
       </c>
       <c r="Q25" s="1" t="e">
         <f t="shared" si="11"/>
@@ -6113,7 +6114,7 @@
       </c>
       <c r="P26" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [25] = {["ID"] = 1879490637; }; -- The Rarest Bird in the Lone-lands</v>
+        <v xml:space="preserve"> [25] = {["ID"] = 1879490637; ["TIER"] = 1; }; -- The Rarest Bird in the Lone-lands</v>
       </c>
       <c r="Q26" s="1" t="e">
         <f t="shared" si="11"/>
@@ -6296,7 +6297,7 @@
       </c>
       <c r="AH27" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI27" t="str">
         <f t="shared" si="27"/>
@@ -6335,7 +6336,7 @@
       </c>
       <c r="P28" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [27] = {["ID"] = 1879490630; }; -- Birds of The North Downs: Common and Uncommon</v>
+        <v xml:space="preserve"> [27] = {["ID"] = 1879490630; ["TIER"] = 1; }; -- Birds of The North Downs: Common and Uncommon</v>
       </c>
       <c r="Q28" s="1" t="e">
         <f t="shared" si="11"/>
@@ -6446,7 +6447,7 @@
       </c>
       <c r="P29" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [28] = {["ID"] = 1879490626; }; -- Birds of the North Downs: Rare</v>
+        <v xml:space="preserve"> [28] = {["ID"] = 1879490626; ["TIER"] = 1; }; -- Birds of the North Downs: Rare</v>
       </c>
       <c r="Q29" s="1" t="e">
         <f t="shared" si="11"/>
@@ -6557,7 +6558,7 @@
       </c>
       <c r="P30" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [29] = {["ID"] = 1879490625; }; -- The Rarest Bird in the North Downs</v>
+        <v xml:space="preserve"> [29] = {["ID"] = 1879490625; ["TIER"] = 1; }; -- The Rarest Bird in the North Downs</v>
       </c>
       <c r="Q30" s="1" t="e">
         <f t="shared" si="11"/>
@@ -6740,7 +6741,7 @@
       </c>
       <c r="AH31" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI31" t="str">
         <f t="shared" si="27"/>
@@ -6779,7 +6780,7 @@
       </c>
       <c r="P32" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [31] = {["ID"] = 1879490614; }; -- Birds of the Trollshaws: Common and Uncommon</v>
+        <v xml:space="preserve"> [31] = {["ID"] = 1879490614; ["TIER"] = 1; }; -- Birds of the Trollshaws: Common and Uncommon</v>
       </c>
       <c r="Q32" s="1" t="e">
         <f t="shared" si="11"/>
@@ -6890,7 +6891,7 @@
       </c>
       <c r="P33" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [32] = {["ID"] = 1879490639; }; -- Birds of the Trollshaws: Rare</v>
+        <v xml:space="preserve"> [32] = {["ID"] = 1879490639; ["TIER"] = 1; }; -- Birds of the Trollshaws: Rare</v>
       </c>
       <c r="Q33" s="1" t="e">
         <f t="shared" si="11"/>
@@ -7001,7 +7002,7 @@
       </c>
       <c r="P34" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [33] = {["ID"] = 1879490629; }; -- The Rarest Bird in the Trollshaws</v>
+        <v xml:space="preserve"> [33] = {["ID"] = 1879490629; ["TIER"] = 1; }; -- The Rarest Bird in the Trollshaws</v>
       </c>
       <c r="Q34" s="1" t="e">
         <f t="shared" si="11"/>
@@ -7184,7 +7185,7 @@
       </c>
       <c r="AH35" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI35" t="str">
         <f t="shared" si="27"/>
@@ -7223,7 +7224,7 @@
       </c>
       <c r="P36" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [35] = {["ID"] = 1879490650; }; -- Birds of the Misty Mountains: Common and Uncommon</v>
+        <v xml:space="preserve"> [35] = {["ID"] = 1879490650; ["TIER"] = 1; }; -- Birds of the Misty Mountains: Common and Uncommon</v>
       </c>
       <c r="Q36" s="1" t="e">
         <f t="shared" si="11"/>
@@ -7334,7 +7335,7 @@
       </c>
       <c r="P37" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [36] = {["ID"] = 1879490620; }; -- Birds of the Misty Mountains: Rare</v>
+        <v xml:space="preserve"> [36] = {["ID"] = 1879490620; ["TIER"] = 1; }; -- Birds of the Misty Mountains: Rare</v>
       </c>
       <c r="Q37" s="1" t="e">
         <f t="shared" si="11"/>
@@ -7445,7 +7446,7 @@
       </c>
       <c r="P38" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [37] = {["ID"] = 1879490612; }; -- The Rarest Bird in the Misty Mountains</v>
+        <v xml:space="preserve"> [37] = {["ID"] = 1879490612; ["TIER"] = 1; }; -- The Rarest Bird in the Misty Mountains</v>
       </c>
       <c r="Q38" s="1" t="e">
         <f t="shared" si="11"/>
@@ -7628,7 +7629,7 @@
       </c>
       <c r="AH39" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI39" t="str">
         <f t="shared" si="27"/>
@@ -7667,7 +7668,7 @@
       </c>
       <c r="P40" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [39] = {["ID"] = 1879490643; }; -- Birds of Evendim: Common and Uncommon</v>
+        <v xml:space="preserve"> [39] = {["ID"] = 1879490643; ["TIER"] = 1; }; -- Birds of Evendim: Common and Uncommon</v>
       </c>
       <c r="Q40" s="1" t="e">
         <f t="shared" si="11"/>
@@ -7778,7 +7779,7 @@
       </c>
       <c r="P41" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [40] = {["ID"] = 1879490638; }; -- Birds of Evendim: Rare</v>
+        <v xml:space="preserve"> [40] = {["ID"] = 1879490638; ["TIER"] = 1; }; -- Birds of Evendim: Rare</v>
       </c>
       <c r="Q41" s="1" t="e">
         <f t="shared" si="11"/>
@@ -7889,7 +7890,7 @@
       </c>
       <c r="P42" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [41] = {["ID"] = 1879490615; }; -- The Rarest Bird in Evendim</v>
+        <v xml:space="preserve"> [41] = {["ID"] = 1879490615; ["TIER"] = 1; }; -- The Rarest Bird in Evendim</v>
       </c>
       <c r="Q42" s="1" t="e">
         <f t="shared" si="11"/>
@@ -8072,7 +8073,7 @@
       </c>
       <c r="AH43" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI43" t="str">
         <f t="shared" si="27"/>
@@ -8111,7 +8112,7 @@
       </c>
       <c r="P44" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [43] = {["ID"] = 1879490646; }; -- Birds of Angmar: Common and Uncommon</v>
+        <v xml:space="preserve"> [43] = {["ID"] = 1879490646; ["TIER"] = 1; }; -- Birds of Angmar: Common and Uncommon</v>
       </c>
       <c r="Q44" s="1" t="e">
         <f t="shared" si="11"/>
@@ -8222,7 +8223,7 @@
       </c>
       <c r="P45" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [44] = {["ID"] = 1879490636; }; -- Birds of Angmar: Rare</v>
+        <v xml:space="preserve"> [44] = {["ID"] = 1879490636; ["TIER"] = 1; }; -- Birds of Angmar: Rare</v>
       </c>
       <c r="Q45" s="1" t="e">
         <f t="shared" si="11"/>
@@ -8333,7 +8334,7 @@
       </c>
       <c r="P46" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [45] = {["ID"] = 1879490648; }; -- The Rarest Bird in Angmar</v>
+        <v xml:space="preserve"> [45] = {["ID"] = 1879490648; ["TIER"] = 1; }; -- The Rarest Bird in Angmar</v>
       </c>
       <c r="Q46" s="1" t="e">
         <f t="shared" si="11"/>
@@ -8516,7 +8517,7 @@
       </c>
       <c r="AH47" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI47" t="str">
         <f t="shared" si="27"/>
@@ -8555,7 +8556,7 @@
       </c>
       <c r="P48" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [47] = {["ID"] = 1879490613; }; -- Birds of Forochel: Common and Uncommon</v>
+        <v xml:space="preserve"> [47] = {["ID"] = 1879490613; ["TIER"] = 1; }; -- Birds of Forochel: Common and Uncommon</v>
       </c>
       <c r="Q48" s="1" t="e">
         <f t="shared" si="11"/>
@@ -8666,7 +8667,7 @@
       </c>
       <c r="P49" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [48] = {["ID"] = 1879490624; }; -- Birds of Forochel: Rare</v>
+        <v xml:space="preserve"> [48] = {["ID"] = 1879490624; ["TIER"] = 1; }; -- Birds of Forochel: Rare</v>
       </c>
       <c r="Q49" s="1" t="e">
         <f t="shared" si="11"/>
@@ -8777,7 +8778,7 @@
       </c>
       <c r="P50" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [49] = {["ID"] = 1879490618; }; -- The Rarest Bird in Forochel</v>
+        <v xml:space="preserve"> [49] = {["ID"] = 1879490618; ["TIER"] = 1; }; -- The Rarest Bird in Forochel</v>
       </c>
       <c r="Q50" s="1" t="e">
         <f t="shared" si="11"/>
@@ -8960,7 +8961,7 @@
       </c>
       <c r="AH51" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI51" t="str">
         <f t="shared" si="27"/>
@@ -8999,7 +9000,7 @@
       </c>
       <c r="P52" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [51] = {["ID"] = 1879490631; }; -- Birds of Eregion: Common and Uncommon</v>
+        <v xml:space="preserve"> [51] = {["ID"] = 1879490631; ["TIER"] = 1; }; -- Birds of Eregion: Common and Uncommon</v>
       </c>
       <c r="Q52" s="1" t="e">
         <f t="shared" si="11"/>
@@ -9110,7 +9111,7 @@
       </c>
       <c r="P53" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [52] = {["ID"] = 1879490644; }; -- Birds of Eregion: Rare</v>
+        <v xml:space="preserve"> [52] = {["ID"] = 1879490644; ["TIER"] = 1; }; -- Birds of Eregion: Rare</v>
       </c>
       <c r="Q53" s="1" t="e">
         <f t="shared" si="11"/>
@@ -9221,7 +9222,7 @@
       </c>
       <c r="P54" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [53] = {["ID"] = 1879490628; }; -- The Rarest Bird in Eregion</v>
+        <v xml:space="preserve"> [53] = {["ID"] = 1879490628; ["TIER"] = 1; }; -- The Rarest Bird in Eregion</v>
       </c>
       <c r="Q54" s="1" t="e">
         <f t="shared" si="11"/>
@@ -9404,7 +9405,7 @@
       </c>
       <c r="AH55" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI55" t="str">
         <f t="shared" si="27"/>
@@ -9443,7 +9444,7 @@
       </c>
       <c r="P56" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [55] = {["ID"] = 1879490616; }; -- Birds of Enedwaith: Common and Uncommon</v>
+        <v xml:space="preserve"> [55] = {["ID"] = 1879490616; ["TIER"] = 1; }; -- Birds of Enedwaith: Common and Uncommon</v>
       </c>
       <c r="Q56" s="1" t="e">
         <f t="shared" si="11"/>
@@ -9554,7 +9555,7 @@
       </c>
       <c r="P57" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [56] = {["ID"] = 1879490652; }; -- Birds of Enedwaith: Rare</v>
+        <v xml:space="preserve"> [56] = {["ID"] = 1879490652; ["TIER"] = 1; }; -- Birds of Enedwaith: Rare</v>
       </c>
       <c r="Q57" s="1" t="e">
         <f t="shared" si="11"/>
@@ -9665,7 +9666,7 @@
       </c>
       <c r="P58" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [57] = {["ID"] = 1879490653; }; -- The Rarest Bird in Enedwaith</v>
+        <v xml:space="preserve"> [57] = {["ID"] = 1879490653; ["TIER"] = 1; }; -- The Rarest Bird in Enedwaith</v>
       </c>
       <c r="Q58" s="1" t="e">
         <f t="shared" si="11"/>
@@ -9848,7 +9849,7 @@
       </c>
       <c r="AH59" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI59" t="str">
         <f t="shared" si="27"/>
@@ -9887,7 +9888,7 @@
       </c>
       <c r="P60" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [59] = {["ID"] = 1879490623; }; -- Birds of Dunland: Common and Uncommon</v>
+        <v xml:space="preserve"> [59] = {["ID"] = 1879490623; ["TIER"] = 1; }; -- Birds of Dunland: Common and Uncommon</v>
       </c>
       <c r="Q60" s="1" t="e">
         <f t="shared" si="11"/>
@@ -9998,7 +9999,7 @@
       </c>
       <c r="P61" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [60] = {["ID"] = 1879490634; }; -- Birds of Dunland: Rare</v>
+        <v xml:space="preserve"> [60] = {["ID"] = 1879490634; ["TIER"] = 1; }; -- Birds of Dunland: Rare</v>
       </c>
       <c r="Q61" s="1" t="e">
         <f t="shared" si="11"/>
@@ -10109,7 +10110,7 @@
       </c>
       <c r="P62" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [61] = {["ID"] = 1879490619; }; -- The Rarest Bird in Dunland</v>
+        <v xml:space="preserve"> [61] = {["ID"] = 1879490619; ["TIER"] = 1; }; -- The Rarest Bird in Dunland</v>
       </c>
       <c r="Q62" s="1" t="e">
         <f t="shared" si="11"/>
@@ -10292,7 +10293,7 @@
       </c>
       <c r="AH63" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI63" t="str">
         <f t="shared" si="27"/>
@@ -10403,7 +10404,7 @@
       </c>
       <c r="AH64" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI64" t="str">
         <f t="shared" si="27"/>
@@ -10514,7 +10515,7 @@
       </c>
       <c r="AH65" t="str">
         <f t="shared" si="26"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI65" t="str">
         <f t="shared" si="27"/>
@@ -10553,7 +10554,7 @@
       </c>
       <c r="P66" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve"> [65] = {["ID"] = 1879501133; }; -- Birds of Lothlórien: Common and Uncommon</v>
+        <v xml:space="preserve"> [65] = {["ID"] = 1879501133; ["TIER"] = 1; }; -- Birds of Lothlórien: Common and Uncommon</v>
       </c>
       <c r="Q66" s="1" t="e">
         <f t="shared" si="11"/>
@@ -10663,8 +10664,8 @@
         <v>[1879501131] = 1, // Birds of Lothlórien: Rare</v>
       </c>
       <c r="P67" t="str">
-        <f t="shared" ref="P67:P101" si="33">CONCATENATE(S67,U67,V67,AM67," -- ",C67)</f>
-        <v xml:space="preserve"> [66] = {["ID"] = 1879501131; }; -- Birds of Lothlórien: Rare</v>
+        <f t="shared" ref="P67:P130" si="33">CONCATENATE(S67,U67,V67,AH67,AM67," -- ",C67)</f>
+        <v xml:space="preserve"> [66] = {["ID"] = 1879501131; ["TIER"] = 1; }; -- Birds of Lothlórien: Rare</v>
       </c>
       <c r="Q67" s="1" t="e">
         <f t="shared" ref="Q67:Q101" si="34">CONCATENATE(S67,T67,W67,Y67,AA67,AC67,AE67,AG67,AH67,AI67,AJ67,AK67,AL67,AM67)</f>
@@ -10735,7 +10736,7 @@
         <v>#N/A</v>
       </c>
       <c r="AH67" t="str">
-        <f t="shared" ref="AH67:AH101" si="49">CONCATENATE("[""TIER""] = ",TEXT(L67,"0"),"; ")</f>
+        <f t="shared" ref="AH67:AH130" si="49">IF(L67&gt;0,CONCATENATE("[""TIER""] = ",TEXT(L67,"0"),"; "),"")</f>
         <v xml:space="preserve">["TIER"] = 1; </v>
       </c>
       <c r="AI67" t="str">
@@ -10775,7 +10776,7 @@
       </c>
       <c r="P68" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [67] = {["ID"] = 1879501134; }; -- The Rarest Bird in Lothlórien</v>
+        <v xml:space="preserve"> [67] = {["ID"] = 1879501134; ["TIER"] = 1; }; -- The Rarest Bird in Lothlórien</v>
       </c>
       <c r="Q68" s="1" t="e">
         <f t="shared" si="34"/>
@@ -10958,7 +10959,7 @@
       </c>
       <c r="AH69" t="str">
         <f t="shared" si="49"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI69" t="str">
         <f t="shared" si="50"/>
@@ -10997,7 +10998,7 @@
       </c>
       <c r="P70" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [69] = {["ID"] = 1879501162; }; -- Birds of Mirkwood: Common and Uncommon</v>
+        <v xml:space="preserve"> [69] = {["ID"] = 1879501162; ["TIER"] = 1; }; -- Birds of Mirkwood: Common and Uncommon</v>
       </c>
       <c r="Q70" s="1" t="e">
         <f t="shared" si="34"/>
@@ -11108,7 +11109,7 @@
       </c>
       <c r="P71" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [70] = {["ID"] = 1879501161; }; -- Birds of Mirkwood: Rare</v>
+        <v xml:space="preserve"> [70] = {["ID"] = 1879501161; ["TIER"] = 1; }; -- Birds of Mirkwood: Rare</v>
       </c>
       <c r="Q71" s="1" t="e">
         <f t="shared" si="34"/>
@@ -11219,7 +11220,7 @@
       </c>
       <c r="P72" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [71] = {["ID"] = 1879501163; }; -- The Rarest Bird in Mirkwood</v>
+        <v xml:space="preserve"> [71] = {["ID"] = 1879501163; ["TIER"] = 1; }; -- The Rarest Bird in Mirkwood</v>
       </c>
       <c r="Q72" s="1" t="e">
         <f t="shared" si="34"/>
@@ -11402,7 +11403,7 @@
       </c>
       <c r="AH73" t="str">
         <f t="shared" si="49"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI73" t="str">
         <f t="shared" si="50"/>
@@ -11441,7 +11442,7 @@
       </c>
       <c r="P74" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [73] = {["ID"] = 1879501167; }; -- Birds of the Great River: Common and Uncommon</v>
+        <v xml:space="preserve"> [73] = {["ID"] = 1879501167; ["TIER"] = 1; }; -- Birds of the Great River: Common and Uncommon</v>
       </c>
       <c r="Q74" s="1" t="e">
         <f t="shared" si="34"/>
@@ -11552,7 +11553,7 @@
       </c>
       <c r="P75" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [74] = {["ID"] = 1879501168; }; -- Birds of the Great River: Rare</v>
+        <v xml:space="preserve"> [74] = {["ID"] = 1879501168; ["TIER"] = 1; }; -- Birds of the Great River: Rare</v>
       </c>
       <c r="Q75" s="1" t="e">
         <f t="shared" si="34"/>
@@ -11663,7 +11664,7 @@
       </c>
       <c r="P76" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [75] = {["ID"] = 1879501165; }; -- The Rarest Bird of the Great River</v>
+        <v xml:space="preserve"> [75] = {["ID"] = 1879501165; ["TIER"] = 1; }; -- The Rarest Bird of the Great River</v>
       </c>
       <c r="Q76" s="1" t="e">
         <f t="shared" si="34"/>
@@ -11846,7 +11847,7 @@
       </c>
       <c r="AH77" t="str">
         <f t="shared" si="49"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI77" t="str">
         <f t="shared" si="50"/>
@@ -11885,7 +11886,7 @@
       </c>
       <c r="P78" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [77] = {["ID"] = 1879501171; }; -- Birds of the Wold: Common and Uncommon</v>
+        <v xml:space="preserve"> [77] = {["ID"] = 1879501171; ["TIER"] = 1; }; -- Birds of the Wold: Common and Uncommon</v>
       </c>
       <c r="Q78" s="1" t="e">
         <f t="shared" si="34"/>
@@ -11996,7 +11997,7 @@
       </c>
       <c r="P79" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [78] = {["ID"] = 1879501173; }; -- Birds of the Wold: Rare</v>
+        <v xml:space="preserve"> [78] = {["ID"] = 1879501173; ["TIER"] = 1; }; -- Birds of the Wold: Rare</v>
       </c>
       <c r="Q79" s="1" t="e">
         <f t="shared" si="34"/>
@@ -12107,7 +12108,7 @@
       </c>
       <c r="P80" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [79] = {["ID"] = 1879501172; }; -- The Rarest Bird of the Wold</v>
+        <v xml:space="preserve"> [79] = {["ID"] = 1879501172; ["TIER"] = 1; }; -- The Rarest Bird of the Wold</v>
       </c>
       <c r="Q80" s="1" t="e">
         <f t="shared" si="34"/>
@@ -12290,7 +12291,7 @@
       </c>
       <c r="AH81" t="str">
         <f t="shared" si="49"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI81" t="str">
         <f t="shared" si="50"/>
@@ -12329,7 +12330,7 @@
       </c>
       <c r="P82" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [81] = {["ID"] = 1879501176; }; -- Birds of Fangorn: Common and Uncommon</v>
+        <v xml:space="preserve"> [81] = {["ID"] = 1879501176; ["TIER"] = 1; }; -- Birds of Fangorn: Common and Uncommon</v>
       </c>
       <c r="Q82" s="1" t="e">
         <f t="shared" si="34"/>
@@ -12440,7 +12441,7 @@
       </c>
       <c r="P83" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [82] = {["ID"] = 1879501175; }; -- Birds of Fangorn: Rare</v>
+        <v xml:space="preserve"> [82] = {["ID"] = 1879501175; ["TIER"] = 1; }; -- Birds of Fangorn: Rare</v>
       </c>
       <c r="Q83" s="1" t="e">
         <f t="shared" si="34"/>
@@ -12551,7 +12552,7 @@
       </c>
       <c r="P84" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [83] = {["ID"] = 1879501177; }; -- The Rarest Bird in Fangorn</v>
+        <v xml:space="preserve"> [83] = {["ID"] = 1879501177; ["TIER"] = 1; }; -- The Rarest Bird in Fangorn</v>
       </c>
       <c r="Q84" s="1" t="e">
         <f t="shared" si="34"/>
@@ -12734,7 +12735,7 @@
       </c>
       <c r="AH85" t="str">
         <f t="shared" si="49"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI85" t="str">
         <f t="shared" si="50"/>
@@ -12773,7 +12774,7 @@
       </c>
       <c r="P86" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [85] = {["ID"] = 1879501180; }; -- Birds of the Croftlands: Common and Uncommon</v>
+        <v xml:space="preserve"> [85] = {["ID"] = 1879501180; ["TIER"] = 1; }; -- Birds of the Croftlands: Common and Uncommon</v>
       </c>
       <c r="Q86" s="1" t="e">
         <f t="shared" si="34"/>
@@ -12884,7 +12885,7 @@
       </c>
       <c r="P87" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [86] = {["ID"] = 1879501181; }; -- Birds of the Croftlands: Rare</v>
+        <v xml:space="preserve"> [86] = {["ID"] = 1879501181; ["TIER"] = 1; }; -- Birds of the Croftlands: Rare</v>
       </c>
       <c r="Q87" s="1" t="e">
         <f t="shared" si="34"/>
@@ -12995,7 +12996,7 @@
       </c>
       <c r="P88" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [87] = {["ID"] = 1879501179; }; -- The Rarest Bird of the Croftlands</v>
+        <v xml:space="preserve"> [87] = {["ID"] = 1879501179; ["TIER"] = 1; }; -- The Rarest Bird of the Croftlands</v>
       </c>
       <c r="Q88" s="1" t="e">
         <f t="shared" si="34"/>
@@ -13178,7 +13179,7 @@
       </c>
       <c r="AH89" t="str">
         <f t="shared" si="49"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI89" t="str">
         <f t="shared" si="50"/>
@@ -13217,7 +13218,7 @@
       </c>
       <c r="P90" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [89] = {["ID"] = 1879501182; }; -- Birds of the Entwash: Common and Uncommon</v>
+        <v xml:space="preserve"> [89] = {["ID"] = 1879501182; ["TIER"] = 1; }; -- Birds of the Entwash: Common and Uncommon</v>
       </c>
       <c r="Q90" s="1" t="e">
         <f t="shared" si="34"/>
@@ -13328,7 +13329,7 @@
       </c>
       <c r="P91" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [90] = {["ID"] = 1879501183; }; -- Birds of the Entwash: Rare</v>
+        <v xml:space="preserve"> [90] = {["ID"] = 1879501183; ["TIER"] = 1; }; -- Birds of the Entwash: Rare</v>
       </c>
       <c r="Q91" s="1" t="e">
         <f t="shared" si="34"/>
@@ -13439,7 +13440,7 @@
       </c>
       <c r="P92" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [91] = {["ID"] = 1879501184; }; -- The Rarest Bird of the Entwash</v>
+        <v xml:space="preserve"> [91] = {["ID"] = 1879501184; ["TIER"] = 1; }; -- The Rarest Bird of the Entwash</v>
       </c>
       <c r="Q92" s="1" t="e">
         <f t="shared" si="34"/>
@@ -13622,7 +13623,7 @@
       </c>
       <c r="AH93" t="str">
         <f t="shared" si="49"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI93" t="str">
         <f t="shared" si="50"/>
@@ -13661,7 +13662,7 @@
       </c>
       <c r="P94" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [93] = {["ID"] = 1879501189; }; -- Birds of the Westfold: Common and Uncommon</v>
+        <v xml:space="preserve"> [93] = {["ID"] = 1879501189; ["TIER"] = 1; }; -- Birds of the Westfold: Common and Uncommon</v>
       </c>
       <c r="Q94" s="1" t="e">
         <f t="shared" si="34"/>
@@ -13772,7 +13773,7 @@
       </c>
       <c r="P95" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [94] = {["ID"] = 1879501186; }; -- Birds of the Westfold: Rare</v>
+        <v xml:space="preserve"> [94] = {["ID"] = 1879501186; ["TIER"] = 1; }; -- Birds of the Westfold: Rare</v>
       </c>
       <c r="Q95" s="1" t="e">
         <f t="shared" si="34"/>
@@ -13883,7 +13884,7 @@
       </c>
       <c r="P96" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [95] = {["ID"] = 1879501187; }; -- The Rarest Bird in the Westfold</v>
+        <v xml:space="preserve"> [95] = {["ID"] = 1879501187; ["TIER"] = 1; }; -- The Rarest Bird in the Westfold</v>
       </c>
       <c r="Q96" s="1" t="e">
         <f t="shared" si="34"/>
@@ -14066,7 +14067,7 @@
       </c>
       <c r="AH97" t="str">
         <f t="shared" si="49"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI97" t="str">
         <f t="shared" si="50"/>
@@ -14105,7 +14106,7 @@
       </c>
       <c r="P98" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [97] = {["ID"] = 1879501190; }; -- Birds of the Eastfold: Common and Uncommon</v>
+        <v xml:space="preserve"> [97] = {["ID"] = 1879501190; ["TIER"] = 1; }; -- Birds of the Eastfold: Common and Uncommon</v>
       </c>
       <c r="Q98" s="1" t="e">
         <f t="shared" si="34"/>
@@ -14216,7 +14217,7 @@
       </c>
       <c r="P99" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [98] = {["ID"] = 1879501193; }; -- Birds of the Eastfold: Rare</v>
+        <v xml:space="preserve"> [98] = {["ID"] = 1879501193; ["TIER"] = 1; }; -- Birds of the Eastfold: Rare</v>
       </c>
       <c r="Q99" s="1" t="e">
         <f t="shared" si="34"/>
@@ -14327,7 +14328,7 @@
       </c>
       <c r="P100" t="str">
         <f t="shared" si="33"/>
-        <v xml:space="preserve"> [99] = {["ID"] = 1879501192; }; -- The Rarest Bird of the Eastfold</v>
+        <v xml:space="preserve"> [99] = {["ID"] = 1879501192; ["TIER"] = 1; }; -- The Rarest Bird of the Eastfold</v>
       </c>
       <c r="Q100" s="1" t="e">
         <f t="shared" si="34"/>
@@ -14510,7 +14511,7 @@
       </c>
       <c r="AH101" t="str">
         <f t="shared" si="49"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <v/>
       </c>
       <c r="AI101" t="str">
         <f t="shared" si="50"/>
@@ -14548,11 +14549,11 @@
         <v/>
       </c>
       <c r="P102" t="str">
-        <f t="shared" ref="P102:P140" si="55">CONCATENATE(S102,U102,V102,AM102," -- ",C102)</f>
+        <f t="shared" si="33"/>
         <v>[101] = {["CAT_ID"] = 326; }; -- Gondor and Mordor</v>
       </c>
       <c r="Q102" s="1" t="e">
-        <f t="shared" ref="Q102:Q140" si="56">CONCATENATE(S102,T102,W102,Y102,AA102,AC102,AE102,AG102,AH102,AI102,AJ102,AK102,AL102,AM102)</f>
+        <f t="shared" ref="Q102:Q140" si="55">CONCATENATE(S102,T102,W102,Y102,AA102,AC102,AE102,AG102,AH102,AI102,AJ102,AK102,AL102,AM102)</f>
         <v>#N/A</v>
       </c>
       <c r="R102">
@@ -14560,23 +14561,23 @@
         <v>101</v>
       </c>
       <c r="S102" t="str">
-        <f t="shared" ref="S102:S140" si="57">CONCATENATE(REPT(" ",3-LEN(R102)),"[",R102,"] = {")</f>
+        <f t="shared" ref="S102:S140" si="56">CONCATENATE(REPT(" ",3-LEN(R102)),"[",R102,"] = {")</f>
         <v>[101] = {</v>
       </c>
       <c r="T102" t="str">
-        <f t="shared" ref="T102:T140" si="58">IF(LEN(A102)&gt;0,CONCATENATE("[""ID""] = ",A102,"; "),"                     ")</f>
+        <f t="shared" ref="T102:T140" si="57">IF(LEN(A102)&gt;0,CONCATENATE("[""ID""] = ",A102,"; "),"                     ")</f>
         <v xml:space="preserve">                     </v>
       </c>
       <c r="U102" t="str">
-        <f t="shared" ref="U102:U140" si="59">IF(LEN(A102)&gt;0,CONCATENATE("[""ID""] = ",A102,"; "),"")</f>
+        <f t="shared" ref="U102:U140" si="58">IF(LEN(A102)&gt;0,CONCATENATE("[""ID""] = ",A102,"; "),"")</f>
         <v/>
       </c>
       <c r="V102" t="str">
-        <f t="shared" ref="V102:V140" si="60">IF(LEN(M102)&gt;0,CONCATENATE("[""CAT_ID""] = ",M102,"; "),"")</f>
+        <f t="shared" ref="V102:V140" si="59">IF(LEN(M102)&gt;0,CONCATENATE("[""CAT_ID""] = ",M102,"; "),"")</f>
         <v xml:space="preserve">["CAT_ID"] = 326; </v>
       </c>
       <c r="W102" s="1" t="str">
-        <f t="shared" ref="W102:W140" si="61">IF(LEN(B102)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B102)),B102,"; "),"")</f>
+        <f t="shared" ref="W102:W140" si="60">IF(LEN(B102)&gt;0,CONCATENATE("[""SAVE_INDEX""] = ",REPT(" ",1-LEN(B102)),B102,"; "),"")</f>
         <v/>
       </c>
       <c r="X102">
@@ -14584,31 +14585,31 @@
         <v>14</v>
       </c>
       <c r="Y102" t="str">
-        <f t="shared" ref="Y102:Y140" si="62">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(X102)),X102,"; ")</f>
+        <f t="shared" ref="Y102:Y140" si="61">CONCATENATE("[""TYPE""] = ",REPT(" ",2-LEN(X102)),X102,"; ")</f>
         <v xml:space="preserve">["TYPE"] = 14; </v>
       </c>
       <c r="Z102" t="str">
-        <f t="shared" ref="Z102:Z140" si="63">TEXT(E102,0)</f>
+        <f t="shared" ref="Z102:Z140" si="62">TEXT(E102,0)</f>
         <v>0</v>
       </c>
       <c r="AA102" t="str">
-        <f t="shared" ref="AA102:AA140" si="64">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(Z102)),TEXT(Z102,"0"),"; ")</f>
+        <f t="shared" ref="AA102:AA140" si="63">CONCATENATE("[""VXP""] = ",REPT(" ",1-LEN(Z102)),TEXT(Z102,"0"),"; ")</f>
         <v xml:space="preserve">["VXP"] = 0; </v>
       </c>
       <c r="AB102" t="str">
-        <f t="shared" ref="AB102:AB140" si="65">TEXT(G102,0)</f>
+        <f t="shared" ref="AB102:AB140" si="64">TEXT(G102,0)</f>
         <v>0</v>
       </c>
       <c r="AC102" t="str">
-        <f t="shared" ref="AC102:AC140" si="66">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AB102)),TEXT(AB102,"0"),"; ")</f>
+        <f t="shared" ref="AC102:AC140" si="65">CONCATENATE("[""LP""] = ",REPT(" ",1-LEN(AB102)),TEXT(AB102,"0"),"; ")</f>
         <v xml:space="preserve">["LP"] = 0; </v>
       </c>
       <c r="AD102" t="str">
-        <f t="shared" ref="AD102:AD140" si="67">TEXT(H102,0)</f>
+        <f t="shared" ref="AD102:AD140" si="66">TEXT(H102,0)</f>
         <v>0</v>
       </c>
       <c r="AE102" t="str">
-        <f t="shared" ref="AE102:AE140" si="68">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AD102)),TEXT(AD102,"0"),"; ")</f>
+        <f t="shared" ref="AE102:AE140" si="67">CONCATENATE("[""REP""] = ",REPT(" ",1-LEN(AD102)),TEXT(AD102,"0"),"; ")</f>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF102" t="e">
@@ -14616,27 +14617,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG102" t="e">
-        <f t="shared" ref="AG102:AG140" si="69">CONCATENATE("[""FACTION""] = ",TEXT(AF102,"0"),"; ")</f>
+        <f t="shared" ref="AG102:AG140" si="68">CONCATENATE("[""FACTION""] = ",TEXT(AF102,"0"),"; ")</f>
         <v>#N/A</v>
       </c>
       <c r="AH102" t="str">
-        <f t="shared" ref="AH102:AH140" si="70">CONCATENATE("[""TIER""] = ",TEXT(L102,"0"),"; ")</f>
-        <v xml:space="preserve">["TIER"] = 0; </v>
+        <f t="shared" si="49"/>
+        <v/>
       </c>
       <c r="AI102" t="str">
-        <f t="shared" ref="AI102:AI140" si="71">CONCATENATE("[""NAME""] = { [""EN""] = """,C102,"""; }; ")</f>
+        <f t="shared" ref="AI102:AI140" si="69">CONCATENATE("[""NAME""] = { [""EN""] = """,C102,"""; }; ")</f>
         <v xml:space="preserve">["NAME"] = { ["EN"] = "Gondor and Mordor"; }; </v>
       </c>
       <c r="AJ102" t="str">
-        <f t="shared" ref="AJ102:AJ140" si="72">CONCATENATE("[""LORE""] = { [""EN""] = """,K102,"""; }; ")</f>
+        <f t="shared" ref="AJ102:AJ140" si="70">CONCATENATE("[""LORE""] = { [""EN""] = """,K102,"""; }; ")</f>
         <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AK102" t="str">
-        <f t="shared" ref="AK102:AK140" si="73">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,J102,"""; }; ")</f>
+        <f t="shared" ref="AK102:AK140" si="71">CONCATENATE("[""SUMMARY""] = { [""EN""] = """,J102,"""; }; ")</f>
         <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
       </c>
       <c r="AL102" t="str">
-        <f t="shared" ref="AL102:AL140" si="74">IF(LEN(F102)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,F102,"""; }; "),"")</f>
+        <f t="shared" ref="AL102:AL140" si="72">IF(LEN(F102)&gt;0,CONCATENATE("[""TITLE""] = { [""EN""] = """,F102,"""; }; "),"")</f>
         <v/>
       </c>
       <c r="AM102" t="str">
@@ -14659,11 +14660,11 @@
         <v/>
       </c>
       <c r="P103" t="str">
+        <f t="shared" si="33"/>
+        <v>[102] = {["ID"] = 1879507928; }; -- All the Birds of Lamedon</v>
+      </c>
+      <c r="Q103" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[102] = {["ID"] = 1879507928; }; -- All the Birds of Lamedon</v>
-      </c>
-      <c r="Q103" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R103">
@@ -14671,23 +14672,23 @@
         <v>102</v>
       </c>
       <c r="S103" t="str">
+        <f t="shared" si="56"/>
+        <v>[102] = {</v>
+      </c>
+      <c r="T103" t="str">
         <f t="shared" si="57"/>
-        <v>[102] = {</v>
-      </c>
-      <c r="T103" t="str">
+        <v xml:space="preserve">["ID"] = 1879507928; </v>
+      </c>
+      <c r="U103" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507928; </v>
       </c>
-      <c r="U103" t="str">
+      <c r="V103" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507928; </v>
-      </c>
-      <c r="V103" t="str">
+        <v/>
+      </c>
+      <c r="W103" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W103" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X103" t="e">
@@ -14695,31 +14696,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y103" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z103" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z103" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA103" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA103" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB103" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB103" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC103" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD103" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD103" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE103" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF103" t="e">
@@ -14727,27 +14728,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG103" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH103" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="AI103" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH103" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Lamedon"; }; </v>
+      </c>
+      <c r="AJ103" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI103" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK103" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Lamedon"; }; </v>
-      </c>
-      <c r="AJ103" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL103" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK103" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL103" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM103" t="str">
@@ -14770,11 +14771,11 @@
         <v>[1879507930] = 1, // Birds of Lamedon: Common and Uncommon</v>
       </c>
       <c r="P104" t="str">
+        <f t="shared" si="33"/>
+        <v>[103] = {["ID"] = 1879507930; ["TIER"] = 1; }; -- Birds of Lamedon: Common and Uncommon</v>
+      </c>
+      <c r="Q104" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[103] = {["ID"] = 1879507930; }; -- Birds of Lamedon: Common and Uncommon</v>
-      </c>
-      <c r="Q104" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R104">
@@ -14782,23 +14783,23 @@
         <v>103</v>
       </c>
       <c r="S104" t="str">
+        <f t="shared" si="56"/>
+        <v>[103] = {</v>
+      </c>
+      <c r="T104" t="str">
         <f t="shared" si="57"/>
-        <v>[103] = {</v>
-      </c>
-      <c r="T104" t="str">
+        <v xml:space="preserve">["ID"] = 1879507930; </v>
+      </c>
+      <c r="U104" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507930; </v>
       </c>
-      <c r="U104" t="str">
+      <c r="V104" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507930; </v>
-      </c>
-      <c r="V104" t="str">
+        <v/>
+      </c>
+      <c r="W104" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W104" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X104" t="e">
@@ -14806,31 +14807,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y104" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z104" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z104" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA104" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB104" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB104" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC104" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD104" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD104" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE104" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF104" t="e">
@@ -14838,27 +14839,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG104" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH104" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI104" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH104" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lamedon: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AJ104" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI104" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK104" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lamedon: Common and Uncommon"; }; </v>
-      </c>
-      <c r="AJ104" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL104" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK104" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL104" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM104" t="str">
@@ -14881,11 +14882,11 @@
         <v>[1879507929] = 1, // Birds of Lamedon: Rare</v>
       </c>
       <c r="P105" t="str">
+        <f t="shared" si="33"/>
+        <v>[104] = {["ID"] = 1879507929; ["TIER"] = 1; }; -- Birds of Lamedon: Rare</v>
+      </c>
+      <c r="Q105" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[104] = {["ID"] = 1879507929; }; -- Birds of Lamedon: Rare</v>
-      </c>
-      <c r="Q105" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R105">
@@ -14893,23 +14894,23 @@
         <v>104</v>
       </c>
       <c r="S105" t="str">
+        <f t="shared" si="56"/>
+        <v>[104] = {</v>
+      </c>
+      <c r="T105" t="str">
         <f t="shared" si="57"/>
-        <v>[104] = {</v>
-      </c>
-      <c r="T105" t="str">
+        <v xml:space="preserve">["ID"] = 1879507929; </v>
+      </c>
+      <c r="U105" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507929; </v>
       </c>
-      <c r="U105" t="str">
+      <c r="V105" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507929; </v>
-      </c>
-      <c r="V105" t="str">
+        <v/>
+      </c>
+      <c r="W105" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W105" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X105" t="e">
@@ -14917,31 +14918,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y105" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z105" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z105" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA105" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB105" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB105" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC105" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD105" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD105" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE105" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF105" t="e">
@@ -14949,27 +14950,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG105" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH105" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI105" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH105" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lamedon: Rare"; }; </v>
+      </c>
+      <c r="AJ105" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI105" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK105" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lamedon: Rare"; }; </v>
-      </c>
-      <c r="AJ105" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL105" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK105" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL105" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM105" t="str">
@@ -14992,11 +14993,11 @@
         <v>[1879507926] = 1, // The Rarest Bird in Lamedon</v>
       </c>
       <c r="P106" t="str">
+        <f t="shared" si="33"/>
+        <v>[105] = {["ID"] = 1879507926; ["TIER"] = 1; }; -- The Rarest Bird in Lamedon</v>
+      </c>
+      <c r="Q106" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[105] = {["ID"] = 1879507926; }; -- The Rarest Bird in Lamedon</v>
-      </c>
-      <c r="Q106" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R106">
@@ -15004,23 +15005,23 @@
         <v>105</v>
       </c>
       <c r="S106" t="str">
+        <f t="shared" si="56"/>
+        <v>[105] = {</v>
+      </c>
+      <c r="T106" t="str">
         <f t="shared" si="57"/>
-        <v>[105] = {</v>
-      </c>
-      <c r="T106" t="str">
+        <v xml:space="preserve">["ID"] = 1879507926; </v>
+      </c>
+      <c r="U106" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507926; </v>
       </c>
-      <c r="U106" t="str">
+      <c r="V106" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507926; </v>
-      </c>
-      <c r="V106" t="str">
+        <v/>
+      </c>
+      <c r="W106" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W106" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X106" t="e">
@@ -15028,31 +15029,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y106" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z106" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z106" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA106" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB106" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB106" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC106" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD106" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD106" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE106" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF106" t="e">
@@ -15060,27 +15061,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG106" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH106" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI106" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH106" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Lamedon"; }; </v>
+      </c>
+      <c r="AJ106" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI106" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK106" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Lamedon"; }; </v>
-      </c>
-      <c r="AJ106" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL106" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK106" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL106" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM106" t="str">
@@ -15103,11 +15104,11 @@
         <v/>
       </c>
       <c r="P107" t="str">
+        <f t="shared" si="33"/>
+        <v>[106] = {["ID"] = 1879507927; }; -- All the Birds of Belfalas</v>
+      </c>
+      <c r="Q107" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[106] = {["ID"] = 1879507927; }; -- All the Birds of Belfalas</v>
-      </c>
-      <c r="Q107" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R107">
@@ -15115,23 +15116,23 @@
         <v>106</v>
       </c>
       <c r="S107" t="str">
+        <f t="shared" si="56"/>
+        <v>[106] = {</v>
+      </c>
+      <c r="T107" t="str">
         <f t="shared" si="57"/>
-        <v>[106] = {</v>
-      </c>
-      <c r="T107" t="str">
+        <v xml:space="preserve">["ID"] = 1879507927; </v>
+      </c>
+      <c r="U107" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507927; </v>
       </c>
-      <c r="U107" t="str">
+      <c r="V107" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507927; </v>
-      </c>
-      <c r="V107" t="str">
+        <v/>
+      </c>
+      <c r="W107" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W107" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X107" t="e">
@@ -15139,31 +15140,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y107" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z107" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z107" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA107" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB107" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB107" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC107" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD107" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD107" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE107" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF107" t="e">
@@ -15171,27 +15172,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG107" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH107" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="AI107" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH107" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Belfalas"; }; </v>
+      </c>
+      <c r="AJ107" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI107" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK107" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Belfalas"; }; </v>
-      </c>
-      <c r="AJ107" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL107" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK107" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL107" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM107" t="str">
@@ -15214,11 +15215,11 @@
         <v>[1879507924] = 1, // Birds of Belfalas: Common and Uncommon</v>
       </c>
       <c r="P108" t="str">
+        <f t="shared" si="33"/>
+        <v>[107] = {["ID"] = 1879507924; ["TIER"] = 1; }; -- Birds of Belfalas: Common and Uncommon</v>
+      </c>
+      <c r="Q108" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[107] = {["ID"] = 1879507924; }; -- Birds of Belfalas: Common and Uncommon</v>
-      </c>
-      <c r="Q108" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R108">
@@ -15226,23 +15227,23 @@
         <v>107</v>
       </c>
       <c r="S108" t="str">
+        <f t="shared" si="56"/>
+        <v>[107] = {</v>
+      </c>
+      <c r="T108" t="str">
         <f t="shared" si="57"/>
-        <v>[107] = {</v>
-      </c>
-      <c r="T108" t="str">
+        <v xml:space="preserve">["ID"] = 1879507924; </v>
+      </c>
+      <c r="U108" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507924; </v>
       </c>
-      <c r="U108" t="str">
+      <c r="V108" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507924; </v>
-      </c>
-      <c r="V108" t="str">
+        <v/>
+      </c>
+      <c r="W108" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W108" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X108" t="e">
@@ -15250,31 +15251,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y108" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z108" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z108" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA108" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB108" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB108" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC108" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD108" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD108" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE108" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF108" t="e">
@@ -15282,27 +15283,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG108" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH108" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI108" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH108" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Belfalas: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AJ108" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI108" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK108" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Belfalas: Common and Uncommon"; }; </v>
-      </c>
-      <c r="AJ108" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL108" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK108" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL108" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM108" t="str">
@@ -15325,11 +15326,11 @@
         <v>[1879507923] = 1, // Birds of Belfalas: Rare</v>
       </c>
       <c r="P109" t="str">
+        <f t="shared" si="33"/>
+        <v>[108] = {["ID"] = 1879507923; ["TIER"] = 1; }; -- Birds of Belfalas: Rare</v>
+      </c>
+      <c r="Q109" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[108] = {["ID"] = 1879507923; }; -- Birds of Belfalas: Rare</v>
-      </c>
-      <c r="Q109" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R109">
@@ -15337,23 +15338,23 @@
         <v>108</v>
       </c>
       <c r="S109" t="str">
+        <f t="shared" si="56"/>
+        <v>[108] = {</v>
+      </c>
+      <c r="T109" t="str">
         <f t="shared" si="57"/>
-        <v>[108] = {</v>
-      </c>
-      <c r="T109" t="str">
+        <v xml:space="preserve">["ID"] = 1879507923; </v>
+      </c>
+      <c r="U109" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507923; </v>
       </c>
-      <c r="U109" t="str">
+      <c r="V109" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507923; </v>
-      </c>
-      <c r="V109" t="str">
+        <v/>
+      </c>
+      <c r="W109" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W109" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X109" t="e">
@@ -15361,31 +15362,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y109" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z109" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z109" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA109" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA109" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB109" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB109" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC109" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD109" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD109" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE109" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF109" t="e">
@@ -15393,27 +15394,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG109" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH109" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI109" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH109" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Belfalas: Rare"; }; </v>
+      </c>
+      <c r="AJ109" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI109" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK109" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Belfalas: Rare"; }; </v>
-      </c>
-      <c r="AJ109" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL109" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK109" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL109" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM109" t="str">
@@ -15436,11 +15437,11 @@
         <v>[1879507925] = 1, // The Rarest Bird in Belfalas</v>
       </c>
       <c r="P110" t="str">
+        <f t="shared" si="33"/>
+        <v>[109] = {["ID"] = 1879507925; ["TIER"] = 1; }; -- The Rarest Bird in Belfalas</v>
+      </c>
+      <c r="Q110" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[109] = {["ID"] = 1879507925; }; -- The Rarest Bird in Belfalas</v>
-      </c>
-      <c r="Q110" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R110">
@@ -15448,23 +15449,23 @@
         <v>109</v>
       </c>
       <c r="S110" t="str">
+        <f t="shared" si="56"/>
+        <v>[109] = {</v>
+      </c>
+      <c r="T110" t="str">
         <f t="shared" si="57"/>
-        <v>[109] = {</v>
-      </c>
-      <c r="T110" t="str">
+        <v xml:space="preserve">["ID"] = 1879507925; </v>
+      </c>
+      <c r="U110" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507925; </v>
       </c>
-      <c r="U110" t="str">
+      <c r="V110" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507925; </v>
-      </c>
-      <c r="V110" t="str">
+        <v/>
+      </c>
+      <c r="W110" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W110" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X110" t="e">
@@ -15472,31 +15473,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y110" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z110" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z110" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA110" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA110" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB110" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB110" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC110" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD110" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD110" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE110" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF110" t="e">
@@ -15504,27 +15505,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG110" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH110" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI110" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH110" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Belfalas"; }; </v>
+      </c>
+      <c r="AJ110" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI110" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK110" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Belfalas"; }; </v>
-      </c>
-      <c r="AJ110" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL110" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK110" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL110" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM110" t="str">
@@ -15547,11 +15548,11 @@
         <v/>
       </c>
       <c r="P111" t="str">
+        <f t="shared" si="33"/>
+        <v>[110] = {["ID"] = 1879507885; }; -- All the Birds of Lebennin</v>
+      </c>
+      <c r="Q111" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[110] = {["ID"] = 1879507885; }; -- All the Birds of Lebennin</v>
-      </c>
-      <c r="Q111" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R111">
@@ -15559,23 +15560,23 @@
         <v>110</v>
       </c>
       <c r="S111" t="str">
+        <f t="shared" si="56"/>
+        <v>[110] = {</v>
+      </c>
+      <c r="T111" t="str">
         <f t="shared" si="57"/>
-        <v>[110] = {</v>
-      </c>
-      <c r="T111" t="str">
+        <v xml:space="preserve">["ID"] = 1879507885; </v>
+      </c>
+      <c r="U111" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507885; </v>
       </c>
-      <c r="U111" t="str">
+      <c r="V111" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507885; </v>
-      </c>
-      <c r="V111" t="str">
+        <v/>
+      </c>
+      <c r="W111" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W111" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X111" t="e">
@@ -15583,31 +15584,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y111" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z111" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z111" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA111" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB111" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB111" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC111" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD111" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD111" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE111" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF111" t="e">
@@ -15615,27 +15616,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG111" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH111" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="AI111" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH111" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Lebennin"; }; </v>
+      </c>
+      <c r="AJ111" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI111" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK111" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Lebennin"; }; </v>
-      </c>
-      <c r="AJ111" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL111" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK111" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL111" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM111" t="str">
@@ -15658,11 +15659,11 @@
         <v>[1879507884] = 1, // Birds of Lebennin: Common and Uncommon</v>
       </c>
       <c r="P112" t="str">
+        <f t="shared" si="33"/>
+        <v>[111] = {["ID"] = 1879507884; ["TIER"] = 1; }; -- Birds of Lebennin: Common and Uncommon</v>
+      </c>
+      <c r="Q112" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[111] = {["ID"] = 1879507884; }; -- Birds of Lebennin: Common and Uncommon</v>
-      </c>
-      <c r="Q112" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R112">
@@ -15670,23 +15671,23 @@
         <v>111</v>
       </c>
       <c r="S112" t="str">
+        <f t="shared" si="56"/>
+        <v>[111] = {</v>
+      </c>
+      <c r="T112" t="str">
         <f t="shared" si="57"/>
-        <v>[111] = {</v>
-      </c>
-      <c r="T112" t="str">
+        <v xml:space="preserve">["ID"] = 1879507884; </v>
+      </c>
+      <c r="U112" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507884; </v>
       </c>
-      <c r="U112" t="str">
+      <c r="V112" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507884; </v>
-      </c>
-      <c r="V112" t="str">
+        <v/>
+      </c>
+      <c r="W112" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W112" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X112" t="e">
@@ -15694,31 +15695,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y112" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z112" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z112" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA112" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA112" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB112" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB112" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC112" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD112" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD112" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE112" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF112" t="e">
@@ -15726,27 +15727,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG112" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH112" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI112" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH112" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lebennin: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AJ112" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI112" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK112" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lebennin: Common and Uncommon"; }; </v>
-      </c>
-      <c r="AJ112" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL112" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK112" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL112" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM112" t="str">
@@ -15769,11 +15770,11 @@
         <v>[1879507880] = 1, // Birds of Lebennin: Rare</v>
       </c>
       <c r="P113" t="str">
+        <f t="shared" si="33"/>
+        <v>[112] = {["ID"] = 1879507880; ["TIER"] = 1; }; -- Birds of Lebennin: Rare</v>
+      </c>
+      <c r="Q113" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[112] = {["ID"] = 1879507880; }; -- Birds of Lebennin: Rare</v>
-      </c>
-      <c r="Q113" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R113">
@@ -15781,23 +15782,23 @@
         <v>112</v>
       </c>
       <c r="S113" t="str">
+        <f t="shared" si="56"/>
+        <v>[112] = {</v>
+      </c>
+      <c r="T113" t="str">
         <f t="shared" si="57"/>
-        <v>[112] = {</v>
-      </c>
-      <c r="T113" t="str">
+        <v xml:space="preserve">["ID"] = 1879507880; </v>
+      </c>
+      <c r="U113" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507880; </v>
       </c>
-      <c r="U113" t="str">
+      <c r="V113" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507880; </v>
-      </c>
-      <c r="V113" t="str">
+        <v/>
+      </c>
+      <c r="W113" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W113" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X113" t="e">
@@ -15805,31 +15806,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y113" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z113" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z113" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA113" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA113" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB113" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB113" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC113" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD113" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD113" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE113" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF113" t="e">
@@ -15837,27 +15838,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG113" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH113" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI113" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH113" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lebennin: Rare"; }; </v>
+      </c>
+      <c r="AJ113" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI113" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK113" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lebennin: Rare"; }; </v>
-      </c>
-      <c r="AJ113" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL113" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK113" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL113" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM113" t="str">
@@ -15880,11 +15881,11 @@
         <v>[1879507883] = 1, // The Rarest Bird in Lebennin</v>
       </c>
       <c r="P114" t="str">
+        <f t="shared" si="33"/>
+        <v>[113] = {["ID"] = 1879507883; ["TIER"] = 1; }; -- The Rarest Bird in Lebennin</v>
+      </c>
+      <c r="Q114" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[113] = {["ID"] = 1879507883; }; -- The Rarest Bird in Lebennin</v>
-      </c>
-      <c r="Q114" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R114">
@@ -15892,23 +15893,23 @@
         <v>113</v>
       </c>
       <c r="S114" t="str">
+        <f t="shared" si="56"/>
+        <v>[113] = {</v>
+      </c>
+      <c r="T114" t="str">
         <f t="shared" si="57"/>
-        <v>[113] = {</v>
-      </c>
-      <c r="T114" t="str">
+        <v xml:space="preserve">["ID"] = 1879507883; </v>
+      </c>
+      <c r="U114" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507883; </v>
       </c>
-      <c r="U114" t="str">
+      <c r="V114" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507883; </v>
-      </c>
-      <c r="V114" t="str">
+        <v/>
+      </c>
+      <c r="W114" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W114" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X114" t="e">
@@ -15916,31 +15917,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y114" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z114" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z114" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA114" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA114" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB114" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB114" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC114" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD114" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD114" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE114" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF114" t="e">
@@ -15948,27 +15949,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG114" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH114" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI114" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH114" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Lebennin"; }; </v>
+      </c>
+      <c r="AJ114" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI114" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK114" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Lebennin"; }; </v>
-      </c>
-      <c r="AJ114" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL114" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK114" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL114" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM114" t="str">
@@ -15991,11 +15992,11 @@
         <v/>
       </c>
       <c r="P115" t="str">
+        <f t="shared" si="33"/>
+        <v>[114] = {["ID"] = 1879507881; }; -- All the Birds of Lossarnach</v>
+      </c>
+      <c r="Q115" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[114] = {["ID"] = 1879507881; }; -- All the Birds of Lossarnach</v>
-      </c>
-      <c r="Q115" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R115">
@@ -16003,23 +16004,23 @@
         <v>114</v>
       </c>
       <c r="S115" t="str">
+        <f t="shared" si="56"/>
+        <v>[114] = {</v>
+      </c>
+      <c r="T115" t="str">
         <f t="shared" si="57"/>
-        <v>[114] = {</v>
-      </c>
-      <c r="T115" t="str">
+        <v xml:space="preserve">["ID"] = 1879507881; </v>
+      </c>
+      <c r="U115" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507881; </v>
       </c>
-      <c r="U115" t="str">
+      <c r="V115" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507881; </v>
-      </c>
-      <c r="V115" t="str">
+        <v/>
+      </c>
+      <c r="W115" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W115" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X115" t="e">
@@ -16027,31 +16028,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y115" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z115" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z115" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA115" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA115" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB115" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB115" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC115" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD115" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD115" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE115" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF115" t="e">
@@ -16059,27 +16060,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG115" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH115" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="AI115" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH115" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Lossarnach"; }; </v>
+      </c>
+      <c r="AJ115" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI115" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK115" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Lossarnach"; }; </v>
-      </c>
-      <c r="AJ115" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL115" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK115" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL115" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM115" t="str">
@@ -16102,11 +16103,11 @@
         <v>[1879507879] = 1, // Birds of Lossarnach: Common and Uncommon</v>
       </c>
       <c r="P116" t="str">
+        <f t="shared" si="33"/>
+        <v>[115] = {["ID"] = 1879507879; ["TIER"] = 1; }; -- Birds of Lossarnach: Common and Uncommon</v>
+      </c>
+      <c r="Q116" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[115] = {["ID"] = 1879507879; }; -- Birds of Lossarnach: Common and Uncommon</v>
-      </c>
-      <c r="Q116" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R116">
@@ -16114,23 +16115,23 @@
         <v>115</v>
       </c>
       <c r="S116" t="str">
+        <f t="shared" si="56"/>
+        <v>[115] = {</v>
+      </c>
+      <c r="T116" t="str">
         <f t="shared" si="57"/>
-        <v>[115] = {</v>
-      </c>
-      <c r="T116" t="str">
+        <v xml:space="preserve">["ID"] = 1879507879; </v>
+      </c>
+      <c r="U116" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507879; </v>
       </c>
-      <c r="U116" t="str">
+      <c r="V116" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507879; </v>
-      </c>
-      <c r="V116" t="str">
+        <v/>
+      </c>
+      <c r="W116" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W116" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X116" t="e">
@@ -16138,31 +16139,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y116" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z116" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z116" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA116" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA116" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB116" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB116" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC116" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC116" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD116" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD116" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE116" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF116" t="e">
@@ -16170,27 +16171,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG116" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH116" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI116" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH116" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lossarnach: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AJ116" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI116" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK116" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lossarnach: Common and Uncommon"; }; </v>
-      </c>
-      <c r="AJ116" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL116" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK116" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL116" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM116" t="str">
@@ -16213,11 +16214,11 @@
         <v>[1879507882] = 1, // Birds of Lossarnach: Rare</v>
       </c>
       <c r="P117" t="str">
+        <f t="shared" si="33"/>
+        <v>[116] = {["ID"] = 1879507882; ["TIER"] = 1; }; -- Birds of Lossarnach: Rare</v>
+      </c>
+      <c r="Q117" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[116] = {["ID"] = 1879507882; }; -- Birds of Lossarnach: Rare</v>
-      </c>
-      <c r="Q117" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R117">
@@ -16225,23 +16226,23 @@
         <v>116</v>
       </c>
       <c r="S117" t="str">
+        <f t="shared" si="56"/>
+        <v>[116] = {</v>
+      </c>
+      <c r="T117" t="str">
         <f t="shared" si="57"/>
-        <v>[116] = {</v>
-      </c>
-      <c r="T117" t="str">
+        <v xml:space="preserve">["ID"] = 1879507882; </v>
+      </c>
+      <c r="U117" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507882; </v>
       </c>
-      <c r="U117" t="str">
+      <c r="V117" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507882; </v>
-      </c>
-      <c r="V117" t="str">
+        <v/>
+      </c>
+      <c r="W117" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W117" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X117" t="e">
@@ -16249,31 +16250,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y117" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z117" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z117" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA117" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA117" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB117" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB117" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC117" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC117" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD117" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD117" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE117" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF117" t="e">
@@ -16281,27 +16282,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG117" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH117" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI117" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH117" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lossarnach: Rare"; }; </v>
+      </c>
+      <c r="AJ117" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI117" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK117" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lossarnach: Rare"; }; </v>
-      </c>
-      <c r="AJ117" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL117" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK117" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL117" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM117" t="str">
@@ -16324,11 +16325,11 @@
         <v>[1879507886] = 1, // The Rarest Bird in Lossarnach</v>
       </c>
       <c r="P118" t="str">
+        <f t="shared" si="33"/>
+        <v>[117] = {["ID"] = 1879507886; ["TIER"] = 1; }; -- The Rarest Bird in Lossarnach</v>
+      </c>
+      <c r="Q118" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[117] = {["ID"] = 1879507886; }; -- The Rarest Bird in Lossarnach</v>
-      </c>
-      <c r="Q118" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R118">
@@ -16336,23 +16337,23 @@
         <v>117</v>
       </c>
       <c r="S118" t="str">
+        <f t="shared" si="56"/>
+        <v>[117] = {</v>
+      </c>
+      <c r="T118" t="str">
         <f t="shared" si="57"/>
-        <v>[117] = {</v>
-      </c>
-      <c r="T118" t="str">
+        <v xml:space="preserve">["ID"] = 1879507886; </v>
+      </c>
+      <c r="U118" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507886; </v>
       </c>
-      <c r="U118" t="str">
+      <c r="V118" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507886; </v>
-      </c>
-      <c r="V118" t="str">
+        <v/>
+      </c>
+      <c r="W118" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W118" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X118" t="e">
@@ -16360,31 +16361,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y118" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z118" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z118" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA118" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB118" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB118" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC118" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD118" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD118" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE118" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF118" t="e">
@@ -16392,27 +16393,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG118" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH118" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI118" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH118" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Lossarnach"; }; </v>
+      </c>
+      <c r="AJ118" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI118" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK118" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Lossarnach"; }; </v>
-      </c>
-      <c r="AJ118" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL118" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK118" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL118" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM118" t="str">
@@ -16435,11 +16436,11 @@
         <v/>
       </c>
       <c r="P119" t="str">
+        <f t="shared" si="33"/>
+        <v>[118] = {["ID"] = 1879507873; }; -- All the Birds of Ithilien</v>
+      </c>
+      <c r="Q119" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[118] = {["ID"] = 1879507873; }; -- All the Birds of Ithilien</v>
-      </c>
-      <c r="Q119" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R119">
@@ -16447,23 +16448,23 @@
         <v>118</v>
       </c>
       <c r="S119" t="str">
+        <f t="shared" si="56"/>
+        <v>[118] = {</v>
+      </c>
+      <c r="T119" t="str">
         <f t="shared" si="57"/>
-        <v>[118] = {</v>
-      </c>
-      <c r="T119" t="str">
+        <v xml:space="preserve">["ID"] = 1879507873; </v>
+      </c>
+      <c r="U119" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507873; </v>
       </c>
-      <c r="U119" t="str">
+      <c r="V119" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507873; </v>
-      </c>
-      <c r="V119" t="str">
+        <v/>
+      </c>
+      <c r="W119" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W119" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X119" t="e">
@@ -16471,31 +16472,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y119" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z119" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z119" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA119" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA119" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB119" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB119" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC119" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD119" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD119" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE119" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF119" t="e">
@@ -16503,27 +16504,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG119" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH119" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="AI119" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH119" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Ithilien"; }; </v>
+      </c>
+      <c r="AJ119" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI119" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK119" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Ithilien"; }; </v>
-      </c>
-      <c r="AJ119" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL119" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK119" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL119" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM119" t="str">
@@ -16546,11 +16547,11 @@
         <v>[1879507872] = 1, // Birds of Ithilien: Common and Uncommon</v>
       </c>
       <c r="P120" t="str">
+        <f t="shared" si="33"/>
+        <v>[119] = {["ID"] = 1879507872; ["TIER"] = 1; }; -- Birds of Ithilien: Common and Uncommon</v>
+      </c>
+      <c r="Q120" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[119] = {["ID"] = 1879507872; }; -- Birds of Ithilien: Common and Uncommon</v>
-      </c>
-      <c r="Q120" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R120">
@@ -16558,23 +16559,23 @@
         <v>119</v>
       </c>
       <c r="S120" t="str">
+        <f t="shared" si="56"/>
+        <v>[119] = {</v>
+      </c>
+      <c r="T120" t="str">
         <f t="shared" si="57"/>
-        <v>[119] = {</v>
-      </c>
-      <c r="T120" t="str">
+        <v xml:space="preserve">["ID"] = 1879507872; </v>
+      </c>
+      <c r="U120" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507872; </v>
       </c>
-      <c r="U120" t="str">
+      <c r="V120" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507872; </v>
-      </c>
-      <c r="V120" t="str">
+        <v/>
+      </c>
+      <c r="W120" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W120" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X120" t="e">
@@ -16582,31 +16583,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y120" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z120" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z120" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA120" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB120" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB120" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC120" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD120" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD120" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE120" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF120" t="e">
@@ -16614,27 +16615,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG120" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH120" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI120" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH120" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Ithilien: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AJ120" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI120" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK120" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Ithilien: Common and Uncommon"; }; </v>
-      </c>
-      <c r="AJ120" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL120" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK120" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL120" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM120" t="str">
@@ -16657,11 +16658,11 @@
         <v>[1879507877] = 1, // Birds of Ithilien: Rare</v>
       </c>
       <c r="P121" t="str">
+        <f t="shared" si="33"/>
+        <v>[120] = {["ID"] = 1879507877; ["TIER"] = 1; }; -- Birds of Ithilien: Rare</v>
+      </c>
+      <c r="Q121" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[120] = {["ID"] = 1879507877; }; -- Birds of Ithilien: Rare</v>
-      </c>
-      <c r="Q121" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R121">
@@ -16669,23 +16670,23 @@
         <v>120</v>
       </c>
       <c r="S121" t="str">
+        <f t="shared" si="56"/>
+        <v>[120] = {</v>
+      </c>
+      <c r="T121" t="str">
         <f t="shared" si="57"/>
-        <v>[120] = {</v>
-      </c>
-      <c r="T121" t="str">
+        <v xml:space="preserve">["ID"] = 1879507877; </v>
+      </c>
+      <c r="U121" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507877; </v>
       </c>
-      <c r="U121" t="str">
+      <c r="V121" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507877; </v>
-      </c>
-      <c r="V121" t="str">
+        <v/>
+      </c>
+      <c r="W121" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W121" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X121" t="e">
@@ -16693,31 +16694,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y121" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z121" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z121" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA121" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB121" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB121" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC121" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD121" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD121" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE121" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF121" t="e">
@@ -16725,27 +16726,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG121" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH121" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI121" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH121" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Ithilien: Rare"; }; </v>
+      </c>
+      <c r="AJ121" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI121" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK121" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Ithilien: Rare"; }; </v>
-      </c>
-      <c r="AJ121" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL121" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK121" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL121" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM121" t="str">
@@ -16768,11 +16769,11 @@
         <v>[1879507871] = 1, // The Rarest Bird in Ithilien</v>
       </c>
       <c r="P122" t="str">
+        <f t="shared" si="33"/>
+        <v>[121] = {["ID"] = 1879507871; ["TIER"] = 1; }; -- The Rarest Bird in Ithilien</v>
+      </c>
+      <c r="Q122" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[121] = {["ID"] = 1879507871; }; -- The Rarest Bird in Ithilien</v>
-      </c>
-      <c r="Q122" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R122">
@@ -16780,23 +16781,23 @@
         <v>121</v>
       </c>
       <c r="S122" t="str">
+        <f t="shared" si="56"/>
+        <v>[121] = {</v>
+      </c>
+      <c r="T122" t="str">
         <f t="shared" si="57"/>
-        <v>[121] = {</v>
-      </c>
-      <c r="T122" t="str">
+        <v xml:space="preserve">["ID"] = 1879507871; </v>
+      </c>
+      <c r="U122" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507871; </v>
       </c>
-      <c r="U122" t="str">
+      <c r="V122" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507871; </v>
-      </c>
-      <c r="V122" t="str">
+        <v/>
+      </c>
+      <c r="W122" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W122" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X122" t="e">
@@ -16804,31 +16805,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y122" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z122" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z122" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA122" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB122" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB122" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC122" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD122" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD122" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE122" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF122" t="e">
@@ -16836,27 +16837,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG122" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH122" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI122" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH122" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Ithilien"; }; </v>
+      </c>
+      <c r="AJ122" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI122" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK122" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Ithilien"; }; </v>
-      </c>
-      <c r="AJ122" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL122" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK122" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL122" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM122" t="str">
@@ -16879,11 +16880,11 @@
         <v/>
       </c>
       <c r="P123" t="str">
+        <f t="shared" si="33"/>
+        <v>[122] = {["ID"] = 1879507875; }; -- All the Birds of Anórien</v>
+      </c>
+      <c r="Q123" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[122] = {["ID"] = 1879507875; }; -- All the Birds of Anórien</v>
-      </c>
-      <c r="Q123" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R123">
@@ -16891,23 +16892,23 @@
         <v>122</v>
       </c>
       <c r="S123" t="str">
+        <f t="shared" si="56"/>
+        <v>[122] = {</v>
+      </c>
+      <c r="T123" t="str">
         <f t="shared" si="57"/>
-        <v>[122] = {</v>
-      </c>
-      <c r="T123" t="str">
+        <v xml:space="preserve">["ID"] = 1879507875; </v>
+      </c>
+      <c r="U123" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507875; </v>
       </c>
-      <c r="U123" t="str">
+      <c r="V123" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507875; </v>
-      </c>
-      <c r="V123" t="str">
+        <v/>
+      </c>
+      <c r="W123" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W123" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X123" t="e">
@@ -16915,31 +16916,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y123" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z123" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z123" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA123" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB123" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB123" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC123" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD123" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD123" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE123" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF123" t="e">
@@ -16947,27 +16948,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG123" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH123" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="AI123" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH123" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Anórien"; }; </v>
+      </c>
+      <c r="AJ123" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI123" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK123" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Anórien"; }; </v>
-      </c>
-      <c r="AJ123" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL123" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK123" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL123" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM123" t="str">
@@ -16990,11 +16991,11 @@
         <v>[1879507874] = 1, // Birds of Anórien: Common and Uncommon</v>
       </c>
       <c r="P124" t="str">
+        <f t="shared" si="33"/>
+        <v>[123] = {["ID"] = 1879507874; ["TIER"] = 1; }; -- Birds of Anórien: Common and Uncommon</v>
+      </c>
+      <c r="Q124" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[123] = {["ID"] = 1879507874; }; -- Birds of Anórien: Common and Uncommon</v>
-      </c>
-      <c r="Q124" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R124">
@@ -17002,23 +17003,23 @@
         <v>123</v>
       </c>
       <c r="S124" t="str">
+        <f t="shared" si="56"/>
+        <v>[123] = {</v>
+      </c>
+      <c r="T124" t="str">
         <f t="shared" si="57"/>
-        <v>[123] = {</v>
-      </c>
-      <c r="T124" t="str">
+        <v xml:space="preserve">["ID"] = 1879507874; </v>
+      </c>
+      <c r="U124" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507874; </v>
       </c>
-      <c r="U124" t="str">
+      <c r="V124" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507874; </v>
-      </c>
-      <c r="V124" t="str">
+        <v/>
+      </c>
+      <c r="W124" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W124" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X124" t="e">
@@ -17026,31 +17027,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y124" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z124" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z124" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA124" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB124" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB124" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC124" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD124" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD124" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE124" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF124" t="e">
@@ -17058,27 +17059,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG124" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH124" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI124" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH124" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Anórien: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AJ124" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI124" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK124" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Anórien: Common and Uncommon"; }; </v>
-      </c>
-      <c r="AJ124" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL124" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK124" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL124" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM124" t="str">
@@ -17101,11 +17102,11 @@
         <v>[1879507878] = 1, // Birds of Anórien: Rare</v>
       </c>
       <c r="P125" t="str">
+        <f t="shared" si="33"/>
+        <v>[124] = {["ID"] = 1879507878; ["TIER"] = 1; }; -- Birds of Anórien: Rare</v>
+      </c>
+      <c r="Q125" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[124] = {["ID"] = 1879507878; }; -- Birds of Anórien: Rare</v>
-      </c>
-      <c r="Q125" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R125">
@@ -17113,23 +17114,23 @@
         <v>124</v>
       </c>
       <c r="S125" t="str">
+        <f t="shared" si="56"/>
+        <v>[124] = {</v>
+      </c>
+      <c r="T125" t="str">
         <f t="shared" si="57"/>
-        <v>[124] = {</v>
-      </c>
-      <c r="T125" t="str">
+        <v xml:space="preserve">["ID"] = 1879507878; </v>
+      </c>
+      <c r="U125" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507878; </v>
       </c>
-      <c r="U125" t="str">
+      <c r="V125" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507878; </v>
-      </c>
-      <c r="V125" t="str">
+        <v/>
+      </c>
+      <c r="W125" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W125" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X125" t="e">
@@ -17137,31 +17138,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y125" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z125" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z125" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA125" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB125" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB125" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC125" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD125" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD125" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE125" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF125" t="e">
@@ -17169,27 +17170,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG125" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH125" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI125" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH125" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Anórien: Rare"; }; </v>
+      </c>
+      <c r="AJ125" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI125" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK125" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Anórien: Rare"; }; </v>
-      </c>
-      <c r="AJ125" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL125" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK125" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL125" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM125" t="str">
@@ -17212,11 +17213,11 @@
         <v>[1879507876] = 1, // The Rarest Bird in Anórien</v>
       </c>
       <c r="P126" t="str">
+        <f t="shared" si="33"/>
+        <v>[125] = {["ID"] = 1879507876; ["TIER"] = 1; }; -- The Rarest Bird in Anórien</v>
+      </c>
+      <c r="Q126" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[125] = {["ID"] = 1879507876; }; -- The Rarest Bird in Anórien</v>
-      </c>
-      <c r="Q126" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R126">
@@ -17224,23 +17225,23 @@
         <v>125</v>
       </c>
       <c r="S126" t="str">
+        <f t="shared" si="56"/>
+        <v>[125] = {</v>
+      </c>
+      <c r="T126" t="str">
         <f t="shared" si="57"/>
-        <v>[125] = {</v>
-      </c>
-      <c r="T126" t="str">
+        <v xml:space="preserve">["ID"] = 1879507876; </v>
+      </c>
+      <c r="U126" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507876; </v>
       </c>
-      <c r="U126" t="str">
+      <c r="V126" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507876; </v>
-      </c>
-      <c r="V126" t="str">
+        <v/>
+      </c>
+      <c r="W126" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W126" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X126" t="e">
@@ -17248,31 +17249,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y126" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z126" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z126" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA126" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB126" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB126" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC126" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD126" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD126" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE126" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF126" t="e">
@@ -17280,27 +17281,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG126" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH126" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI126" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH126" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Anórien"; }; </v>
+      </c>
+      <c r="AJ126" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI126" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK126" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Anórien"; }; </v>
-      </c>
-      <c r="AJ126" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL126" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK126" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL126" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM126" t="str">
@@ -17323,11 +17324,11 @@
         <v/>
       </c>
       <c r="P127" t="str">
+        <f t="shared" si="33"/>
+        <v>[126] = {["ID"] = 1879507932; }; -- All the Birds of the Wastes</v>
+      </c>
+      <c r="Q127" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[126] = {["ID"] = 1879507932; }; -- All the Birds of the Wastes</v>
-      </c>
-      <c r="Q127" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R127">
@@ -17335,23 +17336,23 @@
         <v>126</v>
       </c>
       <c r="S127" t="str">
+        <f t="shared" si="56"/>
+        <v>[126] = {</v>
+      </c>
+      <c r="T127" t="str">
         <f t="shared" si="57"/>
-        <v>[126] = {</v>
-      </c>
-      <c r="T127" t="str">
+        <v xml:space="preserve">["ID"] = 1879507932; </v>
+      </c>
+      <c r="U127" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507932; </v>
       </c>
-      <c r="U127" t="str">
+      <c r="V127" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507932; </v>
-      </c>
-      <c r="V127" t="str">
+        <v/>
+      </c>
+      <c r="W127" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W127" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X127" t="e">
@@ -17359,31 +17360,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y127" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z127" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z127" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA127" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB127" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB127" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC127" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC127" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD127" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD127" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE127" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF127" t="e">
@@ -17391,27 +17392,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG127" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH127" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="AI127" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH127" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Wastes"; }; </v>
+      </c>
+      <c r="AJ127" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI127" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK127" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of the Wastes"; }; </v>
-      </c>
-      <c r="AJ127" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL127" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK127" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL127" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM127" t="str">
@@ -17434,11 +17435,11 @@
         <v>[1879507937] = 1, // Birds of the Wastes: Common and Uncommon</v>
       </c>
       <c r="P128" t="str">
+        <f t="shared" si="33"/>
+        <v>[127] = {["ID"] = 1879507937; ["TIER"] = 1; }; -- Birds of the Wastes: Common and Uncommon</v>
+      </c>
+      <c r="Q128" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[127] = {["ID"] = 1879507937; }; -- Birds of the Wastes: Common and Uncommon</v>
-      </c>
-      <c r="Q128" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R128">
@@ -17446,23 +17447,23 @@
         <v>127</v>
       </c>
       <c r="S128" t="str">
+        <f t="shared" si="56"/>
+        <v>[127] = {</v>
+      </c>
+      <c r="T128" t="str">
         <f t="shared" si="57"/>
-        <v>[127] = {</v>
-      </c>
-      <c r="T128" t="str">
+        <v xml:space="preserve">["ID"] = 1879507937; </v>
+      </c>
+      <c r="U128" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507937; </v>
       </c>
-      <c r="U128" t="str">
+      <c r="V128" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507937; </v>
-      </c>
-      <c r="V128" t="str">
+        <v/>
+      </c>
+      <c r="W128" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W128" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X128" t="e">
@@ -17470,31 +17471,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y128" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z128" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z128" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA128" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB128" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB128" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC128" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD128" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD128" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE128" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF128" t="e">
@@ -17502,27 +17503,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG128" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH128" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI128" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH128" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Wastes: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AJ128" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI128" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK128" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Wastes: Common and Uncommon"; }; </v>
-      </c>
-      <c r="AJ128" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL128" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK128" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL128" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM128" t="str">
@@ -17545,11 +17546,11 @@
         <v>[1879507935] = 1, // Birds of the Wastes: Rare</v>
       </c>
       <c r="P129" t="str">
+        <f t="shared" si="33"/>
+        <v>[128] = {["ID"] = 1879507935; ["TIER"] = 1; }; -- Birds of the Wastes: Rare</v>
+      </c>
+      <c r="Q129" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[128] = {["ID"] = 1879507935; }; -- Birds of the Wastes: Rare</v>
-      </c>
-      <c r="Q129" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R129">
@@ -17557,23 +17558,23 @@
         <v>128</v>
       </c>
       <c r="S129" t="str">
+        <f t="shared" si="56"/>
+        <v>[128] = {</v>
+      </c>
+      <c r="T129" t="str">
         <f t="shared" si="57"/>
-        <v>[128] = {</v>
-      </c>
-      <c r="T129" t="str">
+        <v xml:space="preserve">["ID"] = 1879507935; </v>
+      </c>
+      <c r="U129" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507935; </v>
       </c>
-      <c r="U129" t="str">
+      <c r="V129" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507935; </v>
-      </c>
-      <c r="V129" t="str">
+        <v/>
+      </c>
+      <c r="W129" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W129" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X129" t="e">
@@ -17581,31 +17582,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y129" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z129" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z129" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA129" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB129" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB129" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC129" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD129" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD129" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE129" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF129" t="e">
@@ -17613,27 +17614,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG129" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH129" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI129" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH129" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Wastes: Rare"; }; </v>
+      </c>
+      <c r="AJ129" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI129" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK129" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of the Wastes: Rare"; }; </v>
-      </c>
-      <c r="AJ129" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL129" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK129" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL129" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM129" t="str">
@@ -17656,11 +17657,11 @@
         <v>[1879507933] = 1, // The Rarest Bird in the Wastes</v>
       </c>
       <c r="P130" t="str">
+        <f t="shared" si="33"/>
+        <v>[129] = {["ID"] = 1879507933; ["TIER"] = 1; }; -- The Rarest Bird in the Wastes</v>
+      </c>
+      <c r="Q130" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[129] = {["ID"] = 1879507933; }; -- The Rarest Bird in the Wastes</v>
-      </c>
-      <c r="Q130" s="1" t="e">
-        <f t="shared" si="56"/>
         <v>#N/A</v>
       </c>
       <c r="R130">
@@ -17668,23 +17669,23 @@
         <v>129</v>
       </c>
       <c r="S130" t="str">
+        <f t="shared" si="56"/>
+        <v>[129] = {</v>
+      </c>
+      <c r="T130" t="str">
         <f t="shared" si="57"/>
-        <v>[129] = {</v>
-      </c>
-      <c r="T130" t="str">
+        <v xml:space="preserve">["ID"] = 1879507933; </v>
+      </c>
+      <c r="U130" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507933; </v>
       </c>
-      <c r="U130" t="str">
+      <c r="V130" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507933; </v>
-      </c>
-      <c r="V130" t="str">
+        <v/>
+      </c>
+      <c r="W130" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W130" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X130" t="e">
@@ -17692,31 +17693,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y130" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z130" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z130" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA130" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB130" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB130" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC130" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD130" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD130" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE130" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF130" t="e">
@@ -17724,27 +17725,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG130" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH130" t="str">
+        <f t="shared" si="49"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI130" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH130" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Wastes"; }; </v>
+      </c>
+      <c r="AJ130" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI130" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK130" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in the Wastes"; }; </v>
-      </c>
-      <c r="AJ130" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL130" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK130" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL130" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM130" t="str">
@@ -17763,39 +17764,39 @@
         <v>0</v>
       </c>
       <c r="O131" t="str">
-        <f t="shared" ref="O131:O140" si="75">IF(AND(A131&gt;0,L131&gt;0),CONCATENATE("[",A131,"] = ",L131,", // ",C131),"")</f>
+        <f t="shared" ref="O131:O140" si="73">IF(AND(A131&gt;0,L131&gt;0),CONCATENATE("[",A131,"] = ",L131,", // ",C131),"")</f>
         <v/>
       </c>
       <c r="P131" t="str">
+        <f t="shared" ref="P131:P140" si="74">CONCATENATE(S131,U131,V131,AH131,AM131," -- ",C131)</f>
+        <v>[130] = {["ID"] = 1879507931; }; -- All the Birds of Lhingris</v>
+      </c>
+      <c r="Q131" s="1" t="e">
         <f t="shared" si="55"/>
-        <v>[130] = {["ID"] = 1879507931; }; -- All the Birds of Lhingris</v>
-      </c>
-      <c r="Q131" s="1" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R131">
+        <f t="shared" ref="R131:R140" si="75">ROW()-1</f>
+        <v>130</v>
+      </c>
+      <c r="S131" t="str">
         <f t="shared" si="56"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R131">
-        <f t="shared" ref="R131:R140" si="76">ROW()-1</f>
-        <v>130</v>
-      </c>
-      <c r="S131" t="str">
+        <v>[130] = {</v>
+      </c>
+      <c r="T131" t="str">
         <f t="shared" si="57"/>
-        <v>[130] = {</v>
-      </c>
-      <c r="T131" t="str">
+        <v xml:space="preserve">["ID"] = 1879507931; </v>
+      </c>
+      <c r="U131" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507931; </v>
       </c>
-      <c r="U131" t="str">
+      <c r="V131" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507931; </v>
-      </c>
-      <c r="V131" t="str">
+        <v/>
+      </c>
+      <c r="W131" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W131" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X131" t="e">
@@ -17803,31 +17804,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y131" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z131" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z131" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA131" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA131" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB131" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB131" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC131" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD131" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD131" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE131" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF131" t="e">
@@ -17835,27 +17836,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG131" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH131" t="str">
+        <f t="shared" ref="AH131:AH140" si="76">IF(L131&gt;0,CONCATENATE("[""TIER""] = ",TEXT(L131,"0"),"; "),"")</f>
+        <v/>
+      </c>
+      <c r="AI131" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH131" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Lhingris"; }; </v>
+      </c>
+      <c r="AJ131" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI131" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK131" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Lhingris"; }; </v>
-      </c>
-      <c r="AJ131" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL131" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK131" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL131" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM131" t="str">
@@ -17874,39 +17875,39 @@
         <v>1</v>
       </c>
       <c r="O132" t="str">
+        <f t="shared" si="73"/>
+        <v>[1879507936] = 1, // Birds of Lhingris: Common and Uncommon</v>
+      </c>
+      <c r="P132" t="str">
+        <f t="shared" si="74"/>
+        <v>[131] = {["ID"] = 1879507936; ["TIER"] = 1; }; -- Birds of Lhingris: Common and Uncommon</v>
+      </c>
+      <c r="Q132" s="1" t="e">
+        <f t="shared" si="55"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R132">
         <f t="shared" si="75"/>
-        <v>[1879507936] = 1, // Birds of Lhingris: Common and Uncommon</v>
-      </c>
-      <c r="P132" t="str">
-        <f t="shared" si="55"/>
-        <v>[131] = {["ID"] = 1879507936; }; -- Birds of Lhingris: Common and Uncommon</v>
-      </c>
-      <c r="Q132" s="1" t="e">
+        <v>131</v>
+      </c>
+      <c r="S132" t="str">
         <f t="shared" si="56"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R132">
-        <f t="shared" si="76"/>
-        <v>131</v>
-      </c>
-      <c r="S132" t="str">
+        <v>[131] = {</v>
+      </c>
+      <c r="T132" t="str">
         <f t="shared" si="57"/>
-        <v>[131] = {</v>
-      </c>
-      <c r="T132" t="str">
+        <v xml:space="preserve">["ID"] = 1879507936; </v>
+      </c>
+      <c r="U132" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507936; </v>
       </c>
-      <c r="U132" t="str">
+      <c r="V132" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507936; </v>
-      </c>
-      <c r="V132" t="str">
+        <v/>
+      </c>
+      <c r="W132" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W132" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X132" t="e">
@@ -17914,31 +17915,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y132" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z132" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z132" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA132" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB132" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB132" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC132" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD132" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD132" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE132" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF132" t="e">
@@ -17946,27 +17947,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG132" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH132" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI132" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH132" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lhingris: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AJ132" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI132" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK132" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lhingris: Common and Uncommon"; }; </v>
-      </c>
-      <c r="AJ132" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL132" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK132" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL132" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM132" t="str">
@@ -17985,39 +17986,39 @@
         <v>1</v>
       </c>
       <c r="O133" t="str">
+        <f t="shared" si="73"/>
+        <v>[1879507934] = 1, // Birds of Lhingris: Rare</v>
+      </c>
+      <c r="P133" t="str">
+        <f t="shared" si="74"/>
+        <v>[132] = {["ID"] = 1879507934; ["TIER"] = 1; }; -- Birds of Lhingris: Rare</v>
+      </c>
+      <c r="Q133" s="1" t="e">
+        <f t="shared" si="55"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R133">
         <f t="shared" si="75"/>
-        <v>[1879507934] = 1, // Birds of Lhingris: Rare</v>
-      </c>
-      <c r="P133" t="str">
-        <f t="shared" si="55"/>
-        <v>[132] = {["ID"] = 1879507934; }; -- Birds of Lhingris: Rare</v>
-      </c>
-      <c r="Q133" s="1" t="e">
+        <v>132</v>
+      </c>
+      <c r="S133" t="str">
         <f t="shared" si="56"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R133">
-        <f t="shared" si="76"/>
-        <v>132</v>
-      </c>
-      <c r="S133" t="str">
+        <v>[132] = {</v>
+      </c>
+      <c r="T133" t="str">
         <f t="shared" si="57"/>
-        <v>[132] = {</v>
-      </c>
-      <c r="T133" t="str">
+        <v xml:space="preserve">["ID"] = 1879507934; </v>
+      </c>
+      <c r="U133" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507934; </v>
       </c>
-      <c r="U133" t="str">
+      <c r="V133" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507934; </v>
-      </c>
-      <c r="V133" t="str">
+        <v/>
+      </c>
+      <c r="W133" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W133" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X133" t="e">
@@ -18025,31 +18026,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y133" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z133" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z133" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA133" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB133" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB133" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC133" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD133" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD133" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE133" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF133" t="e">
@@ -18057,27 +18058,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG133" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH133" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI133" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH133" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lhingris: Rare"; }; </v>
+      </c>
+      <c r="AJ133" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI133" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK133" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Lhingris: Rare"; }; </v>
-      </c>
-      <c r="AJ133" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL133" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK133" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL133" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM133" t="str">
@@ -18096,39 +18097,39 @@
         <v>1</v>
       </c>
       <c r="O134" t="str">
+        <f t="shared" si="73"/>
+        <v>[1879507938] = 1, // The Rarest Bird in Lhingris</v>
+      </c>
+      <c r="P134" t="str">
+        <f t="shared" si="74"/>
+        <v>[133] = {["ID"] = 1879507938; ["TIER"] = 1; }; -- The Rarest Bird in Lhingris</v>
+      </c>
+      <c r="Q134" s="1" t="e">
+        <f t="shared" si="55"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R134">
         <f t="shared" si="75"/>
-        <v>[1879507938] = 1, // The Rarest Bird in Lhingris</v>
-      </c>
-      <c r="P134" t="str">
-        <f t="shared" si="55"/>
-        <v>[133] = {["ID"] = 1879507938; }; -- The Rarest Bird in Lhingris</v>
-      </c>
-      <c r="Q134" s="1" t="e">
+        <v>133</v>
+      </c>
+      <c r="S134" t="str">
         <f t="shared" si="56"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R134">
-        <f t="shared" si="76"/>
-        <v>133</v>
-      </c>
-      <c r="S134" t="str">
+        <v>[133] = {</v>
+      </c>
+      <c r="T134" t="str">
         <f t="shared" si="57"/>
-        <v>[133] = {</v>
-      </c>
-      <c r="T134" t="str">
+        <v xml:space="preserve">["ID"] = 1879507938; </v>
+      </c>
+      <c r="U134" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507938; </v>
       </c>
-      <c r="U134" t="str">
+      <c r="V134" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507938; </v>
-      </c>
-      <c r="V134" t="str">
+        <v/>
+      </c>
+      <c r="W134" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W134" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X134" t="e">
@@ -18136,31 +18137,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y134" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z134" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z134" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA134" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA134" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB134" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB134" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC134" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD134" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD134" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE134" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF134" t="e">
@@ -18168,27 +18169,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG134" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH134" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI134" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH134" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Lhingris"; }; </v>
+      </c>
+      <c r="AJ134" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI134" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK134" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Lhingris"; }; </v>
-      </c>
-      <c r="AJ134" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL134" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK134" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL134" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM134" t="str">
@@ -18207,39 +18208,39 @@
         <v>0</v>
       </c>
       <c r="O135" t="str">
+        <f t="shared" si="73"/>
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <f t="shared" si="74"/>
+        <v>[134] = {["ID"] = 1879507939; }; -- All the Birds of Agarnaith</v>
+      </c>
+      <c r="Q135" s="1" t="e">
+        <f t="shared" si="55"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R135">
         <f t="shared" si="75"/>
-        <v/>
-      </c>
-      <c r="P135" t="str">
-        <f t="shared" si="55"/>
-        <v>[134] = {["ID"] = 1879507939; }; -- All the Birds of Agarnaith</v>
-      </c>
-      <c r="Q135" s="1" t="e">
+        <v>134</v>
+      </c>
+      <c r="S135" t="str">
         <f t="shared" si="56"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R135">
-        <f t="shared" si="76"/>
-        <v>134</v>
-      </c>
-      <c r="S135" t="str">
+        <v>[134] = {</v>
+      </c>
+      <c r="T135" t="str">
         <f t="shared" si="57"/>
-        <v>[134] = {</v>
-      </c>
-      <c r="T135" t="str">
+        <v xml:space="preserve">["ID"] = 1879507939; </v>
+      </c>
+      <c r="U135" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507939; </v>
       </c>
-      <c r="U135" t="str">
+      <c r="V135" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507939; </v>
-      </c>
-      <c r="V135" t="str">
+        <v/>
+      </c>
+      <c r="W135" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W135" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X135" t="e">
@@ -18247,31 +18248,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y135" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z135" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z135" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA135" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB135" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB135" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC135" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD135" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD135" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE135" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF135" t="e">
@@ -18279,27 +18280,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG135" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH135" t="str">
+        <f t="shared" si="76"/>
+        <v/>
+      </c>
+      <c r="AI135" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH135" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Agarnaith"; }; </v>
+      </c>
+      <c r="AJ135" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI135" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK135" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "All the Birds of Agarnaith"; }; </v>
-      </c>
-      <c r="AJ135" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL135" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK135" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL135" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM135" t="str">
@@ -18318,39 +18319,39 @@
         <v>1</v>
       </c>
       <c r="O136" t="str">
+        <f t="shared" si="73"/>
+        <v>[1879507940] = 1, // Birds of Agarnaith: Common and Uncommon</v>
+      </c>
+      <c r="P136" t="str">
+        <f t="shared" si="74"/>
+        <v>[135] = {["ID"] = 1879507940; ["TIER"] = 1; }; -- Birds of Agarnaith: Common and Uncommon</v>
+      </c>
+      <c r="Q136" s="1" t="e">
+        <f t="shared" si="55"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R136">
         <f t="shared" si="75"/>
-        <v>[1879507940] = 1, // Birds of Agarnaith: Common and Uncommon</v>
-      </c>
-      <c r="P136" t="str">
-        <f t="shared" si="55"/>
-        <v>[135] = {["ID"] = 1879507940; }; -- Birds of Agarnaith: Common and Uncommon</v>
-      </c>
-      <c r="Q136" s="1" t="e">
+        <v>135</v>
+      </c>
+      <c r="S136" t="str">
         <f t="shared" si="56"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R136">
-        <f t="shared" si="76"/>
-        <v>135</v>
-      </c>
-      <c r="S136" t="str">
+        <v>[135] = {</v>
+      </c>
+      <c r="T136" t="str">
         <f t="shared" si="57"/>
-        <v>[135] = {</v>
-      </c>
-      <c r="T136" t="str">
+        <v xml:space="preserve">["ID"] = 1879507940; </v>
+      </c>
+      <c r="U136" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507940; </v>
       </c>
-      <c r="U136" t="str">
+      <c r="V136" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507940; </v>
-      </c>
-      <c r="V136" t="str">
+        <v/>
+      </c>
+      <c r="W136" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W136" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X136" t="e">
@@ -18358,31 +18359,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y136" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z136" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z136" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA136" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB136" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB136" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC136" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD136" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD136" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE136" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF136" t="e">
@@ -18390,27 +18391,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG136" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH136" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI136" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH136" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Agarnaith: Common and Uncommon"; }; </v>
+      </c>
+      <c r="AJ136" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI136" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK136" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Agarnaith: Common and Uncommon"; }; </v>
-      </c>
-      <c r="AJ136" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL136" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK136" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL136" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM136" t="str">
@@ -18429,39 +18430,39 @@
         <v>1</v>
       </c>
       <c r="O137" t="str">
+        <f t="shared" si="73"/>
+        <v>[1879507942] = 1, // Birds of Agarnaith: Rare</v>
+      </c>
+      <c r="P137" t="str">
+        <f t="shared" si="74"/>
+        <v>[136] = {["ID"] = 1879507942; ["TIER"] = 1; }; -- Birds of Agarnaith: Rare</v>
+      </c>
+      <c r="Q137" s="1" t="e">
+        <f t="shared" si="55"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R137">
         <f t="shared" si="75"/>
-        <v>[1879507942] = 1, // Birds of Agarnaith: Rare</v>
-      </c>
-      <c r="P137" t="str">
-        <f t="shared" si="55"/>
-        <v>[136] = {["ID"] = 1879507942; }; -- Birds of Agarnaith: Rare</v>
-      </c>
-      <c r="Q137" s="1" t="e">
+        <v>136</v>
+      </c>
+      <c r="S137" t="str">
         <f t="shared" si="56"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R137">
-        <f t="shared" si="76"/>
-        <v>136</v>
-      </c>
-      <c r="S137" t="str">
+        <v>[136] = {</v>
+      </c>
+      <c r="T137" t="str">
         <f t="shared" si="57"/>
-        <v>[136] = {</v>
-      </c>
-      <c r="T137" t="str">
+        <v xml:space="preserve">["ID"] = 1879507942; </v>
+      </c>
+      <c r="U137" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507942; </v>
       </c>
-      <c r="U137" t="str">
+      <c r="V137" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507942; </v>
-      </c>
-      <c r="V137" t="str">
+        <v/>
+      </c>
+      <c r="W137" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W137" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X137" t="e">
@@ -18469,31 +18470,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y137" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z137" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z137" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA137" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA137" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB137" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB137" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC137" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD137" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD137" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE137" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF137" t="e">
@@ -18501,27 +18502,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG137" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH137" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI137" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH137" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Agarnaith: Rare"; }; </v>
+      </c>
+      <c r="AJ137" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI137" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK137" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "Birds of Agarnaith: Rare"; }; </v>
-      </c>
-      <c r="AJ137" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL137" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK137" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL137" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM137" t="str">
@@ -18540,39 +18541,39 @@
         <v>1</v>
       </c>
       <c r="O138" t="str">
+        <f t="shared" si="73"/>
+        <v>[1879507943] = 1, // The Rarest Bird in Agarnaith</v>
+      </c>
+      <c r="P138" t="str">
+        <f t="shared" si="74"/>
+        <v>[137] = {["ID"] = 1879507943; ["TIER"] = 1; }; -- The Rarest Bird in Agarnaith</v>
+      </c>
+      <c r="Q138" s="1" t="e">
+        <f t="shared" si="55"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R138">
         <f t="shared" si="75"/>
-        <v>[1879507943] = 1, // The Rarest Bird in Agarnaith</v>
-      </c>
-      <c r="P138" t="str">
-        <f t="shared" si="55"/>
-        <v>[137] = {["ID"] = 1879507943; }; -- The Rarest Bird in Agarnaith</v>
-      </c>
-      <c r="Q138" s="1" t="e">
+        <v>137</v>
+      </c>
+      <c r="S138" t="str">
         <f t="shared" si="56"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R138">
-        <f t="shared" si="76"/>
-        <v>137</v>
-      </c>
-      <c r="S138" t="str">
+        <v>[137] = {</v>
+      </c>
+      <c r="T138" t="str">
         <f t="shared" si="57"/>
-        <v>[137] = {</v>
-      </c>
-      <c r="T138" t="str">
+        <v xml:space="preserve">["ID"] = 1879507943; </v>
+      </c>
+      <c r="U138" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507943; </v>
       </c>
-      <c r="U138" t="str">
+      <c r="V138" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507943; </v>
-      </c>
-      <c r="V138" t="str">
+        <v/>
+      </c>
+      <c r="W138" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W138" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X138" t="e">
@@ -18580,31 +18581,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y138" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z138" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z138" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA138" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA138" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB138" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB138" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC138" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD138" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD138" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE138" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF138" t="e">
@@ -18612,27 +18613,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG138" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH138" t="str">
+        <f t="shared" si="76"/>
+        <v xml:space="preserve">["TIER"] = 1; </v>
+      </c>
+      <c r="AI138" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH138" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Agarnaith"; }; </v>
+      </c>
+      <c r="AJ138" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 1; </v>
-      </c>
-      <c r="AI138" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK138" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest Bird in Agarnaith"; }; </v>
-      </c>
-      <c r="AJ138" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL138" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK138" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL138" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM138" t="str">
@@ -18651,39 +18652,39 @@
         <v>0</v>
       </c>
       <c r="O139" t="str">
+        <f t="shared" si="73"/>
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <f t="shared" si="74"/>
+        <v>[138] = {["ID"] = 1879507941; }; -- The Rarest of Birds in Gondor and Mordor</v>
+      </c>
+      <c r="Q139" s="1" t="e">
+        <f t="shared" si="55"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R139">
         <f t="shared" si="75"/>
-        <v/>
-      </c>
-      <c r="P139" t="str">
-        <f t="shared" si="55"/>
-        <v>[138] = {["ID"] = 1879507941; }; -- The Rarest of Birds in Gondor and Mordor</v>
-      </c>
-      <c r="Q139" s="1" t="e">
+        <v>138</v>
+      </c>
+      <c r="S139" t="str">
         <f t="shared" si="56"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R139">
-        <f t="shared" si="76"/>
-        <v>138</v>
-      </c>
-      <c r="S139" t="str">
+        <v>[138] = {</v>
+      </c>
+      <c r="T139" t="str">
         <f t="shared" si="57"/>
-        <v>[138] = {</v>
-      </c>
-      <c r="T139" t="str">
+        <v xml:space="preserve">["ID"] = 1879507941; </v>
+      </c>
+      <c r="U139" t="str">
         <f t="shared" si="58"/>
         <v xml:space="preserve">["ID"] = 1879507941; </v>
       </c>
-      <c r="U139" t="str">
+      <c r="V139" t="str">
         <f t="shared" si="59"/>
-        <v xml:space="preserve">["ID"] = 1879507941; </v>
-      </c>
-      <c r="V139" t="str">
+        <v/>
+      </c>
+      <c r="W139" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W139" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X139" t="e">
@@ -18691,31 +18692,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y139" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z139" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z139" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA139" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA139" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB139" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB139" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC139" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD139" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD139" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE139" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF139" t="e">
@@ -18723,27 +18724,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG139" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH139" t="str">
+        <f t="shared" si="76"/>
+        <v/>
+      </c>
+      <c r="AI139" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH139" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest of Birds in Gondor and Mordor"; }; </v>
+      </c>
+      <c r="AJ139" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI139" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK139" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = "The Rarest of Birds in Gondor and Mordor"; }; </v>
-      </c>
-      <c r="AJ139" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL139" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK139" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL139" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM139" t="str">
@@ -18753,39 +18754,39 @@
     </row>
     <row r="140" spans="1:39" x14ac:dyDescent="0.25">
       <c r="O140" t="str">
+        <f t="shared" si="73"/>
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <f t="shared" si="74"/>
+        <v xml:space="preserve">[139] = {}; -- </v>
+      </c>
+      <c r="Q140" s="1" t="e">
+        <f t="shared" si="55"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R140">
         <f t="shared" si="75"/>
-        <v/>
-      </c>
-      <c r="P140" t="str">
-        <f t="shared" si="55"/>
-        <v xml:space="preserve">[139] = {}; -- </v>
-      </c>
-      <c r="Q140" s="1" t="e">
+        <v>139</v>
+      </c>
+      <c r="S140" t="str">
         <f t="shared" si="56"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R140">
-        <f t="shared" si="76"/>
-        <v>139</v>
-      </c>
-      <c r="S140" t="str">
+        <v>[139] = {</v>
+      </c>
+      <c r="T140" t="str">
         <f t="shared" si="57"/>
-        <v>[139] = {</v>
-      </c>
-      <c r="T140" t="str">
+        <v xml:space="preserve">                     </v>
+      </c>
+      <c r="U140" t="str">
         <f t="shared" si="58"/>
-        <v xml:space="preserve">                     </v>
-      </c>
-      <c r="U140" t="str">
+        <v/>
+      </c>
+      <c r="V140" t="str">
         <f t="shared" si="59"/>
         <v/>
       </c>
-      <c r="V140" t="str">
+      <c r="W140" s="1" t="str">
         <f t="shared" si="60"/>
-        <v/>
-      </c>
-      <c r="W140" s="1" t="str">
-        <f t="shared" si="61"/>
         <v/>
       </c>
       <c r="X140" t="e">
@@ -18793,31 +18794,31 @@
         <v>#N/A</v>
       </c>
       <c r="Y140" t="e">
+        <f t="shared" si="61"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z140" t="str">
         <f t="shared" si="62"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z140" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="str">
         <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="AA140" t="str">
+        <v xml:space="preserve">["VXP"] = 0; </v>
+      </c>
+      <c r="AB140" t="str">
         <f t="shared" si="64"/>
-        <v xml:space="preserve">["VXP"] = 0; </v>
-      </c>
-      <c r="AB140" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="str">
         <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AC140" t="str">
+        <v xml:space="preserve">["LP"] = 0; </v>
+      </c>
+      <c r="AD140" t="str">
         <f t="shared" si="66"/>
-        <v xml:space="preserve">["LP"] = 0; </v>
-      </c>
-      <c r="AD140" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="str">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE140" t="str">
-        <f t="shared" si="68"/>
         <v xml:space="preserve">["REP"] = 0; </v>
       </c>
       <c r="AF140" t="e">
@@ -18825,27 +18826,27 @@
         <v>#N/A</v>
       </c>
       <c r="AG140" t="e">
+        <f t="shared" si="68"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH140" t="str">
+        <f t="shared" si="76"/>
+        <v/>
+      </c>
+      <c r="AI140" t="str">
         <f t="shared" si="69"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH140" t="str">
+        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AJ140" t="str">
         <f t="shared" si="70"/>
-        <v xml:space="preserve">["TIER"] = 0; </v>
-      </c>
-      <c r="AI140" t="str">
+        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AK140" t="str">
         <f t="shared" si="71"/>
-        <v xml:space="preserve">["NAME"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AJ140" t="str">
+        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
+      </c>
+      <c r="AL140" t="str">
         <f t="shared" si="72"/>
-        <v xml:space="preserve">["LORE"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AK140" t="str">
-        <f t="shared" si="73"/>
-        <v xml:space="preserve">["SUMMARY"] = { ["EN"] = ""; }; </v>
-      </c>
-      <c r="AL140" t="str">
-        <f t="shared" si="74"/>
         <v/>
       </c>
       <c r="AM140" t="str">
